--- a/templates/Калькуляция_проект_v1.xlsx
+++ b/templates/Калькуляция_проект_v1.xlsx
@@ -11,11 +11,12 @@
     <sheet name="Калькуляция" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Металл" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Параметры" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Касса заказа" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Касса" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Инструкция" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Калькуляция'!$B$15:$L$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Металл'!$B$5:$J$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,11 +24,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="167" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -192,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -228,6 +230,7 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -235,6 +238,9 @@
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -627,7 +633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G49"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -745,7 +751,7 @@
     <row r="10">
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Клиент (опц.)</t>
+          <t>Клиент</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
@@ -760,6 +766,12 @@
       </c>
     </row>
     <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>№ клиента</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Агентские</t>
@@ -1116,7 +1128,7 @@
     <row r="42">
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Строка 20% — базовый ориентир. Целевую маржу меняйте на листе Параметры — пересчитается рекомендуемая цена.</t>
+          <t>Строка 20% — базовый ориентир. Целевую маржу меняйте на листе Параметры.</t>
         </is>
       </c>
     </row>
@@ -1168,10 +1180,11 @@
     <row r="49">
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Порядок: 1) Металл и Калькуляция → 2) рекомендуемая цена → 3) вписать цену КП в D24 → 4) проверить статус.</t>
-        </is>
-      </c>
-    </row>
+          <t>Рабочий контур: Металл → Калькуляция → Сводка (цена КП). Лист «Касса» — только ПОСЛЕ сделки, для авансов/выплат. На расчёт цены НЕ влияет — можно не трогать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="B2:G2"/>
@@ -1188,7 +1201,6 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B49:G49"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B29:C29"/>
@@ -1202,6 +1214,7 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B49:G50"/>
     <mergeCell ref="B26:C26"/>
   </mergeCells>
   <conditionalFormatting sqref="D31">
@@ -1228,7 +1241,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$B$19:$B$24</formula1>
+      <formula1>Параметры!$B$19:$B$26</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1255,7 +1268,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="3" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
     <col width="3" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -2215,7 +2228,7 @@
         </is>
       </c>
       <c r="E36" s="28">
-        <f>Металл!H19</f>
+        <f>Металл!H37</f>
         <v/>
       </c>
       <c r="F36" s="30" t="n">
@@ -2240,7 +2253,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>Себестоимость проката (цена поставщика)</t>
+          <t>Себестоимость проката (каталог, цена за шт 6м)</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2274,7 @@
         </is>
       </c>
       <c r="E37" s="28">
-        <f>Металл!H28</f>
+        <f>Металл!H52</f>
         <v/>
       </c>
       <c r="F37" s="30" t="n">
@@ -2303,7 +2316,7 @@
         </is>
       </c>
       <c r="E38" s="28">
-        <f>Металл!H39</f>
+        <f>Металл!H67</f>
         <v/>
       </c>
       <c r="F38" s="30" t="n">
@@ -2345,7 +2358,7 @@
         </is>
       </c>
       <c r="E39" s="28">
-        <f>Металл!H48</f>
+        <f>Металл!H82</f>
         <v/>
       </c>
       <c r="F39" s="30" t="n">
@@ -4901,7 +4914,7 @@
     <row r="116">
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Пустые строки ниже — для своих позиций. Тип «закупка» включает наценку менеджера автоматически.</t>
+          <t>Пустые строки — для своих позиций. Тип «закупка» включает наценку менеджера автоматически.</t>
         </is>
       </c>
     </row>
@@ -4937,38 +4950,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I54"/>
+  <dimension ref="B2:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>МЕТАЛЛ И КОМПЛЕКТУЮЩИЕ</t>
+          <t>МЕТАЛЛ И КОМПЛЕКТУЮЩИЕ — каталог</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>F — цена поставщика (обновляйте по прайсу). D — кол-во под заказ. Наценка менеджера: себестоимость × % (исправлена ошибка старого шаблона G×15%).</t>
+          <t>Цена поставщика = за 1 шт (штанга 6 м). Кол-во — сколько штанг в заказ. Вес 6м — справочно. Наценка менеджера: себестоимость × % из Параметров.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ПРОКАТ</t>
+          <t>ПРОКАТ (каталог поставщика)</t>
         </is>
       </c>
       <c r="C4" s="11" t="n"/>
@@ -5002,7 +5016,7 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Цена поставщика</t>
+          <t>Цена поставщика, ₽/шт (6м)</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -5018,18 +5032,23 @@
       <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Вес 6м, кг</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Квадрат</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>15х15х1.5</t>
+          <t>10х10</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
@@ -5041,7 +5060,7 @@
         </is>
       </c>
       <c r="F6" s="29" t="n">
-        <v>1200</v>
+        <v>428.3</v>
       </c>
       <c r="G6" s="9">
         <f>H6*(1+Параметры!$C$6)</f>
@@ -5055,16 +5074,19 @@
         <f>H6*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J6" s="31" t="n">
+        <v>5.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Квадрат</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>15х15х2.0</t>
+          <t>12х12</t>
         </is>
       </c>
       <c r="D7" s="6" t="n">
@@ -5076,7 +5098,7 @@
         </is>
       </c>
       <c r="F7" s="29" t="n">
-        <v>650</v>
+        <v>596.26</v>
       </c>
       <c r="G7" s="9">
         <f>H7*(1+Параметры!$C$6)</f>
@@ -5090,16 +5112,19 @@
         <f>H7*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J7" s="31" t="n">
+        <v>7.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Квадрат</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>20х20х1.5</t>
+          <t>14х14</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
@@ -5111,7 +5136,7 @@
         </is>
       </c>
       <c r="F8" s="29" t="n">
-        <v>575.7</v>
+        <v>797.8099999999999</v>
       </c>
       <c r="G8" s="9">
         <f>H8*(1+Параметры!$C$6)</f>
@@ -5125,16 +5150,19 @@
         <f>H8*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J8" s="31" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Квадрат</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>20х20х2.0</t>
+          <t>16х16</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
@@ -5145,7 +5173,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F9" s="29" t="n"/>
+      <c r="F9" s="29" t="n">
+        <v>1058.15</v>
+      </c>
       <c r="G9" s="9">
         <f>H9*(1+Параметры!$C$6)</f>
         <v/>
@@ -5158,16 +5188,19 @@
         <f>H9*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J9" s="31" t="n">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>50х25</t>
+          <t>15х15х1.5</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
@@ -5179,7 +5212,7 @@
         </is>
       </c>
       <c r="F10" s="29" t="n">
-        <v>1200</v>
+        <v>383.8</v>
       </c>
       <c r="G10" s="9">
         <f>H10*(1+Параметры!$C$6)</f>
@@ -5193,16 +5226,19 @@
         <f>H10*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J10" s="31" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Труба профильная</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>40х20</t>
+          <t>20х20х1.5</t>
         </is>
       </c>
       <c r="D11" s="6" t="n">
@@ -5214,7 +5250,7 @@
         </is>
       </c>
       <c r="F11" s="29" t="n">
-        <v>850</v>
+        <v>575.7</v>
       </c>
       <c r="G11" s="9">
         <f>H11*(1+Параметры!$C$6)</f>
@@ -5228,16 +5264,19 @@
         <f>H11*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J11" s="31" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Круг</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>40х40х1.5</t>
+          <t>20х20х2.0</t>
         </is>
       </c>
       <c r="D12" s="6" t="n">
@@ -5249,7 +5288,7 @@
         </is>
       </c>
       <c r="F12" s="29" t="n">
-        <v>750</v>
+        <v>586.53</v>
       </c>
       <c r="G12" s="9">
         <f>H12*(1+Параметры!$C$6)</f>
@@ -5263,16 +5302,19 @@
         <f>H12*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J12" s="31" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Квадрат</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>40х40х2.0</t>
+          <t>30х30х2.0</t>
         </is>
       </c>
       <c r="D13" s="6" t="n">
@@ -5284,7 +5326,7 @@
         </is>
       </c>
       <c r="F13" s="29" t="n">
-        <v>690</v>
+        <v>921.6900000000001</v>
       </c>
       <c r="G13" s="9">
         <f>H13*(1+Параметры!$C$6)</f>
@@ -5298,16 +5340,19 @@
         <f>H13*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J13" s="31" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Квадрат</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>40х40х3.0</t>
+          <t>40х40х1.5</t>
         </is>
       </c>
       <c r="D14" s="6" t="n">
@@ -5318,7 +5363,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F14" s="29" t="n"/>
+      <c r="F14" s="29" t="n">
+        <v>1151.4</v>
+      </c>
       <c r="G14" s="9">
         <f>H14*(1+Параметры!$C$6)</f>
         <v/>
@@ -5331,16 +5378,19 @@
         <f>H14*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J14" s="31" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>Труба квадрат.</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>10х10</t>
+          <t>40х40х2.0</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
@@ -5351,7 +5401,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F15" s="29" t="n"/>
+      <c r="F15" s="29" t="n">
+        <v>1256.85</v>
+      </c>
       <c r="G15" s="9">
         <f>H15*(1+Параметры!$C$6)</f>
         <v/>
@@ -5364,16 +5416,19 @@
         <f>H15*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J15" s="31" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>Труба прямоуг.</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>12х12</t>
+          <t>40х20х1.5</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -5384,7 +5439,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F16" s="29" t="n"/>
+      <c r="F16" s="29" t="n">
+        <v>863.55</v>
+      </c>
       <c r="G16" s="9">
         <f>H16*(1+Параметры!$C$6)</f>
         <v/>
@@ -5397,16 +5454,19 @@
         <f>H16*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J16" s="31" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>Труба прямоуг.</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>14х14</t>
+          <t>40х20х2.0</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
@@ -5417,7 +5477,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F17" s="29" t="n"/>
+      <c r="F17" s="29" t="n">
+        <v>921.6900000000001</v>
+      </c>
       <c r="G17" s="9">
         <f>H17*(1+Параметры!$C$6)</f>
         <v/>
@@ -5430,16 +5492,19 @@
         <f>H17*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J17" s="31" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>Труба прямоуг.</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>16х16</t>
+          <t>50х25х1.5</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
@@ -5450,7 +5515,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="F18" s="29" t="n"/>
+      <c r="F18" s="29" t="n">
+        <v>1151.4</v>
+      </c>
       <c r="G18" s="9">
         <f>H18*(1+Параметры!$C$6)</f>
         <v/>
@@ -5463,85 +5530,211 @@
         <f>H18*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J18" s="31" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
-      <c r="F19" s="31" t="inlineStr">
-        <is>
-          <t>Прокат — себестоимость:</t>
-        </is>
-      </c>
-      <c r="G19" s="13">
-        <f>SUM(G6:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="13">
-        <f>SUM(H6:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="13">
-        <f>SUM(I6:I18)</f>
-        <v/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Труба прямоуг.</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>50х25х2.0</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>1173.06</v>
+      </c>
+      <c r="G19" s="9">
+        <f>H19*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>IF(OR(D19="",F19=""),0,D19*F19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="9">
+        <f>H19*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J19" s="31" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>20х4 мм</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>397.04</v>
+      </c>
+      <c r="G20" s="9">
+        <f>H20*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>IF(OR(D20="",F20=""),0,D20*F20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="9">
+        <f>H20*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J20" s="31" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ПЛАЗМА / ЛАЗЕР</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>25х4 мм</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F21" s="29" t="n">
+        <v>493.88</v>
+      </c>
+      <c r="G21" s="9">
+        <f>H21*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>IF(OR(D21="",F21=""),0,D21*F21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="9">
+        <f>H21*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J21" s="31" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>30х4 мм</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F22" s="29" t="n">
+        <v>557.85</v>
+      </c>
+      <c r="G22" s="9">
+        <f>H22*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>IF(OR(D22="",F22=""),0,D22*F22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="9">
+        <f>H22*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J22" s="31" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Позиция</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Сечение</t>
-        </is>
-      </c>
-      <c r="D23" s="10" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="F23" s="10" t="inlineStr">
-        <is>
-          <t>Цена поставщика</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>Сумма</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>Наценка</t>
-        </is>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>40х4 мм</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F23" s="29" t="n">
+        <v>731.6</v>
+      </c>
+      <c r="G23" s="9">
+        <f>H23*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF(OR(D23="",F23=""),0,D23*F23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>H23*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J23" s="31" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>50х4 мм</t>
+        </is>
+      </c>
       <c r="D24" s="6" t="n">
         <v>0</v>
       </c>
@@ -5551,23 +5744,35 @@
         </is>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0</v>
+        <v>914.5</v>
       </c>
       <c r="G24" s="9">
-        <f>H24</f>
+        <f>H24*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H24" s="9">
         <f>IF(OR(D24="",F24=""),0,D24*F24)</f>
         <v/>
       </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
+      <c r="I24" s="9">
+        <f>H24*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J24" s="31" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Полоса</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>100х10 мм</t>
+        </is>
+      </c>
       <c r="D25" s="6" t="n">
         <v>0</v>
       </c>
@@ -5577,23 +5782,35 @@
         </is>
       </c>
       <c r="F25" s="29" t="n">
-        <v>0</v>
+        <v>4687.83</v>
       </c>
       <c r="G25" s="9">
-        <f>H25</f>
+        <f>H25*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H25" s="9">
         <f>IF(OR(D25="",F25=""),0,D25*F25)</f>
         <v/>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>0</v>
+      <c r="I25" s="9">
+        <f>H25*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J25" s="31" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Труба в/г</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>15х2.8</t>
+        </is>
+      </c>
       <c r="D26" s="6" t="n">
         <v>0</v>
       </c>
@@ -5603,23 +5820,35 @@
         </is>
       </c>
       <c r="F26" s="29" t="n">
-        <v>0</v>
+        <v>641.52</v>
       </c>
       <c r="G26" s="9">
-        <f>H26</f>
+        <f>H26*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H26" s="9">
         <f>IF(OR(D26="",F26=""),0,D26*F26)</f>
         <v/>
       </c>
-      <c r="I26" s="9" t="n">
-        <v>0</v>
+      <c r="I26" s="9">
+        <f>H26*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J26" s="31" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Труба в/г</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>20х2.8</t>
+        </is>
+      </c>
       <c r="D27" s="6" t="n">
         <v>0</v>
       </c>
@@ -5629,96 +5858,223 @@
         </is>
       </c>
       <c r="F27" s="29" t="n">
-        <v>0</v>
+        <v>882.09</v>
       </c>
       <c r="G27" s="9">
-        <f>H27</f>
+        <f>H27*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H27" s="9">
         <f>IF(OR(D27="",F27=""),0,D27*F27)</f>
         <v/>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>0</v>
+      <c r="I27" s="9">
+        <f>H27*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J27" s="31" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="28">
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Плазма — себестоимость:</t>
-        </is>
-      </c>
-      <c r="H28" s="13">
-        <f>SUM(H24:H27)</f>
-        <v/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Труба в/г</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>25х3.2</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F28" s="29" t="n">
+        <v>1268.8</v>
+      </c>
+      <c r="G28" s="9">
+        <f>H28*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>IF(OR(D28="",F28=""),0,D28*F28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="9">
+        <f>H28*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J28" s="31" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Труба в/г</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>32х3.2</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F29" s="29" t="n">
+        <v>1586</v>
+      </c>
+      <c r="G29" s="9">
+        <f>H29*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>IF(OR(D29="",F29=""),0,D29*F29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="9">
+        <f>H29*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J29" s="31" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>КОВАНЫЕ ЭЛЕМЕНТЫ / СПЕЦ. ПРОКАТ</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="4" t="n"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Труба в/г</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>40х3.5</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F30" s="29" t="n">
+        <v>1982.5</v>
+      </c>
+      <c r="G30" s="9">
+        <f>H30*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>IF(OR(D30="",F30=""),0,D30*F30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="9">
+        <f>H30*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J30" s="31" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Прокат круглый</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Ø6</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F31" s="29" t="n">
+        <v>156.24</v>
+      </c>
+      <c r="G31" s="9">
+        <f>H31*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF(OR(D31="",F31=""),0,D31*F31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="9">
+        <f>H31*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="32">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>Элемент</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Сечение</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="inlineStr">
-        <is>
-          <t>Цена поставщика</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="inlineStr">
-        <is>
-          <t>С наценкой</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
-        <is>
-          <t>Наценка менеджера</t>
-        </is>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Прокат круглый</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Ø8</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F32" s="29" t="n">
+        <v>270.87</v>
+      </c>
+      <c r="G32" s="9">
+        <f>H32*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>IF(OR(D32="",F32=""),0,D32*F32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="9">
+        <f>H32*Параметры!$C$6</f>
+        <v/>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>11.032</t>
+          <t>Прокат круглый</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>12х6</t>
+          <t>Ø10</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
@@ -5730,7 +6086,7 @@
         </is>
       </c>
       <c r="F33" s="29" t="n">
-        <v>50</v>
+        <v>387.8</v>
       </c>
       <c r="G33" s="9">
         <f>H33*(1+Параметры!$C$6)</f>
@@ -5744,16 +6100,19 @@
         <f>H33*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J33" s="31" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>41.401</t>
+          <t>Прокат круглый</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Ø12</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
@@ -5765,7 +6124,7 @@
         </is>
       </c>
       <c r="F34" s="29" t="n">
-        <v>230</v>
+        <v>581.7</v>
       </c>
       <c r="G34" s="9">
         <f>H34*(1+Параметры!$C$6)</f>
@@ -5779,10 +6138,21 @@
         <f>H34*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J34" s="31" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="35">
-      <c r="B35" s="6" t="inlineStr"/>
-      <c r="C35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Прокат круглый</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Ø14</t>
+        </is>
+      </c>
       <c r="D35" s="6" t="n">
         <v>0</v>
       </c>
@@ -5792,7 +6162,7 @@
         </is>
       </c>
       <c r="F35" s="29" t="n">
-        <v>2500</v>
+        <v>1352.55</v>
       </c>
       <c r="G35" s="9">
         <f>H35*(1+Параметры!$C$6)</f>
@@ -5806,10 +6176,21 @@
         <f>H35*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J35" s="31" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="36">
-      <c r="B36" s="6" t="inlineStr"/>
-      <c r="C36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Прокат круглый</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Ø16</t>
+        </is>
+      </c>
       <c r="D36" s="6" t="n">
         <v>0</v>
       </c>
@@ -5819,7 +6200,7 @@
         </is>
       </c>
       <c r="F36" s="29" t="n">
-        <v>200</v>
+        <v>901.7</v>
       </c>
       <c r="G36" s="9">
         <f>H36*(1+Параметры!$C$6)</f>
@@ -5833,134 +6214,140 @@
         <f>H36*Параметры!$C$6</f>
         <v/>
       </c>
+      <c r="J36" s="31" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="37">
-      <c r="B37" s="6" t="inlineStr"/>
-      <c r="C37" s="6" t="inlineStr"/>
-      <c r="D37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>Итого прокат</t>
+        </is>
+      </c>
+      <c r="F37" s="32" t="inlineStr">
+        <is>
+          <t>Прокат — себестоимость:</t>
+        </is>
+      </c>
+      <c r="G37" s="13">
+        <f>SUM(G6:G36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="13">
+        <f>SUM(H6:H36)</f>
+        <v/>
+      </c>
+      <c r="I37" s="13">
+        <f>SUM(I6:I36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>ПЛАЗМА / ЛАЗЕР (до 10 позиций)</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Сечение / описание</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Цена поставщика</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость</t>
+        </is>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Наценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="9">
-        <f>H37*(1+Параметры!$C$6)</f>
-        <v/>
-      </c>
-      <c r="H37" s="9">
-        <f>IF(OR(D37="",F37=""),0,D37*F37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="9">
-        <f>H37*Параметры!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="6" t="inlineStr"/>
-      <c r="C38" s="6" t="inlineStr"/>
-      <c r="D38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <f>H42</f>
+        <v/>
+      </c>
+      <c r="H42" s="9">
+        <f>IF(OR(D42="",F42=""),0,D42*F42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="F38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="9">
-        <f>H38*(1+Параметры!$C$6)</f>
-        <v/>
-      </c>
-      <c r="H38" s="9">
-        <f>IF(OR(D38="",F38=""),0,D38*F38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="9">
-        <f>H38*Параметры!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Ковка — себестоимость:</t>
-        </is>
-      </c>
-      <c r="G39" s="13">
-        <f>SUM(G33:G38)</f>
-        <v/>
-      </c>
-      <c r="H39" s="13">
-        <f>SUM(H33:H38)</f>
-        <v/>
-      </c>
-      <c r="I39" s="13">
-        <f>SUM(I33:I38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>ТОКАРНЫЕ РАБОТЫ</t>
-        </is>
-      </c>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Позиция</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>Сечение</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>Цена</t>
-        </is>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
-        <is>
-          <t>Сумма</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>Себестоимость</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>Наценка</t>
-        </is>
+      <c r="F43" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="9">
+        <f>H43</f>
+        <v/>
+      </c>
+      <c r="H43" s="9">
+        <f>IF(OR(D43="",F43=""),0,D43*F43)</f>
+        <v/>
+      </c>
+      <c r="I43" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -6068,54 +6455,847 @@
       </c>
     </row>
     <row r="48">
-      <c r="F48" t="inlineStr">
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F48" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <f>H48</f>
+        <v/>
+      </c>
+      <c r="H48" s="9">
+        <f>IF(OR(D48="",F48=""),0,D48*F48)</f>
+        <v/>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <f>H49</f>
+        <v/>
+      </c>
+      <c r="H49" s="9">
+        <f>IF(OR(D49="",F49=""),0,D49*F49)</f>
+        <v/>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <f>H50</f>
+        <v/>
+      </c>
+      <c r="H50" s="9">
+        <f>IF(OR(D50="",F50=""),0,D50*F50)</f>
+        <v/>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <f>H51</f>
+        <v/>
+      </c>
+      <c r="H51" s="9">
+        <f>IF(OR(D51="",F51=""),0,D51*F51)</f>
+        <v/>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Плазма/лазер — себестоимость:</t>
+        </is>
+      </c>
+      <c r="H52" s="13">
+        <f>SUM(H42:H51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>КОВАНЫЕ ЭЛЕМЕНТЫ / СПЕЦ. ПРОКАТ (до 10 позиций)</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Элемент / артикул</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Сечение</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Цена поставщика</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>С наценкой</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость</t>
+        </is>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Наценка менеджера</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>11.032</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>12х6</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F57" s="29" t="n">
+        <v>50</v>
+      </c>
+      <c r="G57" s="9">
+        <f>H57*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H57" s="9">
+        <f>IF(OR(D57="",F57=""),0,D57*F57)</f>
+        <v/>
+      </c>
+      <c r="I57" s="9">
+        <f>H57*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>41.401</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F58" s="29" t="n">
+        <v>230</v>
+      </c>
+      <c r="G58" s="9">
+        <f>H58*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H58" s="9">
+        <f>IF(OR(D58="",F58=""),0,D58*F58)</f>
+        <v/>
+      </c>
+      <c r="I58" s="9">
+        <f>H58*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <f>H59*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H59" s="9">
+        <f>IF(OR(D59="",F59=""),0,D59*F59)</f>
+        <v/>
+      </c>
+      <c r="I59" s="9">
+        <f>H59*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <f>H60*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H60" s="9">
+        <f>IF(OR(D60="",F60=""),0,D60*F60)</f>
+        <v/>
+      </c>
+      <c r="I60" s="9">
+        <f>H60*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F61" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <f>H61*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H61" s="9">
+        <f>IF(OR(D61="",F61=""),0,D61*F61)</f>
+        <v/>
+      </c>
+      <c r="I61" s="9">
+        <f>H61*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <f>H62*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H62" s="9">
+        <f>IF(OR(D62="",F62=""),0,D62*F62)</f>
+        <v/>
+      </c>
+      <c r="I62" s="9">
+        <f>H62*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F63" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <f>H63*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H63" s="9">
+        <f>IF(OR(D63="",F63=""),0,D63*F63)</f>
+        <v/>
+      </c>
+      <c r="I63" s="9">
+        <f>H63*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F64" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <f>H64*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H64" s="9">
+        <f>IF(OR(D64="",F64=""),0,D64*F64)</f>
+        <v/>
+      </c>
+      <c r="I64" s="9">
+        <f>H64*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F65" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <f>H65*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H65" s="9">
+        <f>IF(OR(D65="",F65=""),0,D65*F65)</f>
+        <v/>
+      </c>
+      <c r="I65" s="9">
+        <f>H65*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <f>H66*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H66" s="9">
+        <f>IF(OR(D66="",F66=""),0,D66*F66)</f>
+        <v/>
+      </c>
+      <c r="I66" s="9">
+        <f>H66*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ковка — себестоимость:</t>
+        </is>
+      </c>
+      <c r="G67" s="13">
+        <f>SUM(G57:G66)</f>
+        <v/>
+      </c>
+      <c r="H67" s="13">
+        <f>SUM(H57:H66)</f>
+        <v/>
+      </c>
+      <c r="I67" s="13">
+        <f>SUM(I57:I66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>ТОКАРНЫЕ РАБОТЫ (до 10 позиций)</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+      <c r="F69" s="11" t="n"/>
+      <c r="G69" s="11" t="n"/>
+      <c r="H69" s="11" t="n"/>
+      <c r="I69" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Сечение / описание</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>Цена</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Наценка</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F72" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="9">
+        <f>H72</f>
+        <v/>
+      </c>
+      <c r="H72" s="9">
+        <f>IF(OR(D72="",F72=""),0,D72*F72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F73" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="9">
+        <f>H73</f>
+        <v/>
+      </c>
+      <c r="H73" s="9">
+        <f>IF(OR(D73="",F73=""),0,D73*F73)</f>
+        <v/>
+      </c>
+      <c r="I73" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="6" t="n"/>
+      <c r="D74" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F74" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <f>H74</f>
+        <v/>
+      </c>
+      <c r="H74" s="9">
+        <f>IF(OR(D74="",F74=""),0,D74*F74)</f>
+        <v/>
+      </c>
+      <c r="I74" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F75" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <f>H75</f>
+        <v/>
+      </c>
+      <c r="H75" s="9">
+        <f>IF(OR(D75="",F75=""),0,D75*F75)</f>
+        <v/>
+      </c>
+      <c r="I75" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <f>H76</f>
+        <v/>
+      </c>
+      <c r="H76" s="9">
+        <f>IF(OR(D76="",F76=""),0,D76*F76)</f>
+        <v/>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <f>H77</f>
+        <v/>
+      </c>
+      <c r="H77" s="9">
+        <f>IF(OR(D77="",F77=""),0,D77*F77)</f>
+        <v/>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F78" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9">
+        <f>H78</f>
+        <v/>
+      </c>
+      <c r="H78" s="9">
+        <f>IF(OR(D78="",F78=""),0,D78*F78)</f>
+        <v/>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F79" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="9">
+        <f>H79</f>
+        <v/>
+      </c>
+      <c r="H79" s="9">
+        <f>IF(OR(D79="",F79=""),0,D79*F79)</f>
+        <v/>
+      </c>
+      <c r="I79" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F80" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="9">
+        <f>H80</f>
+        <v/>
+      </c>
+      <c r="H80" s="9">
+        <f>IF(OR(D80="",F80=""),0,D80*F80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F81" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="9">
+        <f>H81</f>
+        <v/>
+      </c>
+      <c r="H81" s="9">
+        <f>IF(OR(D81="",F81=""),0,D81*F81)</f>
+        <v/>
+      </c>
+      <c r="I81" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Токарка — себестоимость:</t>
         </is>
       </c>
-      <c r="H48" s="13">
-        <f>SUM(H44:H47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="F50" s="31" t="inlineStr">
+      <c r="H82" s="13">
+        <f>SUM(H72:H81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="F84" s="32" t="inlineStr">
         <is>
           <t>ВСЕГО металл — себестоимость:</t>
         </is>
       </c>
-      <c r="H50" s="18">
-        <f>H19+H28+H39+H48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="F51" s="31" t="inlineStr">
-        <is>
-          <t>ВСЕГО наценка менеджера с металла:</t>
-        </is>
-      </c>
-      <c r="H51" s="32">
-        <f>I19+I39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Следующий этап: вынести цены в отдельный справочник поставщика; в заказе оставить кол-во. Связь с Калькуляцией уже через H19 / H28 / H39 / H48.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
+      <c r="H84" s="18">
+        <f>H37+H52+H67+H82</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="F85" s="32" t="inlineStr">
+        <is>
+          <t>ВСЕГО наценка менеджера с металла (прокат+ковка):</t>
+        </is>
+      </c>
+      <c r="H85" s="33">
+        <f>I37+I67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Обновление прайса: меняйте жёлтые цены в колонке F. Кол-во D — под конкретный заказ. Итоги уходят в Калькуляцию автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
   </sheetData>
+  <autoFilter ref="B5:J36"/>
   <mergeCells count="7">
-    <mergeCell ref="B30:I30"/>
-    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B54:I54"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B53:I54"/>
-    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B87:J88"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6128,7 +7308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6176,10 +7356,10 @@
           <t>Наценка менеджера на закупки</t>
         </is>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="34" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr">
         <is>
           <t>От цены поставщика. Ваша прибыль как менеджера.</t>
         </is>
@@ -6191,10 +7371,10 @@
           <t>Целевая маржа проекта (от выручки)</t>
         </is>
       </c>
-      <c r="C7" s="33" t="n">
+      <c r="C7" s="34" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>Чистая маржа после НПД. Диапазон обычно 10%…30%+.</t>
         </is>
@@ -6206,10 +7386,10 @@
           <t>Минимальная допустимая маржа</t>
         </is>
       </c>
-      <c r="C8" s="33" t="n">
+      <c r="C8" s="34" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr">
         <is>
           <t>Ниже — статус «НИЖЕ МИНИМУМА».</t>
         </is>
@@ -6221,10 +7401,10 @@
           <t>Налог НПД (самозанятость)</t>
         </is>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="34" t="n">
         <v>0.04</v>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>4% — физлица, 6% — юрлица/ИП.</t>
         </is>
@@ -6236,10 +7416,10 @@
           <t>Аренда, ₽ / рабочий день</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="36" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>Ставка аренды цеха на рабочий день.</t>
         </is>
@@ -6251,10 +7431,10 @@
           <t>Рабочих дней в месяце</t>
         </is>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>Справочно для пересчёта постоянных расходов.</t>
         </is>
@@ -6266,17 +7446,17 @@
           <t>Агентские, % от цены КП</t>
         </is>
       </c>
-      <c r="C12" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="C12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>Если есть посредник — поставьте %, иначе 0.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>Авто-коэффициенты</t>
         </is>
@@ -6288,11 +7468,11 @@
           <t>Множитель цены при целевой марже</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="37">
         <f>1/(1-C9-C7-C12)</f>
         <v/>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>Цена КП ≈ Себестоимость × коэффициент</t>
         </is>
@@ -6304,14 +7484,14 @@
           <t>Множитель цены при минимальной марже</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="37">
         <f>1/(1-C9-C8-C12)</f>
         <v/>
       </c>
-      <c r="D16" s="34" t="n"/>
+      <c r="D16" s="35" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="32" t="inlineStr">
         <is>
           <t>Тип изделия (список для шапки)</t>
         </is>
@@ -6355,36 +7535,52 @@
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
+          <t>Экстерьер</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Сувенир</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>Прочее</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="31" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="32" t="inlineStr">
         <is>
           <t>Правило маржи</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="96" customHeight="1">
-      <c r="B27" s="37" t="inlineStr">
+    <row r="29" ht="110" customHeight="1">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>Себестоимость C = реальные выплаты (материалы по цене поставщика, труд, транспорт, аренда, расходники, субподряд).
 Наценка менеджера = % только на тип «закупка» — это часть вашей прибыли, не расход.
 Цена для целевой маржи P = C / (1 − НПД% − целевая маржа% − агентские%).
 Прибыль = P − C − P×НПД − P×агентские.  Маржа % = Прибыль / P.
-Не добавляйте «+15% на закупки» и «+20% маржа» как две наценки на одну базу: 15% уже внутри итоговой прибыли.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
+Не добавляйте «+15% на закупки» и «+20% маржа» как две наценки на одну базу: 15% уже внутри итоговой прибыли.
+КАССА ЗАКАЗА — отдельный опциональный учёт денег после сделки. На рентабельность и цену КП НЕ влияет.</t>
+        </is>
+      </c>
+    </row>
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B27:F32"/>
+    <mergeCell ref="B29:F35"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:F3"/>
   </mergeCells>
@@ -6398,74 +7594,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D47"/>
+  <dimension ref="B2:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>КАССА ЗАКАЗА (не путать с прибылью)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Только деньги: сколько получили и сколько выплатили. Прибыль — на листе Сводка.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>ПРИХОДЫ ОТ КЛИЕНТА</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="n"/>
-      <c r="D5" s="4" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="10" t="inlineStr">
+          <t>КАССА ЗАКАЗА — опционально (после сделки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="B3" s="39" t="inlineStr">
+        <is>
+          <t>ЭТОТ ЛИСТ НЕ УЧАСТВУЕТ В РАСЧЁТЕ ЦЕНЫ И МАРЖИ.
+Нужен только чтобы помнить: сколько клиент уже заплатил и сколько вы уже потратили по заказу.
+Если считаете только КП — этот лист можно полностью игнорировать.
+Связь со Сводкой: одна — подтягивает «Цену КП» (сколько договорились), чтобы показать остаток к получению.
+Обратно в Сводку / Калькуляцию / Металл касса НИЧЕГО не отправляет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1"/>
+    <row r="5" ht="18" customHeight="1"/>
+    <row r="6" ht="18" customHeight="1"/>
+    <row r="7" ht="18" customHeight="1"/>
+    <row r="9">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>1) СКОЛЬКО ПОЛУЧИЛИ ОТ КЛИЕНТА</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Что за платёж</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="29" t="n"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="29" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="29" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="29" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="6" t="n"/>
@@ -6473,83 +7658,83 @@
       <c r="D11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Итого получено:</t>
-        </is>
-      </c>
-      <c r="D12" s="13">
-        <f>SUM(D7:D11)</f>
-        <v/>
-      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="29" t="n"/>
     </row>
     <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Цена КП (из Сводки):</t>
-        </is>
-      </c>
-      <c r="D13" s="9">
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="29" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="29" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="29" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Всего получено:</t>
+        </is>
+      </c>
+      <c r="D16" s="13">
+        <f>SUM(D11:D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Цена КП (из Сводки, только для справки):</t>
+        </is>
+      </c>
+      <c r="D17" s="9">
         <f>Сводка!D24</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Остаток к получению:</t>
-        </is>
-      </c>
-      <c r="D14" s="38">
-        <f>D13-D12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>РАСХОДЫ ПО ЗАКАЗУ (факт выплат)</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ещё должен клиент:</t>
+        </is>
+      </c>
+      <c r="D18" s="40">
+        <f>D17-D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>2) СКОЛЬКО УЖЕ ВЫПЛАТИЛИ ПО ЗАКАЗУ</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>Основание</t>
-        </is>
-      </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Кому / за что</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="29" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="29" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="29" t="n"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="29" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="6" t="n"/>
@@ -6651,45 +7836,43 @@
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="29" t="n"/>
     </row>
-    <row r="42">
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="29" t="n"/>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Всего выплат:</t>
+        </is>
+      </c>
+      <c r="D43" s="13">
+        <f>SUM(D22:D41)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>Итого выплат:</t>
-        </is>
-      </c>
-      <c r="D44" s="13">
-        <f>SUM(D18:D42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Касса заказа (получено − выплачено):</t>
-        </is>
-      </c>
-      <c r="D45" s="18">
-        <f>D12-D44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Это не прибыль. Прибыль = цена КП − себестоимость − НПД − агентские (Сводка).</t>
-        </is>
-      </c>
-    </row>
+          <t>Живые деньги по заказу сейчас (получено − выплаты):</t>
+        </is>
+      </c>
+      <c r="D44" s="18">
+        <f>D16-D43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Пример: КП 100 000, аванс 50 000, купили металл 20 000 → получено 50 000, выплат 20 000, в кассе заказа 30 000. Прибыль при этом смотрите на Сводке, не здесь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B2:D2"/>
+  <mergeCells count="5">
+    <mergeCell ref="B46:E47"/>
+    <mergeCell ref="B3:E7"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6701,7 +7884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B13"/>
+  <dimension ref="B2:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6716,64 +7899,92 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="39" t="inlineStr">
-        <is>
-          <t>1. «Параметры» — наценка менеджера 15%, целевая маржа 20%, мин. маржа 10%, НПД 4% или 6%, аренда 2000 ₽/день.</t>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>ГЛАВНЫЙ КОНТУР (для цены КП):</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="39" t="inlineStr">
-        <is>
-          <t>2. «Металл» — кол-во и цены поставщика. Наценка менеджера считается как себестоимость × %.</t>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>1. «Параметры» — % менеджера, целевая/мин. маржа, НПД, аренда/день.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="39" t="inlineStr">
-        <is>
-          <t>3. «Калькуляция» — количества по этапам. Тип «закупка» → наценка менеджера. Аренда из Параметров.</t>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>2. «Металл» — в каталоге проката поставьте кол-во штанг (шт = 6 м). Цены уже загружены; при смене прайса правьте колонку F.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="39" t="inlineStr">
-        <is>
-          <t>4. «Сводка» — себестоимость и рекомендуемая цена. Введите цену КП в D24. Смотрите статус.</t>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>3. «Калькуляция» — количества по этапам (дни, рейсы, материалы).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="39" t="inlineStr">
-        <is>
-          <t>5. Таблица гибкой маржи 10%…35% — чтобы торговаться и не уходить ниже минимума.</t>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>4. «Сводка» — смотрите рекомендуемую цену, впишите цену КП в жёлтую ячейку, проверьте статус.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="39" t="inlineStr">
-        <is>
-          <t>6. «Касса заказа» — авансы и факт выплат. Не смешивать с маржой.</t>
-        </is>
-      </c>
+      <c r="B9" s="41" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="39" t="inlineStr"/>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>КАССА — НЕ ДЛЯ РАСЧЁТА ЦЕНЫ:</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" s="39" t="inlineStr">
-        <is>
-          <t>Уточнение про «нормы»: шаблоны расхода (например, на 1 м забора — X кг профиля и Y часов). Если их нет — каждый заказ считаем с нуля. Позже можно сделать заготовки под Ворота/Забор/Лестница.</t>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>• Нужна после сделки: авансы клиента и факт выплат (металл, ЗП, транспорт).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="39" t="inlineStr"/>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>• Из Сводки берёт только «Цену КП», чтобы показать остаток к получению.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>Следующий этап по вашему запросу: справочник металла с ценами поставщика и связью с заказом.</t>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>• В Сводку / маржу / калькуляцию ничего не возвращает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>• Пока готовите КП — лист Касса можно не открывать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="41" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Типы изделий: Ворота, Забор, Лестница, Мебель, Интерьер, Экстерьер, Сувенир, Прочее.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>В шапке Сводки: Клиент + № клиента.</t>
         </is>
       </c>
     </row>

--- a/templates/Калькуляция_проект_v1.xlsx
+++ b/templates/Калькуляция_проект_v1.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Инструкция" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Калькуляция'!$B$15:$L$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Калькуляция'!$B$15:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Металл'!$B$5:$J$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O116"/>
+  <dimension ref="B2:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E37" s="28">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>услуга</t>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E39" s="28">
@@ -2384,66 +2384,62 @@
       <c r="L39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>Металл</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Доп. комплектующие (лист Металл)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>закупка</t>
+        </is>
+      </c>
+      <c r="E40" s="28">
+        <f>Металл!H97</f>
+        <v/>
+      </c>
+      <c r="F40" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>сводка</t>
+        </is>
+      </c>
+      <c r="H40" s="28">
+        <f>IF(OR(E40="",F40=""),0,E40*F40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="28">
+        <f>IF(D40="закупка",H40*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J40" s="28">
+        <f>H40+I40</f>
+        <v/>
+      </c>
+      <c r="L40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>4. Производство</t>
         </is>
       </c>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
-      <c r="I40" s="26" t="n"/>
-      <c r="J40" s="26" t="n"/>
-      <c r="L40" s="26" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>Производство</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Аренда цеха</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>аренда</t>
-        </is>
-      </c>
-      <c r="E41" s="28">
-        <f>Параметры!$C$10</f>
-        <v/>
-      </c>
-      <c r="F41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>день</t>
-        </is>
-      </c>
-      <c r="H41" s="28">
-        <f>IF(OR(E41="",F41=""),0,E41*F41)</f>
-        <v/>
-      </c>
-      <c r="I41" s="28">
-        <f>IF(D41="закупка",H41*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J41" s="28">
-        <f>H41+I41</f>
-        <v/>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>Ставка аренды из Параметры</t>
-        </is>
-      </c>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
+      <c r="H41" s="26" t="n"/>
+      <c r="I41" s="26" t="n"/>
+      <c r="J41" s="26" t="n"/>
+      <c r="L41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="27" t="inlineStr">
@@ -2453,16 +2449,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Оплата труда: мастер</t>
+          <t>Аренда цеха</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>труд</t>
-        </is>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>6000</v>
+          <t>аренда</t>
+        </is>
+      </c>
+      <c r="E42" s="28">
+        <f>Параметры!$C$10</f>
+        <v/>
       </c>
       <c r="F42" s="6" t="n">
         <v>0</v>
@@ -2486,7 +2483,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>ФИО в примечании</t>
+          <t>Ставка аренды из Параметры</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2495,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Оплата труда: рабочий</t>
+          <t>Оплата труда: мастер</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -2507,7 +2504,7 @@
         </is>
       </c>
       <c r="E43" s="29" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>0</v>
@@ -2529,7 +2526,11 @@
         <f>H43+I43</f>
         <v/>
       </c>
-      <c r="L43" s="6" t="inlineStr"/>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>ФИО в примечании</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="27" t="inlineStr">
@@ -2539,7 +2540,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>Оплата труда: доп.1</t>
+          <t>Оплата труда: рабочий</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2548,7 +2549,7 @@
         </is>
       </c>
       <c r="E44" s="29" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>0</v>
@@ -2580,7 +2581,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Оплата труда: доп.2</t>
+          <t>Оплата труда: доп.1</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -2589,7 +2590,7 @@
         </is>
       </c>
       <c r="E45" s="29" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0</v>
@@ -2614,66 +2615,61 @@
       <c r="L45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="B46" s="26" t="inlineStr">
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>Производство</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Оплата труда: доп.2</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>труд</t>
+        </is>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>день</t>
+        </is>
+      </c>
+      <c r="H46" s="28">
+        <f>IF(OR(E46="",F46=""),0,E46*F46)</f>
+        <v/>
+      </c>
+      <c r="I46" s="28">
+        <f>IF(D46="закупка",H46*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J46" s="28">
+        <f>H46+I46</f>
+        <v/>
+      </c>
+      <c r="L46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>5. Предмонтаж</t>
         </is>
       </c>
-      <c r="C46" s="26" t="n"/>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="n"/>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="n"/>
-      <c r="I46" s="26" t="n"/>
-      <c r="J46" s="26" t="n"/>
-      <c r="L46" s="26" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>Предмонтаж</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>аренда</t>
-        </is>
-      </c>
-      <c r="E47" s="28">
-        <f>Параметры!$C$10</f>
-        <v/>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>день</t>
-        </is>
-      </c>
-      <c r="H47" s="28">
-        <f>IF(OR(E47="",F47=""),0,E47*F47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="28">
-        <f>IF(D47="закупка",H47*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J47" s="28">
-        <f>H47+I47</f>
-        <v/>
-      </c>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>Ставка аренды из Параметры</t>
-        </is>
-      </c>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="26" t="n"/>
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="26" t="n"/>
+      <c r="G47" s="26" t="n"/>
+      <c r="H47" s="26" t="n"/>
+      <c r="I47" s="26" t="n"/>
+      <c r="J47" s="26" t="n"/>
+      <c r="L47" s="26" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="27" t="inlineStr">
@@ -2683,16 +2679,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>Монтажники</t>
+          <t>Аренда</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>труд</t>
-        </is>
-      </c>
-      <c r="E48" s="29" t="n">
-        <v>7300</v>
+          <t>аренда</t>
+        </is>
+      </c>
+      <c r="E48" s="28">
+        <f>Параметры!$C$10</f>
+        <v/>
       </c>
       <c r="F48" s="6" t="n">
         <v>0</v>
@@ -2714,7 +2711,11 @@
         <f>H48+I48</f>
         <v/>
       </c>
-      <c r="L48" s="6" t="inlineStr"/>
+      <c r="L48" s="6" t="inlineStr">
+        <is>
+          <t>Ставка аренды из Параметры</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="27" t="inlineStr">
@@ -2724,7 +2725,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Помощник</t>
+          <t>Монтажники</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -2733,7 +2734,7 @@
         </is>
       </c>
       <c r="E49" s="29" t="n">
-        <v>5000</v>
+        <v>7300</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>0</v>
@@ -2765,23 +2766,23 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>Транспорт цех → объект</t>
+          <t>Помощник</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>труд</t>
         </is>
       </c>
       <c r="E50" s="29" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>день</t>
         </is>
       </c>
       <c r="H50" s="28">
@@ -2806,7 +2807,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Транспорт объект → цех</t>
+          <t>Транспорт цех → объект</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2847,7 +2848,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Такси</t>
+          <t>Транспорт объект → цех</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2856,14 +2857,14 @@
         </is>
       </c>
       <c r="E52" s="29" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>поездка</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="H52" s="28">
@@ -2881,66 +2882,61 @@
       <c r="L52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="B53" s="26" t="inlineStr">
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>Предмонтаж</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Такси</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>транспорт</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>поездка</t>
+        </is>
+      </c>
+      <c r="H53" s="28">
+        <f>IF(OR(E53="",F53=""),0,E53*F53)</f>
+        <v/>
+      </c>
+      <c r="I53" s="28">
+        <f>IF(D53="закупка",H53*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="28">
+        <f>H53+I53</f>
+        <v/>
+      </c>
+      <c r="L53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>6. Покраска эмалью</t>
         </is>
       </c>
-      <c r="C53" s="26" t="n"/>
-      <c r="D53" s="26" t="n"/>
-      <c r="E53" s="26" t="n"/>
-      <c r="F53" s="26" t="n"/>
-      <c r="G53" s="26" t="n"/>
-      <c r="H53" s="26" t="n"/>
-      <c r="I53" s="26" t="n"/>
-      <c r="J53" s="26" t="n"/>
-      <c r="L53" s="26" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="27" t="inlineStr">
-        <is>
-          <t>Покраска эмаль</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>аренда</t>
-        </is>
-      </c>
-      <c r="E54" s="28">
-        <f>Параметры!$C$10</f>
-        <v/>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>день</t>
-        </is>
-      </c>
-      <c r="H54" s="28">
-        <f>IF(OR(E54="",F54=""),0,E54*F54)</f>
-        <v/>
-      </c>
-      <c r="I54" s="28">
-        <f>IF(D54="закупка",H54*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J54" s="28">
-        <f>H54+I54</f>
-        <v/>
-      </c>
-      <c r="L54" s="6" t="inlineStr">
-        <is>
-          <t>Ставка аренды из Параметры</t>
-        </is>
-      </c>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="26" t="n"/>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="26" t="n"/>
+      <c r="G54" s="26" t="n"/>
+      <c r="H54" s="26" t="n"/>
+      <c r="I54" s="26" t="n"/>
+      <c r="J54" s="26" t="n"/>
+      <c r="L54" s="26" t="n"/>
     </row>
     <row r="55">
       <c r="B55" s="27" t="inlineStr">
@@ -2950,16 +2946,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>Маляр</t>
+          <t>Аренда</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>труд</t>
-        </is>
-      </c>
-      <c r="E55" s="29" t="n">
-        <v>3000</v>
+          <t>аренда</t>
+        </is>
+      </c>
+      <c r="E55" s="28">
+        <f>Параметры!$C$10</f>
+        <v/>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
@@ -2981,7 +2978,11 @@
         <f>H55+I55</f>
         <v/>
       </c>
-      <c r="L55" s="6" t="inlineStr"/>
+      <c r="L55" s="6" t="inlineStr">
+        <is>
+          <t>Ставка аренды из Параметры</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="27" t="inlineStr">
@@ -2991,7 +2992,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>Рабочий</t>
+          <t>Маляр</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -3000,7 +3001,7 @@
         </is>
       </c>
       <c r="E56" s="29" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>0</v>
@@ -3032,23 +3033,23 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>Респиратор</t>
+          <t>Рабочий</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>закупка</t>
+          <t>труд</t>
         </is>
       </c>
       <c r="E57" s="29" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>день</t>
         </is>
       </c>
       <c r="H57" s="28">
@@ -3073,7 +3074,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>Грунт</t>
+          <t>Респиратор</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -3082,7 +3083,7 @@
         </is>
       </c>
       <c r="E58" s="29" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>0</v>
@@ -3114,7 +3115,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Лак</t>
+          <t>Грунт</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -3123,7 +3124,7 @@
         </is>
       </c>
       <c r="E59" s="29" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>0</v>
@@ -3155,7 +3156,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>Эмаль 0,8л</t>
+          <t>Лак</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -3164,7 +3165,7 @@
         </is>
       </c>
       <c r="E60" s="29" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>0</v>
@@ -3196,7 +3197,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>Эмаль 2,0л</t>
+          <t>Эмаль 0,8л</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -3205,7 +3206,7 @@
         </is>
       </c>
       <c r="E61" s="29" t="n">
-        <v>3500</v>
+        <v>1200</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>0</v>
@@ -3237,7 +3238,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>Мет.щётки, кисти</t>
+          <t>Эмаль 2,0л</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -3246,14 +3247,14 @@
         </is>
       </c>
       <c r="E62" s="29" t="n">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>набор</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="H62" s="28">
@@ -3278,7 +3279,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>Растворитель</t>
+          <t>Мет.щётки, кисти</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -3287,14 +3288,14 @@
         </is>
       </c>
       <c r="E63" s="29" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="6" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>набор</t>
         </is>
       </c>
       <c r="H63" s="28">
@@ -3319,7 +3320,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>Холодный цинк</t>
+          <t>Растворитель</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -3328,7 +3329,7 @@
         </is>
       </c>
       <c r="E64" s="29" t="n">
-        <v>2500</v>
+        <v>370</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>0</v>
@@ -3360,23 +3361,23 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Транспорт микроавтобус</t>
+          <t>Холодный цинк</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E65" s="29" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="6" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="H65" s="28">
@@ -3401,7 +3402,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Транспорт бортовая 4м</t>
+          <t>Транспорт микроавтобус</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -3410,7 +3411,7 @@
         </is>
       </c>
       <c r="E66" s="29" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>0</v>
@@ -3442,7 +3443,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Транспорт бортовая 6м</t>
+          <t>Транспорт бортовая 4м</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -3451,7 +3452,7 @@
         </is>
       </c>
       <c r="E67" s="29" t="n">
-        <v>3500</v>
+        <v>1500</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>0</v>
@@ -3476,61 +3477,61 @@
       <c r="L67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="B68" s="26" t="inlineStr">
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>Покраска эмаль</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Транспорт бортовая 6м</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>транспорт</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="H68" s="28">
+        <f>IF(OR(E68="",F68=""),0,E68*F68)</f>
+        <v/>
+      </c>
+      <c r="I68" s="28">
+        <f>IF(D68="закупка",H68*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J68" s="28">
+        <f>H68+I68</f>
+        <v/>
+      </c>
+      <c r="L68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="26" t="inlineStr">
         <is>
           <t>7. Пескоструй</t>
         </is>
       </c>
-      <c r="C68" s="26" t="n"/>
-      <c r="D68" s="26" t="n"/>
-      <c r="E68" s="26" t="n"/>
-      <c r="F68" s="26" t="n"/>
-      <c r="G68" s="26" t="n"/>
-      <c r="H68" s="26" t="n"/>
-      <c r="I68" s="26" t="n"/>
-      <c r="J68" s="26" t="n"/>
-      <c r="L68" s="26" t="n"/>
-    </row>
-    <row r="69">
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>Пескоструй</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Услуга пескоструй</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>услуга</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="n">
-        <v>900</v>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="H69" s="28">
-        <f>IF(OR(E69="",F69=""),0,E69*F69)</f>
-        <v/>
-      </c>
-      <c r="I69" s="28">
-        <f>IF(D69="закупка",H69*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J69" s="28">
-        <f>H69+I69</f>
-        <v/>
-      </c>
-      <c r="L69" s="6" t="inlineStr"/>
+      <c r="C69" s="26" t="n"/>
+      <c r="D69" s="26" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n"/>
+      <c r="G69" s="26" t="n"/>
+      <c r="H69" s="26" t="n"/>
+      <c r="I69" s="26" t="n"/>
+      <c r="J69" s="26" t="n"/>
+      <c r="L69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="B70" s="27" t="inlineStr">
@@ -3540,23 +3541,23 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>Транспорт на пескоструй</t>
+          <t>Услуга пескоструй</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="E70" s="29" t="n">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>м</t>
         </is>
       </c>
       <c r="H70" s="28">
@@ -3581,7 +3582,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>Транспорт с пескоструя</t>
+          <t>Транспорт на пескоструй</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -3615,61 +3616,61 @@
       <c r="L71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="B72" s="26" t="inlineStr">
+      <c r="B72" s="27" t="inlineStr">
+        <is>
+          <t>Пескоструй</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Транспорт с пескоструя</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>транспорт</t>
+        </is>
+      </c>
+      <c r="E72" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="H72" s="28">
+        <f>IF(OR(E72="",F72=""),0,E72*F72)</f>
+        <v/>
+      </c>
+      <c r="I72" s="28">
+        <f>IF(D72="закупка",H72*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J72" s="28">
+        <f>H72+I72</f>
+        <v/>
+      </c>
+      <c r="L72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="26" t="inlineStr">
         <is>
           <t>8. Порошковая покраска</t>
         </is>
       </c>
-      <c r="C72" s="26" t="n"/>
-      <c r="D72" s="26" t="n"/>
-      <c r="E72" s="26" t="n"/>
-      <c r="F72" s="26" t="n"/>
-      <c r="G72" s="26" t="n"/>
-      <c r="H72" s="26" t="n"/>
-      <c r="I72" s="26" t="n"/>
-      <c r="J72" s="26" t="n"/>
-      <c r="L72" s="26" t="n"/>
-    </row>
-    <row r="73">
-      <c r="B73" s="27" t="inlineStr">
-        <is>
-          <t>Порошок</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>Покраска обычная</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>услуга</t>
-        </is>
-      </c>
-      <c r="E73" s="29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>услуга</t>
-        </is>
-      </c>
-      <c r="H73" s="28">
-        <f>IF(OR(E73="",F73=""),0,E73*F73)</f>
-        <v/>
-      </c>
-      <c r="I73" s="28">
-        <f>IF(D73="закупка",H73*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J73" s="28">
-        <f>H73+I73</f>
-        <v/>
-      </c>
-      <c r="L73" s="6" t="inlineStr"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
+      <c r="H73" s="26" t="n"/>
+      <c r="I73" s="26" t="n"/>
+      <c r="J73" s="26" t="n"/>
+      <c r="L73" s="26" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="27" t="inlineStr">
@@ -3679,7 +3680,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>Покраска с цинком</t>
+          <t>Покраска обычная</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -3688,7 +3689,7 @@
         </is>
       </c>
       <c r="E74" s="29" t="n">
-        <v>2400</v>
+        <v>2000</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>0</v>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>Покраска шагрень</t>
+          <t>Покраска с цинком</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -3729,7 +3730,7 @@
         </is>
       </c>
       <c r="E75" s="29" t="n">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>0</v>
@@ -3761,7 +3762,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>Покраска антик (молотковая)</t>
+          <t>Покраска шагрень</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -3770,7 +3771,7 @@
         </is>
       </c>
       <c r="E76" s="29" t="n">
-        <v>2200</v>
+        <v>2300</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>0</v>
@@ -3802,23 +3803,23 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Транспорт на покраску</t>
+          <t>Покраска антик (молотковая)</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="E77" s="29" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G77" s="6" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>услуга</t>
         </is>
       </c>
       <c r="H77" s="28">
@@ -3843,7 +3844,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>Транспорт с покраски</t>
+          <t>Транспорт на покраску</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -3884,7 +3885,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>Транспорт людей</t>
+          <t>Транспорт с покраски</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -3893,14 +3894,14 @@
         </is>
       </c>
       <c r="E79" s="29" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G79" s="6" t="inlineStr">
         <is>
-          <t>поездка</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="H79" s="28">
@@ -3918,66 +3919,61 @@
       <c r="L79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="B80" s="26" t="inlineStr">
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>Порошок</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Транспорт людей</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>транспорт</t>
+        </is>
+      </c>
+      <c r="E80" s="29" t="n">
+        <v>500</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>поездка</t>
+        </is>
+      </c>
+      <c r="H80" s="28">
+        <f>IF(OR(E80="",F80=""),0,E80*F80)</f>
+        <v/>
+      </c>
+      <c r="I80" s="28">
+        <f>IF(D80="закупка",H80*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J80" s="28">
+        <f>H80+I80</f>
+        <v/>
+      </c>
+      <c r="L80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="26" t="inlineStr">
         <is>
           <t>9. Монтаж</t>
         </is>
       </c>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
-      <c r="G80" s="26" t="n"/>
-      <c r="H80" s="26" t="n"/>
-      <c r="I80" s="26" t="n"/>
-      <c r="J80" s="26" t="n"/>
-      <c r="L80" s="26" t="n"/>
-    </row>
-    <row r="81">
-      <c r="B81" s="27" t="inlineStr">
-        <is>
-          <t>Монтаж</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Аренда</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>аренда</t>
-        </is>
-      </c>
-      <c r="E81" s="28">
-        <f>Параметры!$C$10</f>
-        <v/>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>день</t>
-        </is>
-      </c>
-      <c r="H81" s="28">
-        <f>IF(OR(E81="",F81=""),0,E81*F81)</f>
-        <v/>
-      </c>
-      <c r="I81" s="28">
-        <f>IF(D81="закупка",H81*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J81" s="28">
-        <f>H81+I81</f>
-        <v/>
-      </c>
-      <c r="L81" s="6" t="inlineStr">
-        <is>
-          <t>Ставка аренды из Параметры</t>
-        </is>
-      </c>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="26" t="n"/>
+      <c r="J81" s="26" t="n"/>
+      <c r="L81" s="26" t="n"/>
     </row>
     <row r="82">
       <c r="B82" s="27" t="inlineStr">
@@ -3987,16 +3983,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>Монтажники</t>
+          <t>Аренда</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>труд</t>
-        </is>
-      </c>
-      <c r="E82" s="29" t="n">
-        <v>5000</v>
+          <t>аренда</t>
+        </is>
+      </c>
+      <c r="E82" s="28">
+        <f>Параметры!$C$10</f>
+        <v/>
       </c>
       <c r="F82" s="6" t="n">
         <v>0</v>
@@ -4018,7 +4015,11 @@
         <f>H82+I82</f>
         <v/>
       </c>
-      <c r="L82" s="6" t="inlineStr"/>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>Ставка аренды из Параметры</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="B83" s="27" t="inlineStr">
@@ -4028,7 +4029,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Помощник</t>
+          <t>Монтажники</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -4037,7 +4038,7 @@
         </is>
       </c>
       <c r="E83" s="29" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>0</v>
@@ -4069,23 +4070,23 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>Крепежи, хим.анкер</t>
+          <t>Помощник</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>закупка</t>
+          <t>труд</t>
         </is>
       </c>
       <c r="E84" s="29" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
-          <t>набор</t>
+          <t>день</t>
         </is>
       </c>
       <c r="H84" s="28">
@@ -4110,23 +4111,23 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>Транспорт рабочих</t>
+          <t>Крепежи, хим.анкер</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>транспорт</t>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E85" s="29" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>поездка</t>
+          <t>набор</t>
         </is>
       </c>
       <c r="H85" s="28">
@@ -4151,7 +4152,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>Транспорт оборудования на объект</t>
+          <t>Транспорт рабочих</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -4160,14 +4161,14 @@
         </is>
       </c>
       <c r="E86" s="29" t="n">
-        <v>2000</v>
+        <v>500</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>поездка</t>
         </is>
       </c>
       <c r="H86" s="28">
@@ -4192,7 +4193,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>Транспорт оборудования в цех</t>
+          <t>Транспорт оборудования на объект</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -4226,61 +4227,61 @@
       <c r="L87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="B88" s="26" t="inlineStr">
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>Монтаж</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Транспорт оборудования в цех</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>транспорт</t>
+        </is>
+      </c>
+      <c r="E88" s="29" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="H88" s="28">
+        <f>IF(OR(E88="",F88=""),0,E88*F88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="28">
+        <f>IF(D88="закупка",H88*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J88" s="28">
+        <f>H88+I88</f>
+        <v/>
+      </c>
+      <c r="L88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="26" t="inlineStr">
         <is>
           <t>10. Расходники в день</t>
         </is>
       </c>
-      <c r="C88" s="26" t="n"/>
-      <c r="D88" s="26" t="n"/>
-      <c r="E88" s="26" t="n"/>
-      <c r="F88" s="26" t="n"/>
-      <c r="G88" s="26" t="n"/>
-      <c r="H88" s="26" t="n"/>
-      <c r="I88" s="26" t="n"/>
-      <c r="J88" s="26" t="n"/>
-      <c r="L88" s="26" t="n"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="27" t="inlineStr">
-        <is>
-          <t>Расходники/день</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>Абразивы</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>закупка</t>
-        </is>
-      </c>
-      <c r="E89" s="29" t="n">
-        <v>600</v>
-      </c>
-      <c r="F89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>день</t>
-        </is>
-      </c>
-      <c r="H89" s="28">
-        <f>IF(OR(E89="",F89=""),0,E89*F89)</f>
-        <v/>
-      </c>
-      <c r="I89" s="28">
-        <f>IF(D89="закупка",H89*Параметры!$C$6,0)</f>
-        <v/>
-      </c>
-      <c r="J89" s="28">
-        <f>H89+I89</f>
-        <v/>
-      </c>
-      <c r="L89" s="6" t="inlineStr"/>
+      <c r="C89" s="26" t="n"/>
+      <c r="D89" s="26" t="n"/>
+      <c r="E89" s="26" t="n"/>
+      <c r="F89" s="26" t="n"/>
+      <c r="G89" s="26" t="n"/>
+      <c r="H89" s="26" t="n"/>
+      <c r="I89" s="26" t="n"/>
+      <c r="J89" s="26" t="n"/>
+      <c r="L89" s="26" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="27" t="inlineStr">
@@ -4290,7 +4291,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>Кислород</t>
+          <t>Абразивы</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -4299,7 +4300,7 @@
         </is>
       </c>
       <c r="E90" s="29" t="n">
-        <v>330</v>
+        <v>600</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>0</v>
@@ -4321,11 +4322,7 @@
         <f>H90+I90</f>
         <v/>
       </c>
-      <c r="L90" s="6" t="inlineStr">
-        <is>
-          <t>ориентир: баллон / срок</t>
-        </is>
-      </c>
+      <c r="L90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="B91" s="27" t="inlineStr">
@@ -4335,7 +4332,7 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>Углекислота</t>
+          <t>Кислород</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -4344,7 +4341,7 @@
         </is>
       </c>
       <c r="E91" s="29" t="n">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>0</v>
@@ -4366,7 +4363,11 @@
         <f>H91+I91</f>
         <v/>
       </c>
-      <c r="L91" s="6" t="inlineStr"/>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>ориентир: баллон / срок</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="B92" s="27" t="inlineStr">
@@ -4376,7 +4377,7 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>Пропан (газ)</t>
+          <t>Углекислота</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -4385,7 +4386,7 @@
         </is>
       </c>
       <c r="E92" s="29" t="n">
-        <v>690</v>
+        <v>65</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>0</v>
@@ -4417,7 +4418,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>Ковка (уголь)</t>
+          <t>Пропан (газ)</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -4426,7 +4427,7 @@
         </is>
       </c>
       <c r="E93" s="29" t="n">
-        <v>3100</v>
+        <v>690</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>0</v>
@@ -4458,16 +4459,16 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>Амортизация инструмента</t>
+          <t>Ковка (уголь)</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>прочее</t>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E94" s="29" t="n">
-        <v>740</v>
+        <v>3100</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>0</v>
@@ -4492,12 +4493,32 @@
       <c r="L94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="B95" s="27" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="29" t="n"/>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="n"/>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Расходники/день</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Амортизация инструмента</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>прочее</t>
+        </is>
+      </c>
+      <c r="E95" s="29" t="n">
+        <v>740</v>
+      </c>
+      <c r="F95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>день</t>
+        </is>
+      </c>
       <c r="H95" s="28">
         <f>IF(OR(E95="",F95=""),0,E95*F95)</f>
         <v/>
@@ -4510,7 +4531,7 @@
         <f>H95+I95</f>
         <v/>
       </c>
-      <c r="L95" s="6" t="n"/>
+      <c r="L95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="B96" s="27" t="n"/>
@@ -4911,32 +4932,53 @@
       </c>
       <c r="L114" s="6" t="n"/>
     </row>
-    <row r="116">
-      <c r="B116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="27" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="29" t="n"/>
+      <c r="F115" s="6" t="n"/>
+      <c r="G115" s="6" t="n"/>
+      <c r="H115" s="28">
+        <f>IF(OR(E115="",F115=""),0,E115*F115)</f>
+        <v/>
+      </c>
+      <c r="I115" s="28">
+        <f>IF(D115="закупка",H115*Параметры!$C$6,0)</f>
+        <v/>
+      </c>
+      <c r="J115" s="28">
+        <f>H115+I115</f>
+        <v/>
+      </c>
+      <c r="L115" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Пустые строки — для своих позиций. Тип «закупка» включает наценку менеджера автоматически.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B15:L114"/>
+  <autoFilter ref="B15:L115"/>
   <mergeCells count="13">
-    <mergeCell ref="B53:L53"/>
-    <mergeCell ref="B88:L88"/>
-    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B73:L73"/>
     <mergeCell ref="B16:L16"/>
-    <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="B69:L69"/>
     <mergeCell ref="B3:L3"/>
     <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="B89:L89"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B23:L23"/>
-    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B41:L41"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D17 D18 D19 D20 D21 D22 D24 D25 D26 D27 D28 D29 D30 D31 D33 D34 D35 D36 D37 D38 D39 D41 D42 D43 D44 D45 D47 D48 D49 D50 D51 D52 D54 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D69 D70 D71 D73 D74 D75 D76 D77 D78 D79 D81 D82 D83 D84 D85 D86 D87 D89 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D17 D18 D19 D20 D21 D22 D24 D25 D26 D27 D28 D29 D30 D31 D33 D34 D35 D36 D37 D38 D39 D40 D42 D43 D44 D45 D46 D48 D49 D50 D51 D52 D53 D55 D56 D57 D58 D59 D60 D61 D62 D63 D64 D65 D66 D67 D68 D70 D71 D72 D74 D75 D76 D77 D78 D79 D80 D82 D83 D84 D85 D86 D87 D88 D90 D91 D92 D93 D94 D95 D96 D97 D98 D99 D100 D101 D102 D103 D104 D105 D106 D107 D108 D109 D110 D111 D112 D113 D114 D115" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"закупка,труд,транспорт,аренда,услуга,прочее"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4950,7 +4992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J88"/>
+  <dimension ref="B2:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -6284,7 +6326,7 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Сумма</t>
+          <t>С наценкой менеджера</t>
         </is>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -6294,7 +6336,7 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
@@ -6313,15 +6355,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="9">
-        <f>H42</f>
+        <f>H42*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H42" s="9">
         <f>IF(OR(D42="",F42=""),0,D42*F42)</f>
         <v/>
       </c>
-      <c r="I42" s="9" t="n">
-        <v>0</v>
+      <c r="I42" s="9">
+        <f>H42*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -6339,15 +6382,16 @@
         <v>0</v>
       </c>
       <c r="G43" s="9">
-        <f>H43</f>
+        <f>H43*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H43" s="9">
         <f>IF(OR(D43="",F43=""),0,D43*F43)</f>
         <v/>
       </c>
-      <c r="I43" s="9" t="n">
-        <v>0</v>
+      <c r="I43" s="9">
+        <f>H43*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -6365,15 +6409,16 @@
         <v>0</v>
       </c>
       <c r="G44" s="9">
-        <f>H44</f>
+        <f>H44*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H44" s="9">
         <f>IF(OR(D44="",F44=""),0,D44*F44)</f>
         <v/>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
+      <c r="I44" s="9">
+        <f>H44*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -6391,15 +6436,16 @@
         <v>0</v>
       </c>
       <c r="G45" s="9">
-        <f>H45</f>
+        <f>H45*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H45" s="9">
         <f>IF(OR(D45="",F45=""),0,D45*F45)</f>
         <v/>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>0</v>
+      <c r="I45" s="9">
+        <f>H45*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -6417,15 +6463,16 @@
         <v>0</v>
       </c>
       <c r="G46" s="9">
-        <f>H46</f>
+        <f>H46*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H46" s="9">
         <f>IF(OR(D46="",F46=""),0,D46*F46)</f>
         <v/>
       </c>
-      <c r="I46" s="9" t="n">
-        <v>0</v>
+      <c r="I46" s="9">
+        <f>H46*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -6443,15 +6490,16 @@
         <v>0</v>
       </c>
       <c r="G47" s="9">
-        <f>H47</f>
+        <f>H47*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H47" s="9">
         <f>IF(OR(D47="",F47=""),0,D47*F47)</f>
         <v/>
       </c>
-      <c r="I47" s="9" t="n">
-        <v>0</v>
+      <c r="I47" s="9">
+        <f>H47*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -6469,15 +6517,16 @@
         <v>0</v>
       </c>
       <c r="G48" s="9">
-        <f>H48</f>
+        <f>H48*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H48" s="9">
         <f>IF(OR(D48="",F48=""),0,D48*F48)</f>
         <v/>
       </c>
-      <c r="I48" s="9" t="n">
-        <v>0</v>
+      <c r="I48" s="9">
+        <f>H48*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -6495,15 +6544,16 @@
         <v>0</v>
       </c>
       <c r="G49" s="9">
-        <f>H49</f>
+        <f>H49*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H49" s="9">
         <f>IF(OR(D49="",F49=""),0,D49*F49)</f>
         <v/>
       </c>
-      <c r="I49" s="9" t="n">
-        <v>0</v>
+      <c r="I49" s="9">
+        <f>H49*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -6521,15 +6571,16 @@
         <v>0</v>
       </c>
       <c r="G50" s="9">
-        <f>H50</f>
+        <f>H50*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H50" s="9">
         <f>IF(OR(D50="",F50=""),0,D50*F50)</f>
         <v/>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
+      <c r="I50" s="9">
+        <f>H50*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -6547,25 +6598,34 @@
         <v>0</v>
       </c>
       <c r="G51" s="9">
-        <f>H51</f>
+        <f>H51*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H51" s="9">
         <f>IF(OR(D51="",F51=""),0,D51*F51)</f>
         <v/>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>0</v>
+      <c r="I51" s="9">
+        <f>H51*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="F52" t="inlineStr">
         <is>
-          <t>Плазма/лазер — себестоимость:</t>
-        </is>
+          <t>ПЛАЗМА / ЛАЗЕР — себестоимость:</t>
+        </is>
+      </c>
+      <c r="G52" s="13">
+        <f>SUM(G42:G51)</f>
+        <v/>
       </c>
       <c r="H52" s="13">
         <f>SUM(H42:H51)</f>
+        <v/>
+      </c>
+      <c r="I52" s="13">
+        <f>SUM(I42:I51)</f>
         <v/>
       </c>
     </row>
@@ -6611,7 +6671,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>С наценкой</t>
+          <t>С наценкой менеджера</t>
         </is>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -6914,7 +6974,7 @@
     <row r="67">
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ковка — себестоимость:</t>
+          <t>КОВАНЫЕ ЭЛЕМЕНТЫ / СПЕЦ. ПРОКАТ — себестоимость:</t>
         </is>
       </c>
       <c r="G67" s="13">
@@ -6967,12 +7027,12 @@
       </c>
       <c r="F71" s="10" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>Цена поставщика</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Сумма</t>
+          <t>С наценкой менеджера</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
@@ -6982,7 +7042,7 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>Наценка</t>
+          <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
@@ -7001,15 +7061,16 @@
         <v>0</v>
       </c>
       <c r="G72" s="9">
-        <f>H72</f>
+        <f>H72*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H72" s="9">
         <f>IF(OR(D72="",F72=""),0,D72*F72)</f>
         <v/>
       </c>
-      <c r="I72" s="9" t="n">
-        <v>0</v>
+      <c r="I72" s="9">
+        <f>H72*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -7027,15 +7088,16 @@
         <v>0</v>
       </c>
       <c r="G73" s="9">
-        <f>H73</f>
+        <f>H73*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H73" s="9">
         <f>IF(OR(D73="",F73=""),0,D73*F73)</f>
         <v/>
       </c>
-      <c r="I73" s="9" t="n">
-        <v>0</v>
+      <c r="I73" s="9">
+        <f>H73*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -7053,15 +7115,16 @@
         <v>0</v>
       </c>
       <c r="G74" s="9">
-        <f>H74</f>
+        <f>H74*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H74" s="9">
         <f>IF(OR(D74="",F74=""),0,D74*F74)</f>
         <v/>
       </c>
-      <c r="I74" s="9" t="n">
-        <v>0</v>
+      <c r="I74" s="9">
+        <f>H74*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -7079,15 +7142,16 @@
         <v>0</v>
       </c>
       <c r="G75" s="9">
-        <f>H75</f>
+        <f>H75*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H75" s="9">
         <f>IF(OR(D75="",F75=""),0,D75*F75)</f>
         <v/>
       </c>
-      <c r="I75" s="9" t="n">
-        <v>0</v>
+      <c r="I75" s="9">
+        <f>H75*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -7105,15 +7169,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="9">
-        <f>H76</f>
+        <f>H76*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H76" s="9">
         <f>IF(OR(D76="",F76=""),0,D76*F76)</f>
         <v/>
       </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
+      <c r="I76" s="9">
+        <f>H76*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -7131,15 +7196,16 @@
         <v>0</v>
       </c>
       <c r="G77" s="9">
-        <f>H77</f>
+        <f>H77*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H77" s="9">
         <f>IF(OR(D77="",F77=""),0,D77*F77)</f>
         <v/>
       </c>
-      <c r="I77" s="9" t="n">
-        <v>0</v>
+      <c r="I77" s="9">
+        <f>H77*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -7157,15 +7223,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="9">
-        <f>H78</f>
+        <f>H78*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H78" s="9">
         <f>IF(OR(D78="",F78=""),0,D78*F78)</f>
         <v/>
       </c>
-      <c r="I78" s="9" t="n">
-        <v>0</v>
+      <c r="I78" s="9">
+        <f>H78*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -7183,15 +7250,16 @@
         <v>0</v>
       </c>
       <c r="G79" s="9">
-        <f>H79</f>
+        <f>H79*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H79" s="9">
         <f>IF(OR(D79="",F79=""),0,D79*F79)</f>
         <v/>
       </c>
-      <c r="I79" s="9" t="n">
-        <v>0</v>
+      <c r="I79" s="9">
+        <f>H79*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -7209,15 +7277,16 @@
         <v>0</v>
       </c>
       <c r="G80" s="9">
-        <f>H80</f>
+        <f>H80*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H80" s="9">
         <f>IF(OR(D80="",F80=""),0,D80*F80)</f>
         <v/>
       </c>
-      <c r="I80" s="9" t="n">
-        <v>0</v>
+      <c r="I80" s="9">
+        <f>H80*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -7235,67 +7304,422 @@
         <v>0</v>
       </c>
       <c r="G81" s="9">
-        <f>H81</f>
+        <f>H81*(1+Параметры!$C$6)</f>
         <v/>
       </c>
       <c r="H81" s="9">
         <f>IF(OR(D81="",F81=""),0,D81*F81)</f>
         <v/>
       </c>
-      <c r="I81" s="9" t="n">
-        <v>0</v>
+      <c r="I81" s="9">
+        <f>H81*Параметры!$C$6</f>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="F82" t="inlineStr">
         <is>
-          <t>Токарка — себестоимость:</t>
-        </is>
+          <t>ТОКАРНЫЕ РАБОТЫ — себестоимость:</t>
+        </is>
+      </c>
+      <c r="G82" s="13">
+        <f>SUM(G72:G81)</f>
+        <v/>
       </c>
       <c r="H82" s="13">
         <f>SUM(H72:H81)</f>
         <v/>
       </c>
+      <c r="I82" s="13">
+        <f>SUM(I72:I81)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
-      <c r="F84" s="32" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЕ КОМПЛЕКТУЮЩИЕ (до 10 позиций)</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="G84" s="11" t="n"/>
+      <c r="H84" s="11" t="n"/>
+      <c r="I84" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Комплектующая</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Описание / артикул</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Ед.</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Цена поставщика</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>С наценкой менеджера</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Себестоимость</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>Наценка менеджера</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="9">
+        <f>H87*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H87" s="9">
+        <f>IF(OR(D87="",F87=""),0,D87*F87)</f>
+        <v/>
+      </c>
+      <c r="I87" s="9">
+        <f>H87*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="9">
+        <f>H88*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H88" s="9">
+        <f>IF(OR(D88="",F88=""),0,D88*F88)</f>
+        <v/>
+      </c>
+      <c r="I88" s="9">
+        <f>H88*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F89" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="9">
+        <f>H89*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H89" s="9">
+        <f>IF(OR(D89="",F89=""),0,D89*F89)</f>
+        <v/>
+      </c>
+      <c r="I89" s="9">
+        <f>H89*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F90" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="9">
+        <f>H90*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H90" s="9">
+        <f>IF(OR(D90="",F90=""),0,D90*F90)</f>
+        <v/>
+      </c>
+      <c r="I90" s="9">
+        <f>H90*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F91" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="9">
+        <f>H91*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H91" s="9">
+        <f>IF(OR(D91="",F91=""),0,D91*F91)</f>
+        <v/>
+      </c>
+      <c r="I91" s="9">
+        <f>H91*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F92" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="9">
+        <f>H92*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H92" s="9">
+        <f>IF(OR(D92="",F92=""),0,D92*F92)</f>
+        <v/>
+      </c>
+      <c r="I92" s="9">
+        <f>H92*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F93" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="9">
+        <f>H93*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H93" s="9">
+        <f>IF(OR(D93="",F93=""),0,D93*F93)</f>
+        <v/>
+      </c>
+      <c r="I93" s="9">
+        <f>H93*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F94" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="9">
+        <f>H94*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H94" s="9">
+        <f>IF(OR(D94="",F94=""),0,D94*F94)</f>
+        <v/>
+      </c>
+      <c r="I94" s="9">
+        <f>H94*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F95" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="9">
+        <f>H95*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H95" s="9">
+        <f>IF(OR(D95="",F95=""),0,D95*F95)</f>
+        <v/>
+      </c>
+      <c r="I95" s="9">
+        <f>H95*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F96" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="9">
+        <f>H96*(1+Параметры!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H96" s="9">
+        <f>IF(OR(D96="",F96=""),0,D96*F96)</f>
+        <v/>
+      </c>
+      <c r="I96" s="9">
+        <f>H96*Параметры!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНЫЕ КОМПЛЕКТУЮЩИЕ — себестоимость:</t>
+        </is>
+      </c>
+      <c r="G97" s="13">
+        <f>SUM(G87:G96)</f>
+        <v/>
+      </c>
+      <c r="H97" s="13">
+        <f>SUM(H87:H96)</f>
+        <v/>
+      </c>
+      <c r="I97" s="13">
+        <f>SUM(I87:I96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="F99" s="32" t="inlineStr">
         <is>
           <t>ВСЕГО металл — себестоимость:</t>
         </is>
       </c>
-      <c r="H84" s="18">
-        <f>H37+H52+H67+H82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="F85" s="32" t="inlineStr">
-        <is>
-          <t>ВСЕГО наценка менеджера с металла (прокат+ковка):</t>
-        </is>
-      </c>
-      <c r="H85" s="33">
-        <f>I37+I67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Обновление прайса: меняйте жёлтые цены в колонке F. Кол-во D — под конкретный заказ. Итоги уходят в Калькуляцию автоматически.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
+      <c r="H99" s="18">
+        <f>H37+H52+H67+H82+H97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="F100" s="32" t="inlineStr">
+        <is>
+          <t>ВСЕГО наценка менеджера с листа Металл:</t>
+        </is>
+      </c>
+      <c r="H100" s="33">
+        <f>I37+I52+I67+I82+I97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Обновление прайса: меняйте жёлтые цены в колонке F. Кол-во D — под заказ. Прокат, плазма, ковка, токарка и комплектующие — с наценкой менеджера. Итоги уходят в Калькуляцию автоматически.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
   </sheetData>
   <autoFilter ref="B5:J36"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B102:J103"/>
     <mergeCell ref="B39:I39"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="B54:I54"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B87:J88"/>
+    <mergeCell ref="B84:I84"/>
     <mergeCell ref="B4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/Калькуляция_проект_v1.xlsx
+++ b/templates/Калькуляция_проект_v1.xlsx
@@ -10,13 +10,15 @@
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Калькуляция" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Металл" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Параметры" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Касса" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Инструкция" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Предложение" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Параметры" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Касса" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Инструкция" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Калькуляция'!$B$15:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Металл'!$B$5:$J$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Предложение'!$B$3:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,7 +33,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.00&quot; ₽&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +82,12 @@
       <color rgb="002F3E46"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F3E46"/>
+      <sz val="20"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -124,7 +132,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -190,11 +198,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,8 +290,32 @@
     <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,7 +325,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7730,6 +7810,570 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:I50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>ДЛЯ ВАС: после заполнения — Файл → Экспорт → в PDF (только этот лист). Так удобнее, чем скриншот. Жёлтое — текст для клиента. Фото: Вставка → Изображение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>КОММЕРЧЕСКОЕ ПРЕДЛОЖЕНИЕ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Изготовление металлоконструкций: ворота, заборы, лестницы, мебель, интерьер / экстерьер</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>ДАННЫЕ ЗАКАЗА</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Дата</t>
+        </is>
+      </c>
+      <c r="C7" s="35">
+        <f>Сводка!C9</f>
+        <v/>
+      </c>
+      <c r="D7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="C8" s="36">
+        <f>Сводка!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>№ клиента</t>
+        </is>
+      </c>
+      <c r="C9" s="36">
+        <f>Сводка!C11</f>
+        <v/>
+      </c>
+      <c r="D9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Объект</t>
+        </is>
+      </c>
+      <c r="C10" s="36">
+        <f>Сводка!C6</f>
+        <v/>
+      </c>
+      <c r="D10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Изделие / конструкция</t>
+        </is>
+      </c>
+      <c r="C11" s="36">
+        <f>Сводка!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="C12" s="36">
+        <f>Сводка!C8</f>
+        <v/>
+      </c>
+      <c r="D12" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>ОПИСАНИЕ РАБОТ ДЛЯ ЗАКАЗЧИКА</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="37" t="inlineStr">
+        <is>
+          <t>Кратко опишите, что входит в работу: размеры, материал, цвет покраски, монтаж да/нет, сроки. Этот текст увидит клиент.</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="38" t="n"/>
+      <c r="F15" s="38" t="n"/>
+      <c r="G15" s="39" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="B16" s="40" t="n"/>
+      <c r="G16" s="41" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="B17" s="40" t="n"/>
+      <c r="G17" s="41" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="B18" s="42" t="n"/>
+      <c r="C18" s="43" t="n"/>
+      <c r="D18" s="43" t="n"/>
+      <c r="E18" s="43" t="n"/>
+      <c r="F18" s="43" t="n"/>
+      <c r="G18" s="44" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ФОТО / ЭСКИЗЫ</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="B21" s="45" t="inlineStr">
+        <is>
+          <t>ФОТО 1
+Вставка → Изображение
+или Ctrl+V</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="45" t="inlineStr">
+        <is>
+          <t>ФОТО 2
+Вставка → Изображение
+или Ctrl+V</t>
+        </is>
+      </c>
+      <c r="F21" s="38" t="n"/>
+      <c r="G21" s="39" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="40" t="n"/>
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="40" t="n"/>
+      <c r="G22" s="41" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="40" t="n"/>
+      <c r="D23" s="41" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="G23" s="41" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="B24" s="40" t="n"/>
+      <c r="D24" s="41" t="n"/>
+      <c r="E24" s="40" t="n"/>
+      <c r="G24" s="41" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="B25" s="40" t="n"/>
+      <c r="D25" s="41" t="n"/>
+      <c r="E25" s="40" t="n"/>
+      <c r="G25" s="41" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="42" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="44" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>СОСТАВ И СТОИМОСТЬ ПО РАЗДЕЛАМ</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Раскладка нужна: клиенту проще понять, за что платит. Цифры — доля от цены КП (не ваша себестоимость). Если не хотите светить структуру — удалите строки 31–36 и оставьте только ИТОГО.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Раздел</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Что входит</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Сумма для заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>1. Проектирование и подготовка</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="46" t="inlineStr">
+        <is>
+          <t>Замер, эскизы, лекала</t>
+        </is>
+      </c>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="13">
+        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I31/$I$50*Сводка!$D$24)</f>
+        <v/>
+      </c>
+      <c r="I31" s="47">
+        <f>SUMIF(Калькуляция!$B$16:$B$250,"Проектирование",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Лекала",Калькуляция!$H$16:$H$250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>2. Материалы</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="46" t="inlineStr">
+        <is>
+          <t>Металл, комплектующие, резка/токарка</t>
+        </is>
+      </c>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="13">
+        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I32/$I$50*Сводка!$D$24)</f>
+        <v/>
+      </c>
+      <c r="I32" s="47">
+        <f>SUMIF(Калькуляция!$B$16:$B$250,"Металл",Калькуляция!$H$16:$H$250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>3. Изготовление</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="46" t="inlineStr">
+        <is>
+          <t>Работы в цехе, расходники</t>
+        </is>
+      </c>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="13">
+        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I33/$I$50*Сводка!$D$24)</f>
+        <v/>
+      </c>
+      <c r="I33" s="47">
+        <f>SUMIF(Калькуляция!$B$16:$B$250,"Производство",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Расходники/день",Калькуляция!$H$16:$H$250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>4. Окраска и обработка</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="46" t="inlineStr">
+        <is>
+          <t>Эмаль / порошок / пескоструй</t>
+        </is>
+      </c>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="13">
+        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I34/$I$50*Сводка!$D$24)</f>
+        <v/>
+      </c>
+      <c r="I34" s="47">
+        <f>SUMIF(Калькуляция!$B$16:$B$250,"Покраска эмаль",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Пескоструй",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Порошок",Калькуляция!$H$16:$H$250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>5. Монтаж</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="46" t="inlineStr">
+        <is>
+          <t>Доставка, установка на объекте</t>
+        </is>
+      </c>
+      <c r="F35" s="27" t="n"/>
+      <c r="G35" s="13">
+        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I35/$I$50*Сводка!$D$24)</f>
+        <v/>
+      </c>
+      <c r="I35" s="47">
+        <f>SUMIF(Калькуляция!$B$16:$B$250,"Предмонтаж",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Монтаж",Калькуляция!$H$16:$H$250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="48" t="inlineStr">
+        <is>
+          <t>ИТОГО К ОПЛАТЕ</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="18">
+        <f>Сводка!D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Контроль суммы разделов (должно = итогу):</t>
+        </is>
+      </c>
+      <c r="G37" s="49">
+        <f>SUM(G31:G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Цена конечная для заказчика. Налог самозанятого (НПД) учтён во внутреннем расчёте и заложен в итоговую сумму — отдельно клиенту не выставляется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>УСЛОВИЯ</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Срок изготовления, раб. дней</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Аванс, %</t>
+        </is>
+      </c>
+      <c r="E41" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Аванс, ₽</t>
+        </is>
+      </c>
+      <c r="G41" s="13">
+        <f>G36*E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Остаток к оплате, ₽</t>
+        </is>
+      </c>
+      <c r="C42" s="13">
+        <f>G36-G41</f>
+        <v/>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Срок действия КП, дней</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>Доп. условия (оплата, гарантия, доставка):</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="51" t="inlineStr">
+        <is>
+          <t>Оплата: аванс по запуску, остаток после монтажа / готовности. Гарантия на сварные соединения и покраску — по договорённости. Изменения проекта после согласования могут изменить стоимость.</t>
+        </is>
+      </c>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="38" t="n"/>
+      <c r="E44" s="38" t="n"/>
+      <c r="F44" s="38" t="n"/>
+      <c r="G44" s="39" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="40" t="n"/>
+      <c r="G45" s="41" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="42" t="n"/>
+      <c r="C46" s="43" t="n"/>
+      <c r="D46" s="43" t="n"/>
+      <c r="E46" s="43" t="n"/>
+      <c r="F46" s="43" t="n"/>
+      <c r="G46" s="44" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="52" t="inlineStr">
+        <is>
+          <t>Исполнитель: самозанятый</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="52" t="inlineStr">
+        <is>
+          <t>Подпись / согласование заказчика: ______________________    Дата: __________</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="I50">
+        <f>SUM(I31:I35)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="B15:G18"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B44:G46"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E21:G26"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B21:D26"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B36:F36"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F35"/>
@@ -7780,10 +8424,10 @@
           <t>Наценка менеджера на закупки</t>
         </is>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="53" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="46" t="inlineStr">
         <is>
           <t>От цены поставщика. Ваша прибыль как менеджера.</t>
         </is>
@@ -7795,10 +8439,10 @@
           <t>Целевая маржа проекта (от выручки)</t>
         </is>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="53" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>Чистая маржа после НПД. Диапазон обычно 10%…30%+.</t>
         </is>
@@ -7810,10 +8454,10 @@
           <t>Минимальная допустимая маржа</t>
         </is>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="53" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="46" t="inlineStr">
         <is>
           <t>Ниже — статус «НИЖЕ МИНИМУМА».</t>
         </is>
@@ -7825,10 +8469,10 @@
           <t>Налог НПД (самозанятость)</t>
         </is>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C9" s="53" t="n">
         <v>0.04</v>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>4% — физлица, 6% — юрлица/ИП.</t>
         </is>
@@ -7840,10 +8484,10 @@
           <t>Аренда, ₽ / рабочий день</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="54" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
         <is>
           <t>Ставка аренды цеха на рабочий день.</t>
         </is>
@@ -7855,10 +8499,10 @@
           <t>Рабочих дней в месяце</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="54" t="n">
         <v>22</v>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>Справочно для пересчёта постоянных расходов.</t>
         </is>
@@ -7870,10 +8514,10 @@
           <t>Агентские, % от цены КП</t>
         </is>
       </c>
-      <c r="C12" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="C12" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="46" t="inlineStr">
         <is>
           <t>Если есть посредник — поставьте %, иначе 0.</t>
         </is>
@@ -7892,11 +8536,11 @@
           <t>Множитель цены при целевой марже</t>
         </is>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="55">
         <f>1/(1-C9-C7-C12)</f>
         <v/>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>Цена КП ≈ Себестоимость × коэффициент</t>
         </is>
@@ -7908,11 +8552,11 @@
           <t>Множитель цены при минимальной марже</t>
         </is>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="55">
         <f>1/(1-C9-C8-C12)</f>
         <v/>
       </c>
-      <c r="D16" s="35" t="n"/>
+      <c r="D16" s="46" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="32" t="inlineStr">
@@ -7985,7 +8629,7 @@
       </c>
     </row>
     <row r="29" ht="110" customHeight="1">
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="56" t="inlineStr">
         <is>
           <t>Себестоимость C = реальные выплаты (материалы по цене поставщика, труд, транспорт, аренда, расходники, субподряд).
 Наценка менеджера = % только на тип «закупка» — это часть вашей прибыли, не расход.
@@ -8012,7 +8656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8036,7 +8680,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>ЭТОТ ЛИСТ НЕ УЧАСТВУЕТ В РАСЧЁТЕ ЦЕНЫ И МАРЖИ.
 Нужен только чтобы помнить: сколько клиент уже заплатил и сколько вы уже потратили по заказу.
@@ -8129,7 +8773,7 @@
           <t>Ещё должен клиент:</t>
         </is>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="58">
         <f>D17-D16</f>
         <v/>
       </c>
@@ -8302,13 +8946,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -8330,83 +8974,100 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="52" t="inlineStr">
         <is>
           <t>1. «Параметры» — % менеджера, целевая/мин. маржа, НПД, аренда/день.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="41" t="inlineStr">
-        <is>
-          <t>2. «Металл» — в каталоге проката поставьте кол-во штанг (шт = 6 м). Цены уже загружены; при смене прайса правьте колонку F.</t>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>2. «Металл» — кол-во штанг проката (шт = 6 м), плюс плазма/ковка/токарка/комплектующие. На все эти блоки — наценка менеджера.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="52" t="inlineStr">
         <is>
           <t>3. «Калькуляция» — количества по этапам (дни, рейсы, материалы).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>4. «Сводка» — смотрите рекомендуемую цену, впишите цену КП в жёлтую ячейку, проверьте статус.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="41" t="inlineStr"/>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>5. «Предложение» — текст и фото для клиента; суммы разделов и итог подтянутся сами. Затем Экспорт в PDF.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="52" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>ВМЕСТО СКРИНШОТА:</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>• Откройте лист «Предложение» → Файл → Экспорт в PDF (или Печать → PDF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>• Отправьте PDF в WhatsApp / Telegram / почту — выглядит аккуратнее скриншота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="52" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>КАССА — НЕ ДЛЯ РАСЧЁТА ЦЕНЫ:</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="41" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="52" t="inlineStr">
         <is>
           <t>• Нужна после сделки: авансы клиента и факт выплат (металл, ЗП, транспорт).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="41" t="inlineStr">
-        <is>
-          <t>• Из Сводки берёт только «Цену КП», чтобы показать остаток к получению.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="41" t="inlineStr">
-        <is>
-          <t>• В Сводку / маржу / калькуляцию ничего не возвращает.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="41" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="52" t="inlineStr">
         <is>
           <t>• Пока готовите КП — лист Касса можно не открывать.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="41" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="41" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="52" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="52" t="inlineStr">
         <is>
           <t>Типы изделий: Ворота, Забор, Лестница, Мебель, Интерьер, Экстерьер, Сувенир, Прочее.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="41" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="52" t="inlineStr">
         <is>
           <t>В шапке Сводки: Клиент + № клиента.</t>
         </is>

--- a/templates/Калькуляция_проект_v1.xlsx
+++ b/templates/Калькуляция_проект_v1.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Калькуляция'!$B$15:$L$115</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Металл'!$B$5:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Предложение'!$B$3:$G$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Предложение'!$B$3:$F$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,14 +26,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="167" formatCode="#,##0.00&quot; ₽&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="[$-419]D MMMM YYYY;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -83,13 +84,18 @@
       <sz val="14"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Georgia"/>
       <b val="1"/>
-      <color rgb="002F3E46"/>
-      <sz val="20"/>
+      <color rgb="001A1A1A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <color rgb="001A1A1A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +135,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE8A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B9080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C94C4C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6E59A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -229,7 +265,9 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color rgb="00B0B0B0"/>
@@ -238,9 +276,7 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
+      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="00B0B0B0"/>
@@ -251,7 +287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -290,32 +326,42 @@
     <xf numFmtId="168" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="13" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1321,7 +1367,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>Параметры!$B$19:$B$26</formula1>
+      <formula1>Параметры!$B$34:$B$41</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7812,561 +7858,930 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:I50"/>
+  <dimension ref="B1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>ДЛЯ ВАС: после заполнения — Файл → Экспорт → в PDF (только этот лист). Так удобнее, чем скриншот. Жёлтое — текст для клиента. Фото: Вставка → Изображение.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="34" t="inlineStr">
-        <is>
-          <t>КОММЕРЧЕСКОЕ ПРЕДЛОЖЕНИЕ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Изготовление металлоконструкций: ворота, заборы, лестницы, мебель, интерьер / экстерьер</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>ДАННЫЕ ЗАКАЗА</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n"/>
+          <t>ДЛЯ ВАС: заполните смету и вставьте фото → Файл → Экспорт в PDF (этот лист). Ориентир цены со Сводки справа. Шаблон как ваш PDF Андрей_Светлана_Краснознаменск.</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ориентир из Сводки (цена КП):</t>
+        </is>
+      </c>
+      <c r="H1" s="13">
+        <f>Сводка!D24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="B3" s="34">
+        <f>Параметры!C19&amp;CHAR(10)&amp;Параметры!C20</f>
+        <v/>
+      </c>
+      <c r="D3" s="35" t="inlineStr">
+        <is>
+          <t>Предложение №:</t>
+        </is>
+      </c>
+      <c r="E3" s="16">
+        <f>IF(Сводка!C11="","—",Сводка!C11)</f>
+        <v/>
+      </c>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="D4" s="35" t="inlineStr">
+        <is>
+          <t>Дата:</t>
+        </is>
+      </c>
+      <c r="E4" s="36">
+        <f>Сводка!C9</f>
+        <v/>
+      </c>
+      <c r="F4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="D5" s="35" t="inlineStr">
+        <is>
+          <t>Актуально до:</t>
+        </is>
+      </c>
+      <c r="E5" s="37">
+        <f>E4+Параметры!C31</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="C7" s="35">
-        <f>Сводка!C9</f>
-        <v/>
-      </c>
-      <c r="D7" s="4" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Клиент:</t>
+        </is>
+      </c>
+      <c r="C7" s="30">
+        <f>Сводка!C10</f>
+        <v/>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Объект:</t>
+        </is>
+      </c>
+      <c r="E7" s="30">
+        <f>Сводка!C6</f>
+        <v/>
+      </c>
+      <c r="F7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Клиент</t>
-        </is>
-      </c>
-      <c r="C8" s="36">
-        <f>Сводка!C10</f>
-        <v/>
-      </c>
-      <c r="D8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>№ клиента</t>
-        </is>
-      </c>
-      <c r="C9" s="36">
-        <f>Сводка!C11</f>
-        <v/>
-      </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Изделие:</t>
+        </is>
+      </c>
+      <c r="C8" s="30">
+        <f>Сводка!C7</f>
+        <v/>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Тип:</t>
+        </is>
+      </c>
+      <c r="E8" s="30">
+        <f>Сводка!C8</f>
+        <v/>
+      </c>
+      <c r="F8" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Объект</t>
-        </is>
-      </c>
-      <c r="C10" s="36">
-        <f>Сводка!C6</f>
-        <v/>
-      </c>
-      <c r="D10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Изделие / конструкция</t>
-        </is>
-      </c>
-      <c r="C11" s="36">
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>Визуализация изделия «</t>
+        </is>
+      </c>
+      <c r="C10" s="39">
         <f>Сводка!C7</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Тип</t>
-        </is>
-      </c>
-      <c r="C12" s="36">
-        <f>Сводка!C8</f>
-        <v/>
-      </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ОПИСАНИЕ РАБОТ ДЛЯ ЗАКАЗЧИКА</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>Кратко опишите, что входит в работу: размеры, материал, цвет покраски, монтаж да/нет, сроки. Этот текст увидит клиент.</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="38" t="n"/>
-      <c r="F15" s="38" t="n"/>
-      <c r="G15" s="39" t="n"/>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="40" t="n"/>
-      <c r="G16" s="41" t="n"/>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="40" t="n"/>
-      <c r="G17" s="41" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="42" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="44" t="n"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>ФОТО / ЭСКИЗЫ</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="4" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="45" t="inlineStr">
-        <is>
-          <t>ФОТО 1
-Вставка → Изображение
-или Ctrl+V</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="39" t="n"/>
-      <c r="E21" s="45" t="inlineStr">
-        <is>
-          <t>ФОТО 2
-Вставка → Изображение
-или Ctrl+V</t>
-        </is>
-      </c>
-      <c r="F21" s="38" t="n"/>
-      <c r="G21" s="39" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="40" t="n"/>
-      <c r="D22" s="41" t="n"/>
-      <c r="E22" s="40" t="n"/>
-      <c r="G22" s="41" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="40" t="n"/>
-      <c r="D23" s="41" t="n"/>
-      <c r="E23" s="40" t="n"/>
-      <c r="G23" s="41" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="40" t="n"/>
-      <c r="D24" s="41" t="n"/>
-      <c r="E24" s="40" t="n"/>
-      <c r="G24" s="41" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="40" t="n"/>
-      <c r="D25" s="41" t="n"/>
-      <c r="E25" s="40" t="n"/>
-      <c r="G25" s="41" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="42" t="n"/>
-      <c r="C26" s="43" t="n"/>
-      <c r="D26" s="44" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="F26" s="43" t="n"/>
-      <c r="G26" s="44" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="B11" s="40" t="inlineStr">
+        <is>
+          <t>ФОТО / ВИЗУАЛИЗАЦИЯ 1
+Вставка → Изображение  или  Ctrl+V</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="n"/>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>ФОТО / ВИЗУАЛИЗАЦИЯ 2
+Вставка → Изображение  или  Ctrl+V</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="n"/>
+      <c r="F11" s="41" t="n"/>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="B12" s="43" t="n"/>
+      <c r="C12" s="44" t="n"/>
+      <c r="D12" s="43" t="n"/>
+      <c r="F12" s="44" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="B13" s="43" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="43" t="n"/>
+      <c r="F13" s="44" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="B14" s="43" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="43" t="n"/>
+      <c r="F14" s="44" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="B15" s="45" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="47" t="n"/>
+      <c r="F15" s="46" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>Визуализация изделия «</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="B18" s="40" t="inlineStr">
+        <is>
+          <t>ФОТО / ВИЗУАЛИЗАЦИЯ 3
+Вставка → Изображение</t>
+        </is>
+      </c>
+      <c r="C18" s="41" t="n"/>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>ФОТО / ВИЗУАЛИЗАЦИЯ 4
+Вставка → Изображение</t>
+        </is>
+      </c>
+      <c r="E18" s="42" t="n"/>
+      <c r="F18" s="41" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="43" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="43" t="n"/>
+      <c r="F19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="B20" s="43" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="43" t="n"/>
+      <c r="F20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="B21" s="43" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="F21" s="44" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="B22" s="45" t="n"/>
+      <c r="C22" s="46" t="n"/>
+      <c r="D22" s="45" t="n"/>
+      <c r="E22" s="47" t="n"/>
+      <c r="F22" s="46" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>Смета работ и материалов</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Материал / расход / часть</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>ед. изм.</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>количество</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>стоимость за шт</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>общее</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9">
+        <f>IF(OR(D26="",E26=""),0,D26*E26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <f>IF(OR(D27="",E27=""),0,D27*E27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>СОСТАВ И СТОИМОСТЬ ПО РАЗДЕЛАМ</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="4" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9">
+        <f>IF(OR(D28="",E28=""),0,D28*E28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Раскладка нужна: клиенту проще понять, за что платит. Цифры — доля от цены КП (не ваша себестоимость). Если не хотите светить структуру — удалите строки 31–36 и оставьте только ИТОГО.</t>
-        </is>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <f>IF(OR(D29="",E29=""),0,D29*E29)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="10" t="inlineStr">
-        <is>
-          <t>Раздел</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Что входит</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>Сумма для заказчика</t>
-        </is>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9">
+        <f>IF(OR(D30="",E30=""),0,D30*E30)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>1. Проектирование и подготовка</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="46" t="inlineStr">
-        <is>
-          <t>Замер, эскизы, лекала</t>
-        </is>
-      </c>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="13">
-        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I31/$I$50*Сводка!$D$24)</f>
-        <v/>
-      </c>
-      <c r="I31" s="47">
-        <f>SUMIF(Калькуляция!$B$16:$B$250,"Проектирование",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Лекала",Калькуляция!$H$16:$H$250)</f>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <f>IF(OR(D31="",E31=""),0,D31*E31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>2. Материалы</t>
-        </is>
-      </c>
-      <c r="C32" s="27" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="46" t="inlineStr">
-        <is>
-          <t>Металл, комплектующие, резка/токарка</t>
-        </is>
-      </c>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="13">
-        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I32/$I$50*Сводка!$D$24)</f>
-        <v/>
-      </c>
-      <c r="I32" s="47">
-        <f>SUMIF(Калькуляция!$B$16:$B$250,"Металл",Калькуляция!$H$16:$H$250)</f>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="9">
+        <f>IF(OR(D32="",E32=""),0,D32*E32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>3. Изготовление</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="46" t="inlineStr">
-        <is>
-          <t>Работы в цехе, расходники</t>
-        </is>
-      </c>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="13">
-        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I33/$I$50*Сводка!$D$24)</f>
-        <v/>
-      </c>
-      <c r="I33" s="47">
-        <f>SUMIF(Калькуляция!$B$16:$B$250,"Производство",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Расходники/день",Калькуляция!$H$16:$H$250)</f>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="9">
+        <f>IF(OR(D33="",E33=""),0,D33*E33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>4. Окраска и обработка</t>
-        </is>
-      </c>
-      <c r="C34" s="27" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="46" t="inlineStr">
-        <is>
-          <t>Эмаль / порошок / пескоструй</t>
-        </is>
-      </c>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="13">
-        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I34/$I$50*Сводка!$D$24)</f>
-        <v/>
-      </c>
-      <c r="I34" s="47">
-        <f>SUMIF(Калькуляция!$B$16:$B$250,"Покраска эмаль",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Пескоструй",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Порошок",Калькуляция!$H$16:$H$250)</f>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9">
+        <f>IF(OR(D34="",E34=""),0,D34*E34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>5. Монтаж</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="46" t="inlineStr">
-        <is>
-          <t>Доставка, установка на объекте</t>
-        </is>
-      </c>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="13">
-        <f>IF(OR(Сводка!$D$24=0,$I$50=0),0,I35/$I$50*Сводка!$D$24)</f>
-        <v/>
-      </c>
-      <c r="I35" s="47">
-        <f>SUMIF(Калькуляция!$B$16:$B$250,"Предмонтаж",Калькуляция!$H$16:$H$250)+SUMIF(Калькуляция!$B$16:$B$250,"Монтаж",Калькуляция!$H$16:$H$250)</f>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <f>IF(OR(D35="",E35=""),0,D35*E35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="48" t="inlineStr">
-        <is>
-          <t>ИТОГО К ОПЛАТЕ</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="18">
-        <f>Сводка!D24</f>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9">
+        <f>IF(OR(D36="",E36=""),0,D36*E36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Контроль суммы разделов (должно = итогу):</t>
-        </is>
-      </c>
-      <c r="G37" s="49">
-        <f>SUM(G31:G35)</f>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
+        <f>IF(OR(D37="",E37=""),0,D37*E37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Цена конечная для заказчика. Налог самозанятого (НПД) учтён во внутреннем расчёте и заложен в итоговую сумму — отдельно клиенту не выставляется.</t>
-        </is>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="9">
+        <f>IF(OR(D38="",E38=""),0,D38*E38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
+        <f>IF(OR(D39="",E39=""),0,D39*E39)</f>
+        <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>УСЛОВИЯ</t>
-        </is>
-      </c>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="4" t="n"/>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <f>IF(OR(D40="",E40=""),0,D40*E40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Срок изготовления, раб. дней</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Аванс, %</t>
-        </is>
-      </c>
-      <c r="E41" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Аванс, ₽</t>
-        </is>
-      </c>
-      <c r="G41" s="13">
-        <f>G36*E41</f>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
+        <f>IF(OR(D41="",E41=""),0,D41*E41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Остаток к оплате, ₽</t>
-        </is>
-      </c>
-      <c r="C42" s="13">
-        <f>G36-G41</f>
-        <v/>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Срок действия КП, дней</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>10</v>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="9">
+        <f>IF(OR(D42="",E42=""),0,D42*E42)</f>
+        <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="32" t="inlineStr">
-        <is>
-          <t>Доп. условия (оплата, гарантия, доставка):</t>
-        </is>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9">
+        <f>IF(OR(D43="",E43=""),0,D43*E43)</f>
+        <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="51" t="inlineStr">
-        <is>
-          <t>Оплата: аванс по запуску, остаток после монтажа / готовности. Гарантия на сварные соединения и покраску — по договорённости. Изменения проекта после согласования могут изменить стоимость.</t>
-        </is>
-      </c>
-      <c r="C44" s="38" t="n"/>
-      <c r="D44" s="38" t="n"/>
-      <c r="E44" s="38" t="n"/>
-      <c r="F44" s="38" t="n"/>
-      <c r="G44" s="39" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="9">
+        <f>IF(OR(D44="",E44=""),0,D44*E44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="40" t="n"/>
-      <c r="G45" s="41" t="n"/>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
+        <f>IF(OR(D45="",E45=""),0,D45*E45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
-      <c r="B46" s="42" t="n"/>
-      <c r="C46" s="43" t="n"/>
-      <c r="D46" s="43" t="n"/>
-      <c r="E46" s="43" t="n"/>
-      <c r="F46" s="43" t="n"/>
-      <c r="G46" s="44" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <f>IF(OR(D46="",E46=""),0,D46*E46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <f>IF(OR(D47="",E47=""),0,D47*E47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
-      <c r="B48" s="52" t="inlineStr">
-        <is>
-          <t>Исполнитель: самозанятый</t>
-        </is>
+      <c r="B48" s="49" t="inlineStr">
+        <is>
+          <t>Итого расходы на изготовление (материал, расходники, покраска, доставка)</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="n"/>
+      <c r="D48" s="49" t="n"/>
+      <c r="E48" s="49" t="n"/>
+      <c r="F48" s="50">
+        <f>SUM(F26:F47)</f>
+        <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="52" t="inlineStr">
-        <is>
-          <t>Подпись / согласование заказчика: ______________________    Дата: __________</t>
-        </is>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Изготовление конструкции</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>ед.</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
+        <f>D49*E49</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="I50">
-        <f>SUM(I31:I35)</f>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Монтаж</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>ед.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <f>D50*E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="51" t="inlineStr">
+        <is>
+          <t>Итого за работу</t>
+        </is>
+      </c>
+      <c r="C51" s="51" t="n"/>
+      <c r="D51" s="51" t="n"/>
+      <c r="E51" s="51" t="n"/>
+      <c r="F51" s="52">
+        <f>F49+F50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="53" t="inlineStr">
+        <is>
+          <t>Итого общая</t>
+        </is>
+      </c>
+      <c r="C52" s="53" t="n"/>
+      <c r="D52" s="53" t="n"/>
+      <c r="E52" s="53" t="n"/>
+      <c r="F52" s="54">
+        <f>F48+F51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="55" t="inlineStr">
+        <is>
+          <t>Проведение через СЗ 4% физ. лицо</t>
+        </is>
+      </c>
+      <c r="C53" s="55" t="n"/>
+      <c r="D53" s="55" t="n"/>
+      <c r="E53" s="55" t="n"/>
+      <c r="F53" s="56">
+        <f>F52*1.04</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="55" t="inlineStr">
+        <is>
+          <t>Проведение через СЗ 6% Юр. лицо</t>
+        </is>
+      </c>
+      <c r="C54" s="55" t="n"/>
+      <c r="D54" s="55" t="n"/>
+      <c r="E54" s="55" t="n"/>
+      <c r="F54" s="56">
+        <f>F52*1.06</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Цены в смете — для заказчика (уже с вашей наценкой). Строки «СЗ 4%/6%» = Итого общая × 1.04 / 1.06, как в вашем PDF. После заполнения отправьте лист в PDF вместо скриншота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="57" t="inlineStr">
+        <is>
+          <t>Контакты</t>
+        </is>
+      </c>
+      <c r="C57" s="58" t="n"/>
+      <c r="D57" s="58" t="n"/>
+      <c r="E57" s="59" t="inlineStr">
+        <is>
+          <t>С уважением,</t>
+        </is>
+      </c>
+      <c r="F57" s="58" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="60">
+        <f>Параметры!C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="60">
+        <f>"Телефон: "&amp;Параметры!C22</f>
+        <v/>
+      </c>
+      <c r="E59" s="32">
+        <f>Параметры!C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="60">
+        <f>"Сайт: "&amp;Параметры!C23</f>
+        <v/>
+      </c>
+      <c r="E60" s="60">
+        <f>Параметры!C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="60">
+        <f>"Email: "&amp;Параметры!C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="60">
+        <f>"Адрес: "&amp;Параметры!C25</f>
+        <v/>
+      </c>
+      <c r="E62" s="61" t="inlineStr">
+        <is>
+          <t>Подпись</t>
+        </is>
+      </c>
+      <c r="F62" s="41" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="60" t="inlineStr">
+        <is>
+          <t>График работы:</t>
+        </is>
+      </c>
+      <c r="E63" s="43" t="n"/>
+      <c r="F63" s="44" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="60">
+        <f>"Пн-Пт: "&amp;Параметры!C26</f>
+        <v/>
+      </c>
+      <c r="E64" s="43" t="n"/>
+      <c r="F64" s="44" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="60">
+        <f>"Сб: "&amp;Параметры!C27</f>
+        <v/>
+      </c>
+      <c r="E65" s="45" t="n"/>
+      <c r="F65" s="46" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="60">
+        <f>"Вс: "&amp;Параметры!C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="60" t="inlineStr">
+        <is>
+          <t>Профиль:</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="60">
+        <f>"Стаж работы: "&amp;Параметры!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="60">
+        <f>Параметры!C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="32">
+        <f>"Действительно до: "&amp;TEXT(E5,"DD.MM.YYYY")</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B15:G18"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B44:G46"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E21:G26"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B21:D26"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D11:F15"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B3:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="B18:C22"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B11:C15"/>
+    <mergeCell ref="D18:F22"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="E62:F65"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8376,13 +8791,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F35"/>
+  <dimension ref="B2:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
@@ -8424,10 +8839,10 @@
           <t>Наценка менеджера на закупки</t>
         </is>
       </c>
-      <c r="C6" s="53" t="n">
+      <c r="C6" s="62" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="46" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>От цены поставщика. Ваша прибыль как менеджера.</t>
         </is>
@@ -8439,10 +8854,10 @@
           <t>Целевая маржа проекта (от выручки)</t>
         </is>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="62" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="46" t="inlineStr">
+      <c r="D7" s="63" t="inlineStr">
         <is>
           <t>Чистая маржа после НПД. Диапазон обычно 10%…30%+.</t>
         </is>
@@ -8454,10 +8869,10 @@
           <t>Минимальная допустимая маржа</t>
         </is>
       </c>
-      <c r="C8" s="53" t="n">
+      <c r="C8" s="62" t="n">
         <v>0.1</v>
       </c>
-      <c r="D8" s="46" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>Ниже — статус «НИЖЕ МИНИМУМА».</t>
         </is>
@@ -8469,10 +8884,10 @@
           <t>Налог НПД (самозанятость)</t>
         </is>
       </c>
-      <c r="C9" s="53" t="n">
+      <c r="C9" s="62" t="n">
         <v>0.04</v>
       </c>
-      <c r="D9" s="46" t="inlineStr">
+      <c r="D9" s="63" t="inlineStr">
         <is>
           <t>4% — физлица, 6% — юрлица/ИП.</t>
         </is>
@@ -8484,10 +8899,10 @@
           <t>Аренда, ₽ / рабочий день</t>
         </is>
       </c>
-      <c r="C10" s="54" t="n">
+      <c r="C10" s="64" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="46" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>Ставка аренды цеха на рабочий день.</t>
         </is>
@@ -8499,10 +8914,10 @@
           <t>Рабочих дней в месяце</t>
         </is>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="64" t="n">
         <v>22</v>
       </c>
-      <c r="D11" s="46" t="inlineStr">
+      <c r="D11" s="63" t="inlineStr">
         <is>
           <t>Справочно для пересчёта постоянных расходов.</t>
         </is>
@@ -8514,10 +8929,10 @@
           <t>Агентские, % от цены КП</t>
         </is>
       </c>
-      <c r="C12" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="46" t="inlineStr">
+      <c r="C12" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="63" t="inlineStr">
         <is>
           <t>Если есть посредник — поставьте %, иначе 0.</t>
         </is>
@@ -8536,11 +8951,11 @@
           <t>Множитель цены при целевой марже</t>
         </is>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="65">
         <f>1/(1-C9-C7-C12)</f>
         <v/>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D15" s="63" t="inlineStr">
         <is>
           <t>Цена КП ≈ Себестоимость × коэффициент</t>
         </is>
@@ -8552,105 +8967,293 @@
           <t>Множитель цены при минимальной марже</t>
         </is>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="65">
         <f>1/(1-C9-C8-C12)</f>
         <v/>
       </c>
-      <c r="D16" s="46" t="n"/>
+      <c r="D16" s="63" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>Тип изделия (список для шапки)</t>
+          <t>БРЕНД И КОНТАКТЫ ДЛЯ КП</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Ворота</t>
-        </is>
-      </c>
+          <t>Имя в шапке КП</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>Кузнец Илай Саматов</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Забор</t>
-        </is>
-      </c>
+          <t>Подзаголовок</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>мастер художественной ковки</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Лестница</t>
-        </is>
-      </c>
+          <t>ФИО полностью</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Самозанятый Саматов Илай Валерьевич</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Мебель</t>
-        </is>
-      </c>
+          <t>Телефон</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>+7 (952) 058-92-78</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Интерьер</t>
-        </is>
-      </c>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Cenzyk.art</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Экстерьер</t>
-        </is>
-      </c>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>ilja.samatov@yandex.ru</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Сувенир</t>
-        </is>
-      </c>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>г. Калининград, ул. Ручейная, 2а</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>График Пн–Пт</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>9:00-17:00</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>График Сб</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>10:00-14:00</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>График Вс</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>выходной</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Стаж</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>11 лет</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Профиль (текст)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Мебель, лестничные и балконные ограждения, элементы декора.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Срок действия КП, дней</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>Тип изделия (список для шапки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Ворота</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Забор</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Лестница</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Мебель</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Интерьер</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Экстерьер</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Сувенир</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>Прочее</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="32" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="32" t="inlineStr">
         <is>
           <t>Правило маржи</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="110" customHeight="1">
-      <c r="B29" s="56" t="inlineStr">
+    <row r="44" ht="110" customHeight="1">
+      <c r="B44" s="66" t="inlineStr">
         <is>
           <t>Себестоимость C = реальные выплаты (материалы по цене поставщика, труд, транспорт, аренда, расходники, субподряд).
 Наценка менеджера = % только на тип «закупка» — это часть вашей прибыли, не расход.
 Цена для целевой маржи P = C / (1 − НПД% − целевая маржа% − агентские%).
 Прибыль = P − C − P×НПД − P×агентские.  Маржа % = Прибыль / P.
-Не добавляйте «+15% на закупки» и «+20% маржа» как две наценки на одну базу: 15% уже внутри итоговой прибыли.
-КАССА ЗАКАЗА — отдельный опциональный учёт денег после сделки. На рентабельность и цену КП НЕ влияет.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
+В листе «Предложение» варианты СЗ 4%/6% считаются как Итого×1.04 / Итого×1.06 — как в вашем PDF.
+КАССА — опциональный учёт денег после сделки, на цену КП не влияет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B29:F35"/>
+  <mergeCells count="17">
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B44:F50"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8680,7 +9283,7 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="57" t="inlineStr">
+      <c r="B3" s="67" t="inlineStr">
         <is>
           <t>ЭТОТ ЛИСТ НЕ УЧАСТВУЕТ В РАСЧЁТЕ ЦЕНЫ И МАРЖИ.
 Нужен только чтобы помнить: сколько клиент уже заплатил и сколько вы уже потратили по заказу.
@@ -8773,7 +9376,7 @@
           <t>Ещё должен клиент:</t>
         </is>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="68">
         <f>D17-D16</f>
         <v/>
       </c>
@@ -8974,42 +9577,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>1. «Параметры» — % менеджера, целевая/мин. маржа, НПД, аренда/день.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="52" t="inlineStr">
+      <c r="B6" s="60" t="inlineStr">
         <is>
           <t>2. «Металл» — кол-во штанг проката (шт = 6 м), плюс плазма/ковка/токарка/комплектующие. На все эти блоки — наценка менеджера.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="52" t="inlineStr">
+      <c r="B7" s="60" t="inlineStr">
         <is>
           <t>3. «Калькуляция» — количества по этапам (дни, рейсы, материалы).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="52" t="inlineStr">
+      <c r="B8" s="60" t="inlineStr">
         <is>
           <t>4. «Сводка» — смотрите рекомендуемую цену, впишите цену КП в жёлтую ячейку, проверьте статус.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="52" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
         <is>
           <t>5. «Предложение» — текст и фото для клиента; суммы разделов и итог подтянутся сами. Затем Экспорт в PDF.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="52" t="inlineStr"/>
+      <c r="B10" s="60" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="32" t="inlineStr">
@@ -9019,21 +9622,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="52" t="inlineStr">
+      <c r="B12" s="60" t="inlineStr">
         <is>
           <t>• Откройте лист «Предложение» → Файл → Экспорт в PDF (или Печать → PDF).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="52" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
         <is>
           <t>• Отправьте PDF в WhatsApp / Telegram / почту — выглядит аккуратнее скриншота.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="52" t="inlineStr"/>
+      <c r="B14" s="60" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="32" t="inlineStr">
@@ -9043,31 +9646,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="52" t="inlineStr">
+      <c r="B16" s="60" t="inlineStr">
         <is>
           <t>• Нужна после сделки: авансы клиента и факт выплат (металл, ЗП, транспорт).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="52" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>• Пока готовите КП — лист Касса можно не открывать.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="52" t="inlineStr"/>
+      <c r="B18" s="60" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="52" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>Типы изделий: Ворота, Забор, Лестница, Мебель, Интерьер, Экстерьер, Сувенир, Прочее.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="52" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>В шапке Сводки: Клиент + № клиента.</t>
         </is>

--- a/templates/Калькуляция_проект_v1.xlsx
+++ b/templates/Калькуляция_проект_v1.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="168" formatCode="[$-419]D MMMM YYYY"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
@@ -45,13 +45,36 @@
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="FF5A5D55"/>
+      <color rgb="FF666666"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font/>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF2F3E46"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="FF666666"/>
+      <color rgb="FF5A5D55"/>
       <sz val="9"/>
     </font>
     <font>
@@ -61,32 +84,9 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font/>
-    <font>
       <name val="Arial Black"/>
       <color rgb="FF141613"/>
       <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="FF2F3E46"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -123,16 +123,16 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF2F3E46"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="FF5A5D55"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF2F3E46"/>
-      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -187,20 +187,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F3E46"/>
-        <bgColor rgb="FF2F3E46"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF52796F"/>
         <bgColor rgb="FF52796F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8EEF2"/>
-        <bgColor rgb="FFE8EEF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -213,6 +201,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3BF"/>
         <bgColor rgb="FFFFF3BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3E46"/>
+        <bgColor rgb="FF2F3E46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF2"/>
+        <bgColor rgb="FFE8EEF2"/>
       </patternFill>
     </fill>
     <fill>
@@ -235,12 +235,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8E4D8"/>
-        <bgColor rgb="FFE8E4D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD8F3DC"/>
         <bgColor rgb="FFD8F3DC"/>
       </patternFill>
@@ -249,6 +243,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE8A3"/>
         <bgColor rgb="FFFFE8A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8E4D8"/>
+        <bgColor rgb="FFE8E4D8"/>
       </patternFill>
     </fill>
     <fill>
@@ -270,6 +270,14 @@
       <left style="thin">
         <color rgb="FFB0B0B0"/>
       </left>
+      <top style="thin">
+        <color rgb="FFB0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB0B0B0"/>
+      </bottom>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FFB0B0B0"/>
       </right>
@@ -281,9 +289,6 @@
       </bottom>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB0B0B0"/>
-      </left>
       <top style="thin">
         <color rgb="FFB0B0B0"/>
       </top>
@@ -292,6 +297,9 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB0B0B0"/>
+      </left>
       <right style="thin">
         <color rgb="FFB0B0B0"/>
       </right>
@@ -331,14 +339,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF141613"/>
-      </bottom>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FFB0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB0B0B0"/>
       </bottom>
     </border>
     <border>
@@ -534,166 +534,166 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="16" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="16" fillId="9" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="16" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="18" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="6" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="11" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -703,32 +703,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="9" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="23" fillId="8" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1058,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Сначала заполните Металл и Калькуляцию. Жёлтое — ввод. Остальное считается автоматически.</t>
         </is>
@@ -1079,112 +1079,112 @@
       <c r="F5" s="108" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Объект</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="C6" s="9" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="10">
         <f>'Параметры'!C6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Конструкция / изделие</t>
         </is>
       </c>
-      <c r="C7" s="23" t="n"/>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>Целевая маржа</t>
         </is>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="10">
         <f>'Параметры'!C7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n"/>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="C8" s="9" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>Мин. маржа</t>
         </is>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="10">
         <f>'Параметры'!C8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Дата расчёта</t>
         </is>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="15">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>НПД</t>
         </is>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="10">
         <f>'Параметры'!C9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Клиент</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="C10" s="9" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>Аренда / день</t>
         </is>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="12">
         <f>'Параметры'!C10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>№ клиента</t>
         </is>
       </c>
-      <c r="C11" s="23" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="C11" s="9" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>Агентские</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="10">
         <f>'Параметры'!C12</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>P&amp;L ПРОЕКТА</t>
         </is>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="C14" s="108" t="n"/>
-      <c r="D14" s="18">
+      <c r="D14" s="23">
         <f>'Калькуляция'!O8</f>
         <v/>
       </c>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="C15" s="108" t="n"/>
-      <c r="D15" s="34">
+      <c r="D15" s="12">
         <f>'Калькуляция'!O9</f>
         <v/>
       </c>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="C16" s="108" t="n"/>
-      <c r="D16" s="34">
+      <c r="D16" s="12">
         <f>'Калькуляция'!O10</f>
         <v/>
       </c>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="C17" s="108" t="n"/>
-      <c r="D17" s="34">
+      <c r="D17" s="12">
         <f>'Калькуляция'!O11</f>
         <v/>
       </c>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="C18" s="108" t="n"/>
-      <c r="D18" s="34">
+      <c r="D18" s="12">
         <f>'Калькуляция'!O12</f>
         <v/>
       </c>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C19" s="108" t="n"/>
-      <c r="D19" s="34">
+      <c r="D19" s="12">
         <f>'Калькуляция'!O13</f>
         <v/>
       </c>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="C20" s="108" t="n"/>
-      <c r="D20" s="18">
+      <c r="D20" s="23">
         <f>'Калькуляция'!O14</f>
         <v/>
       </c>
@@ -1283,14 +1283,14 @@
         </is>
       </c>
       <c r="C21" s="108" t="n"/>
-      <c r="D21" s="44">
+      <c r="D21" s="41">
         <f>'Калькуляция'!O15</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="106"/>
     <row r="23" ht="15.75" customHeight="1" s="106">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>ЦЕНА И МАРЖА</t>
         </is>
@@ -1305,54 +1305,54 @@
         </is>
       </c>
       <c r="C24" s="108" t="n"/>
-      <c r="D24" s="48" t="n">
-        <v>337000</v>
+      <c r="D24" s="45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="106">
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Рекомендуемая цена при целевой марже</t>
         </is>
       </c>
       <c r="C25" s="108" t="n"/>
-      <c r="D25" s="57">
+      <c r="D25" s="49">
         <f>IF((1-F9-F7-F11)&lt;=0,"Ошибка %",D14/(1-F9-F7-F11))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="106">
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Минимальная цена (при мин. марже)</t>
         </is>
       </c>
       <c r="C26" s="108" t="n"/>
-      <c r="D26" s="61">
+      <c r="D26" s="50">
         <f>IF((1-F9-F8-F11)&lt;=0,"Ошибка %",D14/(1-F9-F8-F11))</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="106">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>НПД с цены КП</t>
         </is>
       </c>
       <c r="C27" s="108" t="n"/>
-      <c r="D27" s="34">
+      <c r="D27" s="12">
         <f>D24*F9</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Агентские с цены КП</t>
         </is>
       </c>
       <c r="C28" s="108" t="n"/>
-      <c r="D28" s="34">
+      <c r="D28" s="12">
         <f>D24*F11</f>
         <v/>
       </c>
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="C29" s="108" t="n"/>
-      <c r="D29" s="18">
+      <c r="D29" s="23">
         <f>D24-D14-D27-D28</f>
         <v/>
       </c>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="C30" s="108" t="n"/>
-      <c r="D30" s="64">
+      <c r="D30" s="55">
         <f>IF(D24=0,0,D29/D24)</f>
         <v/>
       </c>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="C31" s="108" t="n"/>
-      <c r="D31" s="66">
+      <c r="D31" s="60">
         <f>IF(D24=0,"Введите цену КП",IF(D30&lt;F8,"НИЖЕ МИНИМУМА",IF(D30&lt;F7,"НИЖЕ ЦЕЛИ","ЦЕЛЬ ДОСТИГНУТА")))</f>
         <v/>
       </c>
@@ -1405,132 +1405,132 @@
       <c r="E33" s="108" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="106">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>Целевая маржа</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Цена КП</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>НПД</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>Прибыль</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="106">
-      <c r="B35" s="70" t="n">
+      <c r="B35" s="65" t="n">
         <v>0.1</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="12">
         <f>IF((1-$F$9-B35-$F$11)&lt;=0,0,$D$14/(1-$F$9-B35-$F$11))</f>
         <v/>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="12">
         <f>C35*$F$9</f>
         <v/>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="12">
         <f>C35-$D$14-D35-C35*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="106">
-      <c r="B36" s="70" t="n">
+      <c r="B36" s="65" t="n">
         <v>0.15</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="12">
         <f>IF((1-$F$9-B36-$F$11)&lt;=0,0,$D$14/(1-$F$9-B36-$F$11))</f>
         <v/>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="12">
         <f>C36*$F$9</f>
         <v/>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="12">
         <f>C36-$D$14-D36-C36*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="106">
-      <c r="B37" s="72" t="n">
+      <c r="B37" s="68" t="n">
         <v>0.2</v>
       </c>
-      <c r="C37" s="73">
+      <c r="C37" s="70">
         <f>IF((1-$F$9-B37-$F$11)&lt;=0,0,$D$14/(1-$F$9-B37-$F$11))</f>
         <v/>
       </c>
-      <c r="D37" s="73">
+      <c r="D37" s="70">
         <f>C37*$F$9</f>
         <v/>
       </c>
-      <c r="E37" s="73">
+      <c r="E37" s="70">
         <f>C37-$D$14-D37-C37*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="106">
-      <c r="B38" s="70" t="n">
+      <c r="B38" s="65" t="n">
         <v>0.25</v>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="12">
         <f>IF((1-$F$9-B38-$F$11)&lt;=0,0,$D$14/(1-$F$9-B38-$F$11))</f>
         <v/>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="12">
         <f>C38*$F$9</f>
         <v/>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="12">
         <f>C38-$D$14-D38-C38*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="106">
-      <c r="B39" s="70" t="n">
+      <c r="B39" s="65" t="n">
         <v>0.3</v>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="12">
         <f>IF((1-$F$9-B39-$F$11)&lt;=0,0,$D$14/(1-$F$9-B39-$F$11))</f>
         <v/>
       </c>
-      <c r="D39" s="34">
+      <c r="D39" s="12">
         <f>C39*$F$9</f>
         <v/>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="12">
         <f>C39-$D$14-D39-C39*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106">
-      <c r="B40" s="70" t="n">
+      <c r="B40" s="65" t="n">
         <v>0.35</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="12">
         <f>IF((1-$F$9-B40-$F$11)&lt;=0,0,$D$14/(1-$F$9-B40-$F$11))</f>
         <v/>
       </c>
-      <c r="D40" s="34">
+      <c r="D40" s="12">
         <f>C40*$F$9</f>
         <v/>
       </c>
-      <c r="E40" s="34">
+      <c r="E40" s="12">
         <f>C40-$D$14-D40-C40*$F$11</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="106"/>
     <row r="42" ht="15.75" customHeight="1" s="106">
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Строка 20% — базовый ориентир. Целевую маржу меняйте на листе Параметры.</t>
         </is>
@@ -1547,44 +1547,44 @@
       <c r="D44" s="108" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="106">
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Доля наценки менеджера в прибыли (при цене КП)</t>
         </is>
       </c>
       <c r="C45" s="108" t="n"/>
-      <c r="D45" s="15">
+      <c r="D45" s="10">
         <f>IF(D29&lt;=0,0,D20/D29)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="106">
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Выручка на день цеха</t>
         </is>
       </c>
       <c r="C46" s="108" t="n"/>
-      <c r="D46" s="34">
+      <c r="D46" s="12">
         <f>IF(D21=0,0,D24/D21)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="106">
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Прибыль на день цеха</t>
         </is>
       </c>
       <c r="C47" s="108" t="n"/>
-      <c r="D47" s="34">
+      <c r="D47" s="12">
         <f>IF(D21=0,0,D29/D21)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="106"/>
     <row r="49" ht="15.75" customHeight="1" s="106">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Рабочий контур: Металл → Калькуляция → Сводка (цена КП). Лист «Касса» — только ПОСЛЕ сделки, для авансов/выплат. На расчёт цены НЕ влияет — можно не трогать.</t>
         </is>
@@ -2639,64 +2639,64 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Жёлтые — ввод. Тип «закупка» получает наценку менеджера из Параметров. Аренда подтягивает ставку/день. Итоги справа — для Сводки.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Этап</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Статья / обоснование</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Тип</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Цена / ставка</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>В базу КП</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>ИТОГИ ДЛЯ СВОДКИ</t>
         </is>
@@ -2709,12 +2709,12 @@
           <t>1. Проектирование / замер</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>Контроль суммы себест.</t>
         </is>
       </c>
-      <c r="O6" s="18">
+      <c r="O6" s="23">
         <f>SUM(H6:H250)</f>
         <v/>
       </c>
@@ -2725,51 +2725,51 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Аренда на замер</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="37">
         <f>IF(OR(E7="",F7=""),0,E7*F7)</f>
         <v/>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="37">
         <f>IF(D7="закупка",H7*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="37">
         <f>H7+I7</f>
         <v/>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
       </c>
-      <c r="N7" s="9" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>Контроль наценки менеджера</t>
         </is>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="23">
         <f>SUM(I6:I250)</f>
         <v/>
       </c>
@@ -2780,12 +2780,12 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Транспорт по городу</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -2793,33 +2793,33 @@
       <c r="E8" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="37">
         <f>IF(OR(E8="",F8=""),0,E8*F8)</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="37">
         <f>IF(D8="закупка",H8*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="37">
         <f>H8+I8</f>
         <v/>
       </c>
-      <c r="L8" s="23" t="n"/>
-      <c r="N8" s="9" t="inlineStr">
+      <c r="L8" s="9" t="n"/>
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>Себестоимость проекта</t>
         </is>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="23">
         <f>O6</f>
         <v/>
       </c>
@@ -2830,12 +2830,12 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Транспорт по области</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -2843,33 +2843,33 @@
       <c r="E9" s="102" t="n">
         <v>4000</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>выезд</t>
         </is>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="37">
         <f>IF(OR(E9="",F9=""),0,E9*F9)</f>
         <v/>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="37">
         <f>IF(D9="закупка",H9*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="37">
         <f>H9+I9</f>
         <v/>
       </c>
-      <c r="L9" s="23" t="n"/>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="L9" s="9" t="n"/>
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>Закупки</t>
         </is>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="23">
         <f>SUMIF(D6:D250,"закупка",H6:H250)</f>
         <v/>
       </c>
@@ -2880,12 +2880,12 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Замер</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -2893,33 +2893,33 @@
       <c r="E10" s="102" t="n">
         <v>6000</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="37">
         <f>IF(OR(E10="",F10=""),0,E10*F10)</f>
         <v/>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="37">
         <f>IF(D10="закупка",H10*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="37">
         <f>H10+I10</f>
         <v/>
       </c>
-      <c r="L10" s="23" t="n"/>
-      <c r="N10" s="9" t="inlineStr">
+      <c r="L10" s="9" t="n"/>
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>Труд</t>
         </is>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="23">
         <f>SUMIF(D6:D250,"труд",H6:H250)</f>
         <v/>
       </c>
@@ -2930,12 +2930,12 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Консультация</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -2943,33 +2943,33 @@
       <c r="E11" s="102" t="n">
         <v>6000</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="37">
         <f>IF(OR(E11="",F11=""),0,E11*F11)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="37">
         <f>IF(D11="закупка",H11*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="37">
         <f>H11+I11</f>
         <v/>
       </c>
-      <c r="L11" s="23" t="n"/>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="L11" s="9" t="n"/>
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>Транспорт</t>
         </is>
       </c>
-      <c r="O11" s="18">
+      <c r="O11" s="23">
         <f>SUMIF(D6:D250,"транспорт",H6:H250)</f>
         <v/>
       </c>
@@ -2980,12 +2980,12 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Проектирование, эскизы</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -2993,33 +2993,33 @@
       <c r="E12" s="102" t="n">
         <v>13000</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="37">
         <f>IF(OR(E12="",F12=""),0,E12*F12)</f>
         <v/>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="37">
         <f>IF(D12="закупка",H12*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="37">
         <f>H12+I12</f>
         <v/>
       </c>
-      <c r="L12" s="23" t="n"/>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="L12" s="9" t="n"/>
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="O12" s="18">
+      <c r="O12" s="23">
         <f>SUMIF(D6:D250,"аренда",H6:H250)</f>
         <v/>
       </c>
@@ -3030,12 +3030,12 @@
           <t>2. Снять лекала / подготовка</t>
         </is>
       </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Услуги/прочее</t>
         </is>
       </c>
-      <c r="O13" s="18">
+      <c r="O13" s="23">
         <f>O6-O9-O10-O11-O12</f>
         <v/>
       </c>
@@ -3046,51 +3046,51 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F14" s="23" t="n">
+      <c r="F14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="37">
         <f>IF(OR(E14="",F14=""),0,E14*F14)</f>
         <v/>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="37">
         <f>IF(D14="закупка",H14*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="37">
         <f>H14+I14</f>
         <v/>
       </c>
-      <c r="L14" s="23" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
       </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="23">
         <f>O7</f>
         <v/>
       </c>
@@ -3101,12 +3101,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Мастер</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3114,31 +3114,31 @@
       <c r="E15" s="102" t="n">
         <v>7000</v>
       </c>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="37">
         <f>IF(OR(E15="",F15=""),0,E15*F15)</f>
         <v/>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="37">
         <f>IF(D15="закупка",H15*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="37">
         <f>H15+I15</f>
         <v/>
       </c>
-      <c r="L15" s="23" t="n"/>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="L15" s="9" t="n"/>
+      <c r="N15" s="6" t="inlineStr">
         <is>
           <t>Дни цеха</t>
         </is>
       </c>
-      <c r="O15" s="74">
+      <c r="O15" s="67">
         <f>SUMIF(D6:D250,"аренда",F6:F250)</f>
         <v/>
       </c>
@@ -3149,12 +3149,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Рабочий</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3162,27 +3162,27 @@
       <c r="E16" s="102" t="n">
         <v>5000</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="37">
         <f>IF(OR(E16="",F16=""),0,E16*F16)</f>
         <v/>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="37">
         <f>IF(D16="закупка",H16*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="37">
         <f>H16+I16</f>
         <v/>
       </c>
-      <c r="L16" s="23" t="n"/>
+      <c r="L16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="104" t="inlineStr">
@@ -3190,12 +3190,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Транспорт цех → объект</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -3203,27 +3203,27 @@
       <c r="E17" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="37">
         <f>IF(OR(E17="",F17=""),0,E17*F17)</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="37">
         <f>IF(D17="закупка",H17*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="37">
         <f>H17+I17</f>
         <v/>
       </c>
-      <c r="L17" s="23" t="n"/>
+      <c r="L17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="104" t="inlineStr">
@@ -3231,12 +3231,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Транспорт объект → цех</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -3244,27 +3244,27 @@
       <c r="E18" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="37">
         <f>IF(OR(E18="",F18=""),0,E18*F18)</f>
         <v/>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="37">
         <f>IF(D18="закупка",H18*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="37">
         <f>H18+I18</f>
         <v/>
       </c>
-      <c r="L18" s="23" t="n"/>
+      <c r="L18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="104" t="inlineStr">
@@ -3272,12 +3272,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Картоны</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -3285,27 +3285,27 @@
       <c r="E19" s="102" t="n">
         <v>300</v>
       </c>
-      <c r="F19" s="23" t="n">
+      <c r="F19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="37">
         <f>IF(OR(E19="",F19=""),0,E19*F19)</f>
         <v/>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="37">
         <f>IF(D19="закупка",H19*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="37">
         <f>H19+I19</f>
         <v/>
       </c>
-      <c r="L19" s="23" t="n"/>
+      <c r="L19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="104" t="inlineStr">
@@ -3313,12 +3313,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Расходники</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -3326,27 +3326,27 @@
       <c r="E20" s="102" t="n">
         <v>250</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="9" t="inlineStr">
         <is>
           <t>набор</t>
         </is>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="37">
         <f>IF(OR(E20="",F20=""),0,E20*F20)</f>
         <v/>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="37">
         <f>IF(D20="закупка",H20*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="37">
         <f>H20+I20</f>
         <v/>
       </c>
-      <c r="L20" s="23" t="n"/>
+      <c r="L20" s="9" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="106">
       <c r="B21" s="104" t="inlineStr">
@@ -3354,12 +3354,12 @@
           <t>Лекала</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Дерево</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -3367,27 +3367,27 @@
       <c r="E21" s="102" t="n">
         <v>1500</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="9" t="inlineStr">
         <is>
           <t>набор</t>
         </is>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="37">
         <f>IF(OR(E21="",F21=""),0,E21*F21)</f>
         <v/>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="37">
         <f>IF(D21="закупка",H21*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="37">
         <f>H21+I21</f>
         <v/>
       </c>
-      <c r="L21" s="23" t="n"/>
+      <c r="L21" s="9" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="106">
       <c r="B22" s="113" t="inlineStr">
@@ -3402,12 +3402,12 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Транспорт: микроавтобус (2ч)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -3415,25 +3415,25 @@
       <c r="E23" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="37">
         <f>IF(OR(E23="",F23=""),0,E23*F23)</f>
         <v/>
       </c>
-      <c r="I23" s="27">
+      <c r="I23" s="37">
         <f>IF(D23="закупка",H23*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J23" s="27">
+      <c r="J23" s="37">
         <f>H23+I23</f>
         <v/>
       </c>
-      <c r="L23" s="23" t="n"/>
+      <c r="L23" s="9" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="106">
       <c r="B24" s="104" t="inlineStr">
@@ -3441,12 +3441,12 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Транспорт: бортовая 4м (1ч)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -3454,25 +3454,25 @@
       <c r="E24" s="102" t="n">
         <v>1500</v>
       </c>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="37">
         <f>IF(OR(E24="",F24=""),0,E24*F24)</f>
         <v/>
       </c>
-      <c r="I24" s="27">
+      <c r="I24" s="37">
         <f>IF(D24="закупка",H24*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J24" s="27">
+      <c r="J24" s="37">
         <f>H24+I24</f>
         <v/>
       </c>
-      <c r="L24" s="23" t="n"/>
+      <c r="L24" s="9" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="106">
       <c r="B25" s="104" t="inlineStr">
@@ -3480,12 +3480,12 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Транспорт: бортовая 6м (1ч)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -3493,25 +3493,25 @@
       <c r="E25" s="102" t="n">
         <v>3500</v>
       </c>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="37">
         <f>IF(OR(E25="",F25=""),0,E25*F25)</f>
         <v/>
       </c>
-      <c r="I25" s="27">
+      <c r="I25" s="37">
         <f>IF(D25="закупка",H25*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J25" s="27">
+      <c r="J25" s="37">
         <f>H25+I25</f>
         <v/>
       </c>
-      <c r="L25" s="23" t="n"/>
+      <c r="L25" s="9" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="106">
       <c r="B26" s="104" t="inlineStr">
@@ -3519,39 +3519,41 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Металлопрокат (лист Металл)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="37">
         <f>'Металл'!H37</f>
         <v/>
       </c>
-      <c r="F26" s="88" t="n"/>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="F26" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
         <is>
           <t>сводка</t>
         </is>
       </c>
-      <c r="H26" s="27">
-        <f>IF(OR(E26="",F26=""),0,E26*F26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="27">
+      <c r="H26" s="37">
+        <f>IF(E26="",0,E26*IF(OR(F26="",F26=0),1,F26))</f>
+        <v/>
+      </c>
+      <c r="I26" s="37">
         <f>IF(D26="закупка",H26*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="37">
         <f>H26+I26</f>
         <v/>
       </c>
-      <c r="L26" s="23" t="inlineStr">
+      <c r="L26" s="9" t="inlineStr">
         <is>
           <t>Себестоимость проката (каталог, цена за шт 6м)</t>
         </is>
@@ -3563,39 +3565,41 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Лазер / плазма (лист Металл)</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="37">
         <f>'Металл'!H52</f>
         <v/>
       </c>
-      <c r="F27" s="88" t="n"/>
-      <c r="G27" s="23" t="inlineStr">
+      <c r="F27" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
         <is>
           <t>сводка</t>
         </is>
       </c>
-      <c r="H27" s="27">
-        <f>IF(OR(E27="",F27=""),0,E27*F27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="27">
+      <c r="H27" s="37">
+        <f>IF(E27="",0,E27*IF(OR(F27="",F27=0),1,F27))</f>
+        <v/>
+      </c>
+      <c r="I27" s="37">
         <f>IF(D27="закупка",H27*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="37">
         <f>H27+I27</f>
         <v/>
       </c>
-      <c r="L27" s="23" t="n"/>
+      <c r="L27" s="9" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
       <c r="B28" s="104" t="inlineStr">
@@ -3603,39 +3607,41 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Ков. элементы / спец. прокат</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="37">
         <f>'Металл'!H67</f>
         <v/>
       </c>
-      <c r="F28" s="88" t="n"/>
-      <c r="G28" s="23" t="inlineStr">
+      <c r="F28" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>сводка</t>
         </is>
       </c>
-      <c r="H28" s="27">
-        <f>IF(OR(E28="",F28=""),0,E28*F28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="27">
+      <c r="H28" s="37">
+        <f>IF(E28="",0,E28*IF(OR(F28="",F28=0),1,F28))</f>
+        <v/>
+      </c>
+      <c r="I28" s="37">
         <f>IF(D28="закупка",H28*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="37">
         <f>H28+I28</f>
         <v/>
       </c>
-      <c r="L28" s="23" t="n"/>
+      <c r="L28" s="9" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="106">
       <c r="B29" s="104" t="inlineStr">
@@ -3643,39 +3649,41 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Токарные работы (лист Металл)</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="37">
         <f>'Металл'!H82</f>
         <v/>
       </c>
-      <c r="F29" s="88" t="n"/>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="F29" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
         <is>
           <t>сводка</t>
         </is>
       </c>
-      <c r="H29" s="27">
-        <f>IF(OR(E29="",F29=""),0,E29*F29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="27">
+      <c r="H29" s="37">
+        <f>IF(E29="",0,E29*IF(OR(F29="",F29=0),1,F29))</f>
+        <v/>
+      </c>
+      <c r="I29" s="37">
         <f>IF(D29="закупка",H29*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J29" s="27">
+      <c r="J29" s="37">
         <f>H29+I29</f>
         <v/>
       </c>
-      <c r="L29" s="23" t="n"/>
+      <c r="L29" s="9" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="106">
       <c r="B30" s="104" t="inlineStr">
@@ -3683,39 +3691,41 @@
           <t>Металл</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Доп. комплектующие (лист Металл)</t>
         </is>
       </c>
-      <c r="D30" s="23" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="37">
         <f>'Металл'!H97</f>
         <v/>
       </c>
-      <c r="F30" s="88" t="n"/>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="F30" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>сводка</t>
         </is>
       </c>
-      <c r="H30" s="27">
-        <f>IF(OR(E30="",F30=""),0,E30*F30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="27">
+      <c r="H30" s="37">
+        <f>IF(E30="",0,E30*IF(OR(F30="",F30=0),1,F30))</f>
+        <v/>
+      </c>
+      <c r="I30" s="37">
         <f>IF(D30="закупка",H30*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J30" s="27">
+      <c r="J30" s="37">
         <f>H30+I30</f>
         <v/>
       </c>
-      <c r="L30" s="23" t="n"/>
+      <c r="L30" s="9" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="106">
       <c r="B31" s="113" t="inlineStr">
@@ -3730,39 +3740,41 @@
           <t>Производство</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Аренда цеха</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="23" t="inlineStr">
+      <c r="F32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H32" s="27">
+      <c r="H32" s="37">
         <f>IF(OR(E32="",F32=""),0,E32*F32)</f>
         <v/>
       </c>
-      <c r="I32" s="27">
+      <c r="I32" s="37">
         <f>IF(D32="закупка",H32*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J32" s="27">
+      <c r="J32" s="37">
         <f>H32+I32</f>
         <v/>
       </c>
-      <c r="L32" s="23" t="inlineStr">
+      <c r="L32" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
@@ -3774,12 +3786,12 @@
           <t>Производство</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Оплата труда: мастер</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3787,25 +3799,27 @@
       <c r="E33" s="102" t="n">
         <v>6000</v>
       </c>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="23" t="inlineStr">
+      <c r="F33" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H33" s="27">
+      <c r="H33" s="37">
         <f>IF(OR(E33="",F33=""),0,E33*F33)</f>
         <v/>
       </c>
-      <c r="I33" s="27">
+      <c r="I33" s="37">
         <f>IF(D33="закупка",H33*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J33" s="27">
+      <c r="J33" s="37">
         <f>H33+I33</f>
         <v/>
       </c>
-      <c r="L33" s="23" t="inlineStr">
+      <c r="L33" s="9" t="inlineStr">
         <is>
           <t>ФИО в примечании</t>
         </is>
@@ -3817,12 +3831,12 @@
           <t>Производство</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Оплата труда: рабочий</t>
         </is>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3830,25 +3844,27 @@
       <c r="E34" s="102" t="n">
         <v>4000</v>
       </c>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="23" t="inlineStr">
+      <c r="F34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H34" s="27">
+      <c r="H34" s="37">
         <f>IF(OR(E34="",F34=""),0,E34*F34)</f>
         <v/>
       </c>
-      <c r="I34" s="27">
+      <c r="I34" s="37">
         <f>IF(D34="закупка",H34*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J34" s="27">
+      <c r="J34" s="37">
         <f>H34+I34</f>
         <v/>
       </c>
-      <c r="L34" s="23" t="n"/>
+      <c r="L34" s="9" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="106">
       <c r="B35" s="104" t="inlineStr">
@@ -3856,12 +3872,12 @@
           <t>Производство</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Оплата труда: доп.1</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3869,25 +3885,25 @@
       <c r="E35" s="102" t="n">
         <v>6000</v>
       </c>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="23" t="inlineStr">
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H35" s="27">
+      <c r="H35" s="37">
         <f>IF(OR(E35="",F35=""),0,E35*F35)</f>
         <v/>
       </c>
-      <c r="I35" s="27">
+      <c r="I35" s="37">
         <f>IF(D35="закупка",H35*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J35" s="27">
+      <c r="J35" s="37">
         <f>H35+I35</f>
         <v/>
       </c>
-      <c r="L35" s="23" t="n"/>
+      <c r="L35" s="9" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="106">
       <c r="B36" s="104" t="inlineStr">
@@ -3895,12 +3911,12 @@
           <t>Производство</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Оплата труда: доп.2</t>
         </is>
       </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3908,25 +3924,25 @@
       <c r="E36" s="102" t="n">
         <v>4000</v>
       </c>
-      <c r="F36" s="23" t="n"/>
-      <c r="G36" s="23" t="inlineStr">
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H36" s="27">
+      <c r="H36" s="37">
         <f>IF(OR(E36="",F36=""),0,E36*F36)</f>
         <v/>
       </c>
-      <c r="I36" s="27">
+      <c r="I36" s="37">
         <f>IF(D36="закупка",H36*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J36" s="27">
+      <c r="J36" s="37">
         <f>H36+I36</f>
         <v/>
       </c>
-      <c r="L36" s="23" t="n"/>
+      <c r="L36" s="9" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="106">
       <c r="B37" s="113" t="inlineStr">
@@ -3941,39 +3957,39 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C38" s="23" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F38" s="23" t="n"/>
-      <c r="G38" s="23" t="inlineStr">
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H38" s="27">
+      <c r="H38" s="37">
         <f>IF(OR(E38="",F38=""),0,E38*F38)</f>
         <v/>
       </c>
-      <c r="I38" s="27">
+      <c r="I38" s="37">
         <f>IF(D38="закупка",H38*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J38" s="27">
+      <c r="J38" s="37">
         <f>H38+I38</f>
         <v/>
       </c>
-      <c r="L38" s="23" t="inlineStr">
+      <c r="L38" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
@@ -3985,12 +4001,12 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C39" s="23" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Монтажники</t>
         </is>
       </c>
-      <c r="D39" s="23" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -3998,27 +4014,27 @@
       <c r="E39" s="102" t="n">
         <v>7300</v>
       </c>
-      <c r="F39" s="23" t="n">
+      <c r="F39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="23" t="inlineStr">
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H39" s="27">
+      <c r="H39" s="37">
         <f>IF(OR(E39="",F39=""),0,E39*F39)</f>
         <v/>
       </c>
-      <c r="I39" s="27">
+      <c r="I39" s="37">
         <f>IF(D39="закупка",H39*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J39" s="27">
+      <c r="J39" s="37">
         <f>H39+I39</f>
         <v/>
       </c>
-      <c r="L39" s="23" t="n"/>
+      <c r="L39" s="9" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106">
       <c r="B40" s="104" t="inlineStr">
@@ -4026,12 +4042,12 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Помощник</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -4039,27 +4055,27 @@
       <c r="E40" s="102" t="n">
         <v>5000</v>
       </c>
-      <c r="F40" s="23" t="n">
+      <c r="F40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="23" t="inlineStr">
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H40" s="27">
+      <c r="H40" s="37">
         <f>IF(OR(E40="",F40=""),0,E40*F40)</f>
         <v/>
       </c>
-      <c r="I40" s="27">
+      <c r="I40" s="37">
         <f>IF(D40="закупка",H40*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J40" s="27">
+      <c r="J40" s="37">
         <f>H40+I40</f>
         <v/>
       </c>
-      <c r="L40" s="23" t="n"/>
+      <c r="L40" s="9" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="106">
       <c r="B41" s="104" t="inlineStr">
@@ -4067,12 +4083,12 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C41" s="23" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Транспорт цех → объект</t>
         </is>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4080,27 +4096,27 @@
       <c r="E41" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F41" s="23" t="n">
+      <c r="F41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="23" t="inlineStr">
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="37">
         <f>IF(OR(E41="",F41=""),0,E41*F41)</f>
         <v/>
       </c>
-      <c r="I41" s="27">
+      <c r="I41" s="37">
         <f>IF(D41="закупка",H41*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J41" s="27">
+      <c r="J41" s="37">
         <f>H41+I41</f>
         <v/>
       </c>
-      <c r="L41" s="23" t="n"/>
+      <c r="L41" s="9" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="106">
       <c r="B42" s="104" t="inlineStr">
@@ -4108,12 +4124,12 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C42" s="23" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>Транспорт объект → цех</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4121,27 +4137,27 @@
       <c r="E42" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F42" s="23" t="n">
+      <c r="F42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="23" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="37">
         <f>IF(OR(E42="",F42=""),0,E42*F42)</f>
         <v/>
       </c>
-      <c r="I42" s="27">
+      <c r="I42" s="37">
         <f>IF(D42="закупка",H42*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J42" s="27">
+      <c r="J42" s="37">
         <f>H42+I42</f>
         <v/>
       </c>
-      <c r="L42" s="23" t="n"/>
+      <c r="L42" s="9" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="106">
       <c r="B43" s="104" t="inlineStr">
@@ -4149,12 +4165,12 @@
           <t>Предмонтаж</t>
         </is>
       </c>
-      <c r="C43" s="23" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Такси</t>
         </is>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4162,27 +4178,27 @@
       <c r="E43" s="102" t="n">
         <v>1500</v>
       </c>
-      <c r="F43" s="23" t="n">
+      <c r="F43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="23" t="inlineStr">
+      <c r="G43" s="9" t="inlineStr">
         <is>
           <t>поездка</t>
         </is>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="37">
         <f>IF(OR(E43="",F43=""),0,E43*F43)</f>
         <v/>
       </c>
-      <c r="I43" s="27">
+      <c r="I43" s="37">
         <f>IF(D43="закупка",H43*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J43" s="27">
+      <c r="J43" s="37">
         <f>H43+I43</f>
         <v/>
       </c>
-      <c r="L43" s="23" t="n"/>
+      <c r="L43" s="9" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="106">
       <c r="B44" s="113" t="inlineStr">
@@ -4197,41 +4213,41 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C45" s="23" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D45" s="23" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F45" s="23" t="n">
+      <c r="F45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="23" t="inlineStr">
+      <c r="G45" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H45" s="27">
+      <c r="H45" s="37">
         <f>IF(OR(E45="",F45=""),0,E45*F45)</f>
         <v/>
       </c>
-      <c r="I45" s="27">
+      <c r="I45" s="37">
         <f>IF(D45="закупка",H45*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J45" s="27">
+      <c r="J45" s="37">
         <f>H45+I45</f>
         <v/>
       </c>
-      <c r="L45" s="23" t="inlineStr">
+      <c r="L45" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
@@ -4243,12 +4259,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C46" s="23" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Маляр</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -4256,27 +4272,27 @@
       <c r="E46" s="102" t="n">
         <v>3000</v>
       </c>
-      <c r="F46" s="23" t="n">
+      <c r="F46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="23" t="inlineStr">
+      <c r="G46" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="37">
         <f>IF(OR(E46="",F46=""),0,E46*F46)</f>
         <v/>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="37">
         <f>IF(D46="закупка",H46*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J46" s="27">
+      <c r="J46" s="37">
         <f>H46+I46</f>
         <v/>
       </c>
-      <c r="L46" s="23" t="n"/>
+      <c r="L46" s="9" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="106">
       <c r="B47" s="104" t="inlineStr">
@@ -4284,12 +4300,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
         <is>
           <t>Рабочий</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr">
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -4297,27 +4313,27 @@
       <c r="E47" s="102" t="n">
         <v>5000</v>
       </c>
-      <c r="F47" s="23" t="n">
+      <c r="F47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="23" t="inlineStr">
+      <c r="G47" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="37">
         <f>IF(OR(E47="",F47=""),0,E47*F47)</f>
         <v/>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="37">
         <f>IF(D47="закупка",H47*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J47" s="27">
+      <c r="J47" s="37">
         <f>H47+I47</f>
         <v/>
       </c>
-      <c r="L47" s="23" t="n"/>
+      <c r="L47" s="9" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="106">
       <c r="B48" s="104" t="inlineStr">
@@ -4325,12 +4341,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C48" s="23" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Респиратор</t>
         </is>
       </c>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4338,27 +4354,27 @@
       <c r="E48" s="102" t="n">
         <v>500</v>
       </c>
-      <c r="F48" s="23" t="n">
+      <c r="F48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="23" t="inlineStr">
+      <c r="G48" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H48" s="27">
+      <c r="H48" s="37">
         <f>IF(OR(E48="",F48=""),0,E48*F48)</f>
         <v/>
       </c>
-      <c r="I48" s="27">
+      <c r="I48" s="37">
         <f>IF(D48="закупка",H48*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J48" s="27">
+      <c r="J48" s="37">
         <f>H48+I48</f>
         <v/>
       </c>
-      <c r="L48" s="23" t="n"/>
+      <c r="L48" s="9" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="106">
       <c r="B49" s="104" t="inlineStr">
@@ -4366,12 +4382,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C49" s="23" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Грунт</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4379,27 +4395,27 @@
       <c r="E49" s="102" t="n">
         <v>600</v>
       </c>
-      <c r="F49" s="23" t="n">
+      <c r="F49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="23" t="inlineStr">
+      <c r="G49" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H49" s="27">
+      <c r="H49" s="37">
         <f>IF(OR(E49="",F49=""),0,E49*F49)</f>
         <v/>
       </c>
-      <c r="I49" s="27">
+      <c r="I49" s="37">
         <f>IF(D49="закупка",H49*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J49" s="27">
+      <c r="J49" s="37">
         <f>H49+I49</f>
         <v/>
       </c>
-      <c r="L49" s="23" t="n"/>
+      <c r="L49" s="9" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="106">
       <c r="B50" s="104" t="inlineStr">
@@ -4407,12 +4423,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Лак</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4420,27 +4436,27 @@
       <c r="E50" s="102" t="n">
         <v>1000</v>
       </c>
-      <c r="F50" s="23" t="n">
+      <c r="F50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="23" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H50" s="27">
+      <c r="H50" s="37">
         <f>IF(OR(E50="",F50=""),0,E50*F50)</f>
         <v/>
       </c>
-      <c r="I50" s="27">
+      <c r="I50" s="37">
         <f>IF(D50="закупка",H50*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J50" s="27">
+      <c r="J50" s="37">
         <f>H50+I50</f>
         <v/>
       </c>
-      <c r="L50" s="23" t="n"/>
+      <c r="L50" s="9" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="106">
       <c r="B51" s="104" t="inlineStr">
@@ -4448,12 +4464,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Эмаль 0,8л</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4461,27 +4477,27 @@
       <c r="E51" s="102" t="n">
         <v>1200</v>
       </c>
-      <c r="F51" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
+      <c r="F51" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H51" s="27">
+      <c r="H51" s="37">
         <f>IF(OR(E51="",F51=""),0,E51*F51)</f>
         <v/>
       </c>
-      <c r="I51" s="27">
+      <c r="I51" s="37">
         <f>IF(D51="закупка",H51*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J51" s="27">
+      <c r="J51" s="37">
         <f>H51+I51</f>
         <v/>
       </c>
-      <c r="L51" s="23" t="n"/>
+      <c r="L51" s="9" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="106">
       <c r="B52" s="104" t="inlineStr">
@@ -4489,12 +4505,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Эмаль 2,0л</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4502,27 +4518,27 @@
       <c r="E52" s="102" t="n">
         <v>3500</v>
       </c>
-      <c r="F52" s="23" t="n">
+      <c r="F52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G52" s="23" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H52" s="27">
+      <c r="H52" s="37">
         <f>IF(OR(E52="",F52=""),0,E52*F52)</f>
         <v/>
       </c>
-      <c r="I52" s="27">
+      <c r="I52" s="37">
         <f>IF(D52="закупка",H52*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J52" s="27">
+      <c r="J52" s="37">
         <f>H52+I52</f>
         <v/>
       </c>
-      <c r="L52" s="23" t="n"/>
+      <c r="L52" s="9" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="106">
       <c r="B53" s="104" t="inlineStr">
@@ -4530,12 +4546,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C53" s="23" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Мет.щётки, кисти</t>
         </is>
       </c>
-      <c r="D53" s="23" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4543,27 +4559,27 @@
       <c r="E53" s="102" t="n">
         <v>300</v>
       </c>
-      <c r="F53" s="23" t="n">
+      <c r="F53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G53" s="23" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>набор</t>
         </is>
       </c>
-      <c r="H53" s="27">
+      <c r="H53" s="37">
         <f>IF(OR(E53="",F53=""),0,E53*F53)</f>
         <v/>
       </c>
-      <c r="I53" s="27">
+      <c r="I53" s="37">
         <f>IF(D53="закупка",H53*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J53" s="27">
+      <c r="J53" s="37">
         <f>H53+I53</f>
         <v/>
       </c>
-      <c r="L53" s="23" t="n"/>
+      <c r="L53" s="9" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="106">
       <c r="B54" s="104" t="inlineStr">
@@ -4571,12 +4587,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Растворитель</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4584,27 +4600,27 @@
       <c r="E54" s="102" t="n">
         <v>370</v>
       </c>
-      <c r="F54" s="23" t="n">
+      <c r="F54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="23" t="inlineStr">
+      <c r="G54" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H54" s="27">
+      <c r="H54" s="37">
         <f>IF(OR(E54="",F54=""),0,E54*F54)</f>
         <v/>
       </c>
-      <c r="I54" s="27">
+      <c r="I54" s="37">
         <f>IF(D54="закупка",H54*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J54" s="27">
+      <c r="J54" s="37">
         <f>H54+I54</f>
         <v/>
       </c>
-      <c r="L54" s="23" t="n"/>
+      <c r="L54" s="9" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="106">
       <c r="B55" s="104" t="inlineStr">
@@ -4612,12 +4628,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>Холодный цинк</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -4625,27 +4641,27 @@
       <c r="E55" s="102" t="n">
         <v>2500</v>
       </c>
-      <c r="F55" s="23" t="n">
+      <c r="F55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G55" s="23" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="H55" s="27">
+      <c r="H55" s="37">
         <f>IF(OR(E55="",F55=""),0,E55*F55)</f>
         <v/>
       </c>
-      <c r="I55" s="27">
+      <c r="I55" s="37">
         <f>IF(D55="закупка",H55*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J55" s="27">
+      <c r="J55" s="37">
         <f>H55+I55</f>
         <v/>
       </c>
-      <c r="L55" s="23" t="n"/>
+      <c r="L55" s="9" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="106">
       <c r="B56" s="104" t="inlineStr">
@@ -4653,12 +4669,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Транспорт микроавтобус</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4666,27 +4682,27 @@
       <c r="E56" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F56" s="23" t="n">
+      <c r="F56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="23" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="37">
         <f>IF(OR(E56="",F56=""),0,E56*F56)</f>
         <v/>
       </c>
-      <c r="I56" s="27">
+      <c r="I56" s="37">
         <f>IF(D56="закупка",H56*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J56" s="27">
+      <c r="J56" s="37">
         <f>H56+I56</f>
         <v/>
       </c>
-      <c r="L56" s="23" t="n"/>
+      <c r="L56" s="9" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="106">
       <c r="B57" s="104" t="inlineStr">
@@ -4694,12 +4710,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C57" s="23" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Транспорт бортовая 4м</t>
         </is>
       </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D57" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4707,27 +4723,27 @@
       <c r="E57" s="102" t="n">
         <v>1500</v>
       </c>
-      <c r="F57" s="23" t="n">
+      <c r="F57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="23" t="inlineStr">
+      <c r="G57" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H57" s="27">
+      <c r="H57" s="37">
         <f>IF(OR(E57="",F57=""),0,E57*F57)</f>
         <v/>
       </c>
-      <c r="I57" s="27">
+      <c r="I57" s="37">
         <f>IF(D57="закупка",H57*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J57" s="27">
+      <c r="J57" s="37">
         <f>H57+I57</f>
         <v/>
       </c>
-      <c r="L57" s="23" t="n"/>
+      <c r="L57" s="9" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="106">
       <c r="B58" s="104" t="inlineStr">
@@ -4735,12 +4751,12 @@
           <t>Покраска эмаль</t>
         </is>
       </c>
-      <c r="C58" s="23" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Транспорт бортовая 6м</t>
         </is>
       </c>
-      <c r="D58" s="23" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4748,27 +4764,27 @@
       <c r="E58" s="102" t="n">
         <v>3500</v>
       </c>
-      <c r="F58" s="23" t="n">
+      <c r="F58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="23" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H58" s="27">
+      <c r="H58" s="37">
         <f>IF(OR(E58="",F58=""),0,E58*F58)</f>
         <v/>
       </c>
-      <c r="I58" s="27">
+      <c r="I58" s="37">
         <f>IF(D58="закупка",H58*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J58" s="27">
+      <c r="J58" s="37">
         <f>H58+I58</f>
         <v/>
       </c>
-      <c r="L58" s="23" t="n"/>
+      <c r="L58" s="9" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="106">
       <c r="B59" s="113" t="inlineStr">
@@ -4783,12 +4799,12 @@
           <t>Пескоструй</t>
         </is>
       </c>
-      <c r="C60" s="23" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>Услуга пескоструй</t>
         </is>
       </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -4796,27 +4812,27 @@
       <c r="E60" s="102" t="n">
         <v>900</v>
       </c>
-      <c r="F60" s="23" t="n">
+      <c r="F60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="23" t="inlineStr">
+      <c r="G60" s="9" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="H60" s="27">
+      <c r="H60" s="37">
         <f>IF(OR(E60="",F60=""),0,E60*F60)</f>
         <v/>
       </c>
-      <c r="I60" s="27">
+      <c r="I60" s="37">
         <f>IF(D60="закупка",H60*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J60" s="27">
+      <c r="J60" s="37">
         <f>H60+I60</f>
         <v/>
       </c>
-      <c r="L60" s="23" t="n"/>
+      <c r="L60" s="9" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="106">
       <c r="B61" s="104" t="inlineStr">
@@ -4824,12 +4840,12 @@
           <t>Пескоструй</t>
         </is>
       </c>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>Транспорт на пескоструй</t>
         </is>
       </c>
-      <c r="D61" s="23" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4837,27 +4853,27 @@
       <c r="E61" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F61" s="23" t="n">
+      <c r="F61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="23" t="inlineStr">
+      <c r="G61" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H61" s="27">
+      <c r="H61" s="37">
         <f>IF(OR(E61="",F61=""),0,E61*F61)</f>
         <v/>
       </c>
-      <c r="I61" s="27">
+      <c r="I61" s="37">
         <f>IF(D61="закупка",H61*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J61" s="27">
+      <c r="J61" s="37">
         <f>H61+I61</f>
         <v/>
       </c>
-      <c r="L61" s="23" t="n"/>
+      <c r="L61" s="9" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="106">
       <c r="B62" s="104" t="inlineStr">
@@ -4865,12 +4881,12 @@
           <t>Пескоструй</t>
         </is>
       </c>
-      <c r="C62" s="23" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
         <is>
           <t>Транспорт с пескоструя</t>
         </is>
       </c>
-      <c r="D62" s="23" t="inlineStr">
+      <c r="D62" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -4878,27 +4894,27 @@
       <c r="E62" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F62" s="23" t="n">
+      <c r="F62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="23" t="inlineStr">
+      <c r="G62" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H62" s="27">
+      <c r="H62" s="37">
         <f>IF(OR(E62="",F62=""),0,E62*F62)</f>
         <v/>
       </c>
-      <c r="I62" s="27">
+      <c r="I62" s="37">
         <f>IF(D62="закупка",H62*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J62" s="27">
+      <c r="J62" s="37">
         <f>H62+I62</f>
         <v/>
       </c>
-      <c r="L62" s="23" t="n"/>
+      <c r="L62" s="9" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="106">
       <c r="B63" s="113" t="inlineStr">
@@ -4913,12 +4929,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Покраска обычная</t>
         </is>
       </c>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -4926,25 +4942,25 @@
       <c r="E64" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F64" s="23" t="n"/>
-      <c r="G64" s="23" t="inlineStr">
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H64" s="27">
+      <c r="H64" s="37">
         <f>IF(OR(E64="",F64=""),0,E64*F64)</f>
         <v/>
       </c>
-      <c r="I64" s="27">
+      <c r="I64" s="37">
         <f>IF(D64="закупка",H64*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J64" s="27">
+      <c r="J64" s="37">
         <f>H64+I64</f>
         <v/>
       </c>
-      <c r="L64" s="23" t="n"/>
+      <c r="L64" s="9" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="106">
       <c r="B65" s="104" t="inlineStr">
@@ -4952,12 +4968,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>Покраска с цинком</t>
         </is>
       </c>
-      <c r="D65" s="23" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -4965,25 +4981,25 @@
       <c r="E65" s="102" t="n">
         <v>30000</v>
       </c>
-      <c r="F65" s="23" t="n"/>
-      <c r="G65" s="23" t="inlineStr">
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H65" s="27">
+      <c r="H65" s="37">
         <f>IF(OR(E65="",F65=""),0,E65*F65)</f>
         <v/>
       </c>
-      <c r="I65" s="27">
+      <c r="I65" s="37">
         <f>IF(D65="закупка",H65*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J65" s="27">
+      <c r="J65" s="37">
         <f>H65+I65</f>
         <v/>
       </c>
-      <c r="L65" s="23" t="n"/>
+      <c r="L65" s="9" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="106">
       <c r="B66" s="104" t="inlineStr">
@@ -4991,12 +5007,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C66" s="23" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Покраска шагрень</t>
         </is>
       </c>
-      <c r="D66" s="23" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -5004,25 +5020,25 @@
       <c r="E66" s="102" t="n">
         <v>2300</v>
       </c>
-      <c r="F66" s="23" t="n"/>
-      <c r="G66" s="23" t="inlineStr">
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H66" s="27">
+      <c r="H66" s="37">
         <f>IF(OR(E66="",F66=""),0,E66*F66)</f>
         <v/>
       </c>
-      <c r="I66" s="27">
+      <c r="I66" s="37">
         <f>IF(D66="закупка",H66*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J66" s="27">
+      <c r="J66" s="37">
         <f>H66+I66</f>
         <v/>
       </c>
-      <c r="L66" s="23" t="n"/>
+      <c r="L66" s="9" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="106">
       <c r="B67" s="104" t="inlineStr">
@@ -5030,12 +5046,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C67" s="23" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
         <is>
           <t>Покраска антик (молотковая)</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr">
+      <c r="D67" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
@@ -5043,25 +5059,25 @@
       <c r="E67" s="102" t="n">
         <v>2200</v>
       </c>
-      <c r="F67" s="23" t="n"/>
-      <c r="G67" s="23" t="inlineStr">
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
-      <c r="H67" s="27">
+      <c r="H67" s="37">
         <f>IF(OR(E67="",F67=""),0,E67*F67)</f>
         <v/>
       </c>
-      <c r="I67" s="27">
+      <c r="I67" s="37">
         <f>IF(D67="закупка",H67*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J67" s="27">
+      <c r="J67" s="37">
         <f>H67+I67</f>
         <v/>
       </c>
-      <c r="L67" s="23" t="n"/>
+      <c r="L67" s="9" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="106">
       <c r="B68" s="104" t="inlineStr">
@@ -5069,12 +5085,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C68" s="23" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>Транспорт на покраску</t>
         </is>
       </c>
-      <c r="D68" s="23" t="inlineStr">
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5082,25 +5098,25 @@
       <c r="E68" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F68" s="23" t="n"/>
-      <c r="G68" s="23" t="inlineStr">
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H68" s="27">
+      <c r="H68" s="37">
         <f>IF(OR(E68="",F68=""),0,E68*F68)</f>
         <v/>
       </c>
-      <c r="I68" s="27">
+      <c r="I68" s="37">
         <f>IF(D68="закупка",H68*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J68" s="27">
+      <c r="J68" s="37">
         <f>H68+I68</f>
         <v/>
       </c>
-      <c r="L68" s="23" t="n"/>
+      <c r="L68" s="9" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="106">
       <c r="B69" s="104" t="inlineStr">
@@ -5108,12 +5124,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C69" s="23" t="inlineStr">
+      <c r="C69" s="9" t="inlineStr">
         <is>
           <t>Транспорт с покраски</t>
         </is>
       </c>
-      <c r="D69" s="23" t="inlineStr">
+      <c r="D69" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5121,25 +5137,25 @@
       <c r="E69" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F69" s="23" t="n"/>
-      <c r="G69" s="23" t="inlineStr">
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H69" s="27">
+      <c r="H69" s="37">
         <f>IF(OR(E69="",F69=""),0,E69*F69)</f>
         <v/>
       </c>
-      <c r="I69" s="27">
+      <c r="I69" s="37">
         <f>IF(D69="закупка",H69*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J69" s="27">
+      <c r="J69" s="37">
         <f>H69+I69</f>
         <v/>
       </c>
-      <c r="L69" s="23" t="n"/>
+      <c r="L69" s="9" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="106">
       <c r="B70" s="104" t="inlineStr">
@@ -5147,12 +5163,12 @@
           <t>Порошок</t>
         </is>
       </c>
-      <c r="C70" s="23" t="inlineStr">
+      <c r="C70" s="9" t="inlineStr">
         <is>
           <t>Транспорт людей</t>
         </is>
       </c>
-      <c r="D70" s="23" t="inlineStr">
+      <c r="D70" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5160,25 +5176,25 @@
       <c r="E70" s="102" t="n">
         <v>500</v>
       </c>
-      <c r="F70" s="23" t="n"/>
-      <c r="G70" s="23" t="inlineStr">
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="inlineStr">
         <is>
           <t>поездка</t>
         </is>
       </c>
-      <c r="H70" s="27">
+      <c r="H70" s="37">
         <f>IF(OR(E70="",F70=""),0,E70*F70)</f>
         <v/>
       </c>
-      <c r="I70" s="27">
+      <c r="I70" s="37">
         <f>IF(D70="закупка",H70*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J70" s="27">
+      <c r="J70" s="37">
         <f>H70+I70</f>
         <v/>
       </c>
-      <c r="L70" s="23" t="n"/>
+      <c r="L70" s="9" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="106">
       <c r="B71" s="113" t="inlineStr">
@@ -5193,39 +5209,39 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C72" s="23" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>Аренда</t>
         </is>
       </c>
-      <c r="D72" s="23" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>аренда</t>
         </is>
       </c>
-      <c r="E72" s="27">
+      <c r="E72" s="37">
         <f>'Параметры'!$C$10</f>
         <v/>
       </c>
-      <c r="F72" s="23" t="n"/>
-      <c r="G72" s="23" t="inlineStr">
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H72" s="27">
+      <c r="H72" s="37">
         <f>IF(OR(E72="",F72=""),0,E72*F72)</f>
         <v/>
       </c>
-      <c r="I72" s="27">
+      <c r="I72" s="37">
         <f>IF(D72="закупка",H72*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J72" s="27">
+      <c r="J72" s="37">
         <f>H72+I72</f>
         <v/>
       </c>
-      <c r="L72" s="23" t="inlineStr">
+      <c r="L72" s="9" t="inlineStr">
         <is>
           <t>Ставка аренды из Параметры</t>
         </is>
@@ -5237,12 +5253,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>Монтажники</t>
         </is>
       </c>
-      <c r="D73" s="23" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -5250,25 +5266,25 @@
       <c r="E73" s="102" t="n">
         <v>5000</v>
       </c>
-      <c r="F73" s="23" t="n"/>
-      <c r="G73" s="23" t="inlineStr">
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H73" s="27">
+      <c r="H73" s="37">
         <f>IF(OR(E73="",F73=""),0,E73*F73)</f>
         <v/>
       </c>
-      <c r="I73" s="27">
+      <c r="I73" s="37">
         <f>IF(D73="закупка",H73*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J73" s="27">
+      <c r="J73" s="37">
         <f>H73+I73</f>
         <v/>
       </c>
-      <c r="L73" s="23" t="n"/>
+      <c r="L73" s="9" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="106">
       <c r="B74" s="104" t="inlineStr">
@@ -5276,12 +5292,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C74" s="23" t="inlineStr">
+      <c r="C74" s="9" t="inlineStr">
         <is>
           <t>Помощник</t>
         </is>
       </c>
-      <c r="D74" s="23" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>труд</t>
         </is>
@@ -5289,25 +5305,25 @@
       <c r="E74" s="102" t="n">
         <v>4000</v>
       </c>
-      <c r="F74" s="23" t="n"/>
-      <c r="G74" s="23" t="inlineStr">
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H74" s="27">
+      <c r="H74" s="37">
         <f>IF(OR(E74="",F74=""),0,E74*F74)</f>
         <v/>
       </c>
-      <c r="I74" s="27">
+      <c r="I74" s="37">
         <f>IF(D74="закупка",H74*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J74" s="27">
+      <c r="J74" s="37">
         <f>H74+I74</f>
         <v/>
       </c>
-      <c r="L74" s="23" t="n"/>
+      <c r="L74" s="9" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="106">
       <c r="B75" s="104" t="inlineStr">
@@ -5315,12 +5331,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C75" s="23" t="inlineStr">
+      <c r="C75" s="9" t="inlineStr">
         <is>
           <t>Крепежи, хим.анкер</t>
         </is>
       </c>
-      <c r="D75" s="23" t="inlineStr">
+      <c r="D75" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5328,25 +5344,25 @@
       <c r="E75" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F75" s="23" t="n"/>
-      <c r="G75" s="23" t="inlineStr">
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="inlineStr">
         <is>
           <t>набор</t>
         </is>
       </c>
-      <c r="H75" s="27">
+      <c r="H75" s="37">
         <f>IF(OR(E75="",F75=""),0,E75*F75)</f>
         <v/>
       </c>
-      <c r="I75" s="27">
+      <c r="I75" s="37">
         <f>IF(D75="закупка",H75*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J75" s="27">
+      <c r="J75" s="37">
         <f>H75+I75</f>
         <v/>
       </c>
-      <c r="L75" s="23" t="n"/>
+      <c r="L75" s="9" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="106">
       <c r="B76" s="104" t="inlineStr">
@@ -5354,12 +5370,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C76" s="23" t="inlineStr">
+      <c r="C76" s="9" t="inlineStr">
         <is>
           <t>Транспорт рабочих</t>
         </is>
       </c>
-      <c r="D76" s="23" t="inlineStr">
+      <c r="D76" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5367,27 +5383,27 @@
       <c r="E76" s="102" t="n">
         <v>500</v>
       </c>
-      <c r="F76" s="23" t="n">
+      <c r="F76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="23" t="inlineStr">
+      <c r="G76" s="9" t="inlineStr">
         <is>
           <t>поездка</t>
         </is>
       </c>
-      <c r="H76" s="27">
+      <c r="H76" s="37">
         <f>IF(OR(E76="",F76=""),0,E76*F76)</f>
         <v/>
       </c>
-      <c r="I76" s="27">
+      <c r="I76" s="37">
         <f>IF(D76="закупка",H76*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J76" s="27">
+      <c r="J76" s="37">
         <f>H76+I76</f>
         <v/>
       </c>
-      <c r="L76" s="23" t="n"/>
+      <c r="L76" s="9" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="106">
       <c r="B77" s="104" t="inlineStr">
@@ -5395,12 +5411,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C77" s="23" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>Транспорт оборудования на объект</t>
         </is>
       </c>
-      <c r="D77" s="23" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5408,27 +5424,27 @@
       <c r="E77" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F77" s="23" t="n">
+      <c r="F77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="23" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H77" s="27">
+      <c r="H77" s="37">
         <f>IF(OR(E77="",F77=""),0,E77*F77)</f>
         <v/>
       </c>
-      <c r="I77" s="27">
+      <c r="I77" s="37">
         <f>IF(D77="закупка",H77*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J77" s="27">
+      <c r="J77" s="37">
         <f>H77+I77</f>
         <v/>
       </c>
-      <c r="L77" s="23" t="n"/>
+      <c r="L77" s="9" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="106">
       <c r="B78" s="104" t="inlineStr">
@@ -5436,12 +5452,12 @@
           <t>Монтаж</t>
         </is>
       </c>
-      <c r="C78" s="23" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>Транспорт оборудования в цех</t>
         </is>
       </c>
-      <c r="D78" s="23" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>транспорт</t>
         </is>
@@ -5449,27 +5465,27 @@
       <c r="E78" s="102" t="n">
         <v>2000</v>
       </c>
-      <c r="F78" s="23" t="n">
+      <c r="F78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="23" t="inlineStr">
+      <c r="G78" s="9" t="inlineStr">
         <is>
           <t>рейс</t>
         </is>
       </c>
-      <c r="H78" s="27">
+      <c r="H78" s="37">
         <f>IF(OR(E78="",F78=""),0,E78*F78)</f>
         <v/>
       </c>
-      <c r="I78" s="27">
+      <c r="I78" s="37">
         <f>IF(D78="закупка",H78*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J78" s="27">
+      <c r="J78" s="37">
         <f>H78+I78</f>
         <v/>
       </c>
-      <c r="L78" s="23" t="n"/>
+      <c r="L78" s="9" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="106">
       <c r="B79" s="113" t="inlineStr">
@@ -5484,12 +5500,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C80" s="23" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>Абразивы</t>
         </is>
       </c>
-      <c r="D80" s="23" t="inlineStr">
+      <c r="D80" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5497,25 +5513,27 @@
       <c r="E80" s="102" t="n">
         <v>600</v>
       </c>
-      <c r="F80" s="23" t="n"/>
-      <c r="G80" s="23" t="inlineStr">
+      <c r="F80" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H80" s="27">
+      <c r="H80" s="37">
         <f>IF(OR(E80="",F80=""),0,E80*F80)</f>
         <v/>
       </c>
-      <c r="I80" s="27">
+      <c r="I80" s="37">
         <f>IF(D80="закупка",H80*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J80" s="27">
+      <c r="J80" s="37">
         <f>H80+I80</f>
         <v/>
       </c>
-      <c r="L80" s="23" t="n"/>
+      <c r="L80" s="9" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="106">
       <c r="B81" s="104" t="inlineStr">
@@ -5523,12 +5541,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C81" s="23" t="inlineStr">
+      <c r="C81" s="9" t="inlineStr">
         <is>
           <t>Кислород</t>
         </is>
       </c>
-      <c r="D81" s="23" t="inlineStr">
+      <c r="D81" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5536,27 +5554,27 @@
       <c r="E81" s="102" t="n">
         <v>330</v>
       </c>
-      <c r="F81" s="23" t="n">
+      <c r="F81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="23" t="inlineStr">
+      <c r="G81" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H81" s="27">
+      <c r="H81" s="37">
         <f>IF(OR(E81="",F81=""),0,E81*F81)</f>
         <v/>
       </c>
-      <c r="I81" s="27">
+      <c r="I81" s="37">
         <f>IF(D81="закупка",H81*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J81" s="27">
+      <c r="J81" s="37">
         <f>H81+I81</f>
         <v/>
       </c>
-      <c r="L81" s="23" t="inlineStr">
+      <c r="L81" s="9" t="inlineStr">
         <is>
           <t>ориентир: баллон / срок</t>
         </is>
@@ -5568,12 +5586,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C82" s="23" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>Углекислота</t>
         </is>
       </c>
-      <c r="D82" s="23" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5581,27 +5599,27 @@
       <c r="E82" s="102" t="n">
         <v>65</v>
       </c>
-      <c r="F82" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="23" t="inlineStr">
+      <c r="F82" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H82" s="27">
+      <c r="H82" s="37">
         <f>IF(OR(E82="",F82=""),0,E82*F82)</f>
         <v/>
       </c>
-      <c r="I82" s="27">
+      <c r="I82" s="37">
         <f>IF(D82="закупка",H82*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J82" s="27">
+      <c r="J82" s="37">
         <f>H82+I82</f>
         <v/>
       </c>
-      <c r="L82" s="23" t="n"/>
+      <c r="L82" s="9" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="106">
       <c r="B83" s="104" t="inlineStr">
@@ -5609,12 +5627,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C83" s="23" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>Пропан (газ)</t>
         </is>
       </c>
-      <c r="D83" s="23" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5622,25 +5640,27 @@
       <c r="E83" s="102" t="n">
         <v>690</v>
       </c>
-      <c r="F83" s="23" t="n"/>
-      <c r="G83" s="23" t="inlineStr">
+      <c r="F83" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H83" s="27">
+      <c r="H83" s="37">
         <f>IF(OR(E83="",F83=""),0,E83*F83)</f>
         <v/>
       </c>
-      <c r="I83" s="27">
+      <c r="I83" s="37">
         <f>IF(D83="закупка",H83*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J83" s="27">
+      <c r="J83" s="37">
         <f>H83+I83</f>
         <v/>
       </c>
-      <c r="L83" s="23" t="n"/>
+      <c r="L83" s="9" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="106">
       <c r="B84" s="104" t="inlineStr">
@@ -5648,12 +5668,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C84" s="23" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>Ковка (уголь)</t>
         </is>
       </c>
-      <c r="D84" s="23" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>закупка</t>
         </is>
@@ -5661,27 +5681,27 @@
       <c r="E84" s="102" t="n">
         <v>3100</v>
       </c>
-      <c r="F84" s="23" t="n">
+      <c r="F84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G84" s="23" t="inlineStr">
+      <c r="G84" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H84" s="27">
+      <c r="H84" s="37">
         <f>IF(OR(E84="",F84=""),0,E84*F84)</f>
         <v/>
       </c>
-      <c r="I84" s="27">
+      <c r="I84" s="37">
         <f>IF(D84="закупка",H84*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J84" s="27">
+      <c r="J84" s="37">
         <f>H84+I84</f>
         <v/>
       </c>
-      <c r="L84" s="23" t="n"/>
+      <c r="L84" s="9" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="106">
       <c r="B85" s="104" t="inlineStr">
@@ -5689,12 +5709,12 @@
           <t>Расходники/день</t>
         </is>
       </c>
-      <c r="C85" s="23" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
         <is>
           <t>Амортизация инструмента</t>
         </is>
       </c>
-      <c r="D85" s="23" t="inlineStr">
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>прочее</t>
         </is>
@@ -5702,67 +5722,69 @@
       <c r="E85" s="102" t="n">
         <v>740</v>
       </c>
-      <c r="F85" s="23" t="n"/>
-      <c r="G85" s="23" t="inlineStr">
+      <c r="F85" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
         <is>
           <t>день</t>
         </is>
       </c>
-      <c r="H85" s="27">
+      <c r="H85" s="37">
         <f>IF(OR(E85="",F85=""),0,E85*F85)</f>
         <v/>
       </c>
-      <c r="I85" s="27">
+      <c r="I85" s="37">
         <f>IF(D85="закупка",H85*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J85" s="27">
+      <c r="J85" s="37">
         <f>H85+I85</f>
         <v/>
       </c>
-      <c r="L85" s="23" t="n"/>
+      <c r="L85" s="9" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="106">
       <c r="B86" s="104" t="n"/>
-      <c r="C86" s="23" t="n"/>
-      <c r="D86" s="23" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
       <c r="E86" s="102" t="n"/>
-      <c r="F86" s="23" t="n"/>
-      <c r="G86" s="23" t="n"/>
-      <c r="H86" s="27">
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="37">
         <f>IF(OR(E86="",F86=""),0,E86*F86)</f>
         <v/>
       </c>
-      <c r="I86" s="27">
+      <c r="I86" s="37">
         <f>IF(D86="закупка",H86*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J86" s="27">
+      <c r="J86" s="37">
         <f>H86+I86</f>
         <v/>
       </c>
-      <c r="L86" s="23" t="n"/>
+      <c r="L86" s="9" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="106">
       <c r="B87" s="104" t="n"/>
-      <c r="C87" s="23" t="n"/>
-      <c r="D87" s="23" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
       <c r="E87" s="102" t="n"/>
-      <c r="F87" s="23" t="n"/>
-      <c r="G87" s="23" t="n"/>
-      <c r="H87" s="27">
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
+      <c r="H87" s="37">
         <f>IF(OR(E87="",F87=""),0,E87*F87)</f>
         <v/>
       </c>
-      <c r="I87" s="27">
+      <c r="I87" s="37">
         <f>IF(D87="закупка",H87*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J87" s="27">
+      <c r="J87" s="37">
         <f>H87+I87</f>
         <v/>
       </c>
-      <c r="L87" s="23" t="n"/>
+      <c r="L87" s="9" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="106">
       <c r="B88" s="114" t="inlineStr">
@@ -5777,40 +5799,40 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C89" s="23" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>Разработка проекта</t>
         </is>
       </c>
-      <c r="D89" s="23" t="inlineStr">
-        <is>
-          <t>труд</t>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E89" s="102" t="n">
         <v>1000</v>
       </c>
-      <c r="F89" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="23" t="inlineStr">
+      <c r="F89" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="H89" s="27">
+      <c r="H89" s="37">
         <f>IF(OR(E89="",F89=""),0,E89*F89)</f>
         <v/>
       </c>
-      <c r="I89" s="27">
+      <c r="I89" s="37">
         <f>IF(D89="закупка",H89*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J89" s="27">
+      <c r="J89" s="37">
         <f>H89+I89</f>
         <v/>
       </c>
-      <c r="L89" s="23" t="n"/>
+      <c r="L89" s="9" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="106">
       <c r="B90" s="104" t="inlineStr">
@@ -5818,40 +5840,40 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C90" s="23" t="inlineStr">
+      <c r="C90" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Виктор обрисовка под лазерную резку </t>
         </is>
       </c>
-      <c r="D90" s="23" t="inlineStr">
-        <is>
-          <t>услуга</t>
+      <c r="D90" s="9" t="inlineStr">
+        <is>
+          <t>закупка</t>
         </is>
       </c>
       <c r="E90" s="102" t="n">
-        <v>121</v>
-      </c>
-      <c r="F90" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="23" t="inlineStr">
+        <v>620</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
         <is>
           <t>час</t>
         </is>
       </c>
-      <c r="H90" s="27">
+      <c r="H90" s="37">
         <f>IF(OR(E90="",F90=""),0,E90*F90)</f>
         <v/>
       </c>
-      <c r="I90" s="27">
+      <c r="I90" s="37">
         <f>IF(D90="закупка",H90*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J90" s="27">
+      <c r="J90" s="37">
         <f>H90+I90</f>
         <v/>
       </c>
-      <c r="L90" s="23" t="n"/>
+      <c r="L90" s="9" t="n"/>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="106">
       <c r="B91" s="104" t="inlineStr">
@@ -5859,28 +5881,28 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C91" s="23" t="n"/>
-      <c r="D91" s="23" t="inlineStr">
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>услуга</t>
         </is>
       </c>
       <c r="E91" s="102" t="n"/>
-      <c r="F91" s="23" t="n"/>
-      <c r="G91" s="23" t="n"/>
-      <c r="H91" s="27">
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="37">
         <f>IF(OR(E91="",F91=""),0,E91*F91)</f>
         <v/>
       </c>
-      <c r="I91" s="27">
+      <c r="I91" s="37">
         <f>IF(D91="закупка",H91*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J91" s="27">
+      <c r="J91" s="37">
         <f>H91+I91</f>
         <v/>
       </c>
-      <c r="L91" s="23" t="n"/>
+      <c r="L91" s="9" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="106">
       <c r="B92" s="104" t="inlineStr">
@@ -5888,24 +5910,24 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C92" s="23" t="n"/>
-      <c r="D92" s="23" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
       <c r="E92" s="102" t="n"/>
-      <c r="F92" s="23" t="n"/>
-      <c r="G92" s="23" t="n"/>
-      <c r="H92" s="27">
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="37">
         <f>IF(OR(E92="",F92=""),0,E92*F92)</f>
         <v/>
       </c>
-      <c r="I92" s="27">
+      <c r="I92" s="37">
         <f>IF(D92="закупка",H92*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J92" s="27">
+      <c r="J92" s="37">
         <f>H92+I92</f>
         <v/>
       </c>
-      <c r="L92" s="23" t="n"/>
+      <c r="L92" s="9" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="106">
       <c r="B93" s="104" t="inlineStr">
@@ -5913,24 +5935,24 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C93" s="23" t="n"/>
-      <c r="D93" s="23" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
       <c r="E93" s="102" t="n"/>
-      <c r="F93" s="23" t="n"/>
-      <c r="G93" s="23" t="n"/>
-      <c r="H93" s="27">
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="37">
         <f>IF(OR(E93="",F93=""),0,E93*F93)</f>
         <v/>
       </c>
-      <c r="I93" s="27">
+      <c r="I93" s="37">
         <f>IF(D93="закупка",H93*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J93" s="27">
+      <c r="J93" s="37">
         <f>H93+I93</f>
         <v/>
       </c>
-      <c r="L93" s="23" t="n"/>
+      <c r="L93" s="9" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="106">
       <c r="B94" s="104" t="inlineStr">
@@ -5938,259 +5960,259 @@
           <t>Проектирование</t>
         </is>
       </c>
-      <c r="C94" s="23" t="n"/>
-      <c r="D94" s="23" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
       <c r="E94" s="102" t="n"/>
-      <c r="F94" s="23" t="n"/>
-      <c r="G94" s="23" t="n"/>
-      <c r="H94" s="27">
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="37">
         <f>IF(OR(E94="",F94=""),0,E94*F94)</f>
         <v/>
       </c>
-      <c r="I94" s="27">
+      <c r="I94" s="37">
         <f>IF(D94="закупка",H94*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J94" s="27">
+      <c r="J94" s="37">
         <f>H94+I94</f>
         <v/>
       </c>
-      <c r="L94" s="23" t="n"/>
+      <c r="L94" s="9" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="106">
       <c r="B95" s="104" t="n"/>
-      <c r="C95" s="23" t="n"/>
-      <c r="D95" s="23" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
       <c r="E95" s="102" t="n"/>
-      <c r="F95" s="23" t="n"/>
-      <c r="G95" s="23" t="n"/>
-      <c r="H95" s="27">
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="37">
         <f>IF(OR(E95="",F95=""),0,E95*F95)</f>
         <v/>
       </c>
-      <c r="I95" s="27">
+      <c r="I95" s="37">
         <f>IF(D95="закупка",H95*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J95" s="27">
+      <c r="J95" s="37">
         <f>H95+I95</f>
         <v/>
       </c>
-      <c r="L95" s="23" t="n"/>
+      <c r="L95" s="9" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="106">
       <c r="B96" s="104" t="n"/>
-      <c r="C96" s="23" t="n"/>
-      <c r="D96" s="23" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
       <c r="E96" s="102" t="n"/>
-      <c r="F96" s="23" t="n"/>
-      <c r="G96" s="23" t="n"/>
-      <c r="H96" s="27">
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="37">
         <f>IF(OR(E96="",F96=""),0,E96*F96)</f>
         <v/>
       </c>
-      <c r="I96" s="27">
+      <c r="I96" s="37">
         <f>IF(D96="закупка",H96*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J96" s="27">
+      <c r="J96" s="37">
         <f>H96+I96</f>
         <v/>
       </c>
-      <c r="L96" s="23" t="n"/>
+      <c r="L96" s="9" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="106">
       <c r="B97" s="104" t="n"/>
-      <c r="C97" s="23" t="n"/>
-      <c r="D97" s="23" t="n"/>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
       <c r="E97" s="102" t="n"/>
-      <c r="F97" s="23" t="n"/>
-      <c r="G97" s="23" t="n"/>
-      <c r="H97" s="27">
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="37">
         <f>IF(OR(E97="",F97=""),0,E97*F97)</f>
         <v/>
       </c>
-      <c r="I97" s="27">
+      <c r="I97" s="37">
         <f>IF(D97="закупка",H97*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J97" s="27">
+      <c r="J97" s="37">
         <f>H97+I97</f>
         <v/>
       </c>
-      <c r="L97" s="23" t="n"/>
+      <c r="L97" s="9" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="106">
       <c r="B98" s="104" t="n"/>
-      <c r="C98" s="23" t="n"/>
-      <c r="D98" s="23" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
       <c r="E98" s="102" t="n"/>
-      <c r="F98" s="23" t="n"/>
-      <c r="G98" s="23" t="n"/>
-      <c r="H98" s="27">
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="37">
         <f>IF(OR(E98="",F98=""),0,E98*F98)</f>
         <v/>
       </c>
-      <c r="I98" s="27">
+      <c r="I98" s="37">
         <f>IF(D98="закупка",H98*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J98" s="27">
+      <c r="J98" s="37">
         <f>H98+I98</f>
         <v/>
       </c>
-      <c r="L98" s="23" t="n"/>
+      <c r="L98" s="9" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="106">
       <c r="B99" s="104" t="n"/>
-      <c r="C99" s="23" t="n"/>
-      <c r="D99" s="23" t="n"/>
+      <c r="C99" s="9" t="n"/>
+      <c r="D99" s="9" t="n"/>
       <c r="E99" s="102" t="n"/>
-      <c r="F99" s="23" t="n"/>
-      <c r="G99" s="23" t="n"/>
-      <c r="H99" s="27">
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="9" t="n"/>
+      <c r="H99" s="37">
         <f>IF(OR(E99="",F99=""),0,E99*F99)</f>
         <v/>
       </c>
-      <c r="I99" s="27">
+      <c r="I99" s="37">
         <f>IF(D99="закупка",H99*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J99" s="27">
+      <c r="J99" s="37">
         <f>H99+I99</f>
         <v/>
       </c>
-      <c r="L99" s="23" t="n"/>
+      <c r="L99" s="9" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="106">
       <c r="B100" s="104" t="n"/>
-      <c r="C100" s="23" t="n"/>
-      <c r="D100" s="23" t="n"/>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
       <c r="E100" s="102" t="n"/>
-      <c r="F100" s="23" t="n"/>
-      <c r="G100" s="23" t="n"/>
-      <c r="H100" s="27">
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="37">
         <f>IF(OR(E100="",F100=""),0,E100*F100)</f>
         <v/>
       </c>
-      <c r="I100" s="27">
+      <c r="I100" s="37">
         <f>IF(D100="закупка",H100*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J100" s="27">
+      <c r="J100" s="37">
         <f>H100+I100</f>
         <v/>
       </c>
-      <c r="L100" s="23" t="n"/>
+      <c r="L100" s="9" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="106">
       <c r="B101" s="104" t="n"/>
-      <c r="C101" s="23" t="n"/>
-      <c r="D101" s="23" t="n"/>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="9" t="n"/>
       <c r="E101" s="102" t="n"/>
-      <c r="F101" s="23" t="n"/>
-      <c r="G101" s="23" t="n"/>
-      <c r="H101" s="27">
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
+      <c r="H101" s="37">
         <f>IF(OR(E101="",F101=""),0,E101*F101)</f>
         <v/>
       </c>
-      <c r="I101" s="27">
+      <c r="I101" s="37">
         <f>IF(D101="закупка",H101*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J101" s="27">
+      <c r="J101" s="37">
         <f>H101+I101</f>
         <v/>
       </c>
-      <c r="L101" s="23" t="n"/>
+      <c r="L101" s="9" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="106">
       <c r="B102" s="104" t="n"/>
-      <c r="C102" s="23" t="n"/>
-      <c r="D102" s="23" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
       <c r="E102" s="102" t="n"/>
-      <c r="F102" s="23" t="n"/>
-      <c r="G102" s="23" t="n"/>
-      <c r="H102" s="27">
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="37">
         <f>IF(OR(E102="",F102=""),0,E102*F102)</f>
         <v/>
       </c>
-      <c r="I102" s="27">
+      <c r="I102" s="37">
         <f>IF(D102="закупка",H102*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J102" s="27">
+      <c r="J102" s="37">
         <f>H102+I102</f>
         <v/>
       </c>
-      <c r="L102" s="23" t="n"/>
+      <c r="L102" s="9" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="106">
       <c r="B103" s="104" t="n"/>
-      <c r="C103" s="23" t="n"/>
-      <c r="D103" s="23" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
       <c r="E103" s="102" t="n"/>
-      <c r="F103" s="23" t="n"/>
-      <c r="G103" s="23" t="n"/>
-      <c r="H103" s="27">
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
+      <c r="H103" s="37">
         <f>IF(OR(E103="",F103=""),0,E103*F103)</f>
         <v/>
       </c>
-      <c r="I103" s="27">
+      <c r="I103" s="37">
         <f>IF(D103="закупка",H103*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J103" s="27">
+      <c r="J103" s="37">
         <f>H103+I103</f>
         <v/>
       </c>
-      <c r="L103" s="23" t="n"/>
+      <c r="L103" s="9" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="106">
       <c r="B104" s="104" t="n"/>
-      <c r="C104" s="23" t="n"/>
-      <c r="D104" s="23" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
       <c r="E104" s="102" t="n"/>
-      <c r="F104" s="23" t="n"/>
-      <c r="G104" s="23" t="n"/>
-      <c r="H104" s="27">
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="37">
         <f>IF(OR(E104="",F104=""),0,E104*F104)</f>
         <v/>
       </c>
-      <c r="I104" s="27">
+      <c r="I104" s="37">
         <f>IF(D104="закупка",H104*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J104" s="27">
+      <c r="J104" s="37">
         <f>H104+I104</f>
         <v/>
       </c>
-      <c r="L104" s="23" t="n"/>
+      <c r="L104" s="9" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="106">
       <c r="B105" s="104" t="n"/>
-      <c r="C105" s="23" t="n"/>
-      <c r="D105" s="23" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
       <c r="E105" s="102" t="n"/>
-      <c r="F105" s="23" t="n"/>
-      <c r="G105" s="23" t="n"/>
-      <c r="H105" s="27">
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="9" t="n"/>
+      <c r="H105" s="37">
         <f>IF(OR(E105="",F105=""),0,E105*F105)</f>
         <v/>
       </c>
-      <c r="I105" s="27">
+      <c r="I105" s="37">
         <f>IF(D105="закупка",H105*'Параметры'!$C$6,0)</f>
         <v/>
       </c>
-      <c r="J105" s="27">
+      <c r="J105" s="37">
         <f>H105+I105</f>
         <v/>
       </c>
-      <c r="L105" s="23" t="n"/>
+      <c r="L105" s="9" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="106"/>
     <row r="107" ht="15.75" customHeight="1" s="106">
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Пустые строки — для своих позиций. Тип «закупка» включает наценку менеджера автоматически.</t>
         </is>
@@ -7147,7 +7169,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Цена поставщика = за 1 шт (штанга 6 м). Кол-во — сколько штанг в заказ. Вес 6м — справочно. Наценка менеджера: себестоимость × % из Параметров.</t>
         </is>
@@ -7168,65 +7190,65 @@
       <c r="I4" s="108" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Прокат</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Сечение</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Цена поставщика, ₽/шт (6м)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>С наценкой менеджера</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>Вес 6м, кг</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Квадрат</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>10х10</t>
         </is>
       </c>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7234,35 +7256,35 @@
       <c r="F6" s="102" t="n">
         <v>428.3</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="12">
         <f>H6*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="12">
         <f>IF(OR(D6="",F6=""),0,D6*F6)</f>
         <v/>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="12">
         <f>H6*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J6" s="36" t="n">
+      <c r="J6" s="13" t="n">
         <v>5.1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Квадрат</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>12х12</t>
         </is>
       </c>
-      <c r="D7" s="23" t="n"/>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7270,35 +7292,37 @@
       <c r="F7" s="102" t="n">
         <v>596.26</v>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="12">
         <f>H7*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H7" s="34">
+      <c r="H7" s="12">
         <f>IF(OR(D7="",F7=""),0,D7*F7)</f>
         <v/>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="12">
         <f>H7*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J7" s="36" t="n">
+      <c r="J7" s="13" t="n">
         <v>7.1</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Квадрат</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>14х14</t>
         </is>
       </c>
-      <c r="D8" s="23" t="n"/>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7306,35 +7330,35 @@
       <c r="F8" s="102" t="n">
         <v>797.8099999999999</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="12">
         <f>H8*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="12">
         <f>IF(OR(D8="",F8=""),0,D8*F8)</f>
         <v/>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="12">
         <f>H8*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J8" s="36" t="n">
+      <c r="J8" s="13" t="n">
         <v>9.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Квадрат</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>16х16</t>
         </is>
       </c>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7342,35 +7366,35 @@
       <c r="F9" s="102" t="n">
         <v>1058.15</v>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="12">
         <f>H9*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="12">
         <f>IF(OR(D9="",F9=""),0,D9*F9)</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="12">
         <f>H9*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J9" s="36" t="n">
+      <c r="J9" s="13" t="n">
         <v>12.6</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>15х15х1.5</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7378,35 +7402,37 @@
       <c r="F10" s="102" t="n">
         <v>383.8</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="12">
         <f>H10*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="12">
         <f>IF(OR(D10="",F10=""),0,D10*F10)</f>
         <v/>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="12">
         <f>H10*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J10" s="36" t="n">
+      <c r="J10" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>20х20х1.5</t>
         </is>
       </c>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7414,35 +7440,35 @@
       <c r="F11" s="102" t="n">
         <v>575.7</v>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="12">
         <f>H11*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H11" s="34">
+      <c r="H11" s="12">
         <f>IF(OR(D11="",F11=""),0,D11*F11)</f>
         <v/>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="12">
         <f>H11*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J11" s="36" t="n">
+      <c r="J11" s="13" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>20х20х2.0</t>
         </is>
       </c>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7450,35 +7476,37 @@
       <c r="F12" s="102" t="n">
         <v>586.53</v>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="12">
         <f>H12*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="12">
         <f>IF(OR(D12="",F12=""),0,D12*F12)</f>
         <v/>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="12">
         <f>H12*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J12" s="36" t="n">
+      <c r="J12" s="13" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>30х30х2.0</t>
         </is>
       </c>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7486,35 +7514,35 @@
       <c r="F13" s="102" t="n">
         <v>921.6900000000001</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="12">
         <f>H13*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="12">
         <f>IF(OR(D13="",F13=""),0,D13*F13)</f>
         <v/>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="12">
         <f>H13*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J13" s="36" t="n">
+      <c r="J13" s="13" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>40х40х1.5</t>
         </is>
       </c>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7522,35 +7550,35 @@
       <c r="F14" s="102" t="n">
         <v>1151.4</v>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="12">
         <f>H14*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H14" s="34">
+      <c r="H14" s="12">
         <f>IF(OR(D14="",F14=""),0,D14*F14)</f>
         <v/>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="12">
         <f>H14*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J14" s="36" t="n">
+      <c r="J14" s="13" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Труба квадрат.</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>40х40х2.0</t>
         </is>
       </c>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7558,35 +7586,35 @@
       <c r="F15" s="102" t="n">
         <v>1256.85</v>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="12">
         <f>H15*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="12">
         <f>IF(OR(D15="",F15=""),0,D15*F15)</f>
         <v/>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="12">
         <f>H15*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J15" s="36" t="n">
+      <c r="J15" s="13" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Труба прямоуг.</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>40х20х1.5</t>
         </is>
       </c>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7594,35 +7622,35 @@
       <c r="F16" s="102" t="n">
         <v>863.55</v>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="12">
         <f>H16*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="12">
         <f>IF(OR(D16="",F16=""),0,D16*F16)</f>
         <v/>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="12">
         <f>H16*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J16" s="36" t="n">
+      <c r="J16" s="13" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Труба прямоуг.</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>40х20х2.0</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7630,35 +7658,35 @@
       <c r="F17" s="102" t="n">
         <v>921.6900000000001</v>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="12">
         <f>H17*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="12">
         <f>IF(OR(D17="",F17=""),0,D17*F17)</f>
         <v/>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="12">
         <f>H17*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J17" s="36" t="n">
+      <c r="J17" s="13" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Труба прямоуг.</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>50х25х1.5</t>
         </is>
       </c>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7666,35 +7694,35 @@
       <c r="F18" s="102" t="n">
         <v>1151.4</v>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="12">
         <f>H18*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="12">
         <f>IF(OR(D18="",F18=""),0,D18*F18)</f>
         <v/>
       </c>
-      <c r="I18" s="34">
+      <c r="I18" s="12">
         <f>H18*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J18" s="36" t="n">
+      <c r="J18" s="13" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Труба прямоуг.</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>50х25х2.0</t>
         </is>
       </c>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7702,35 +7730,35 @@
       <c r="F19" s="102" t="n">
         <v>1173.06</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="12">
         <f>H19*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="12">
         <f>IF(OR(D19="",F19=""),0,D19*F19)</f>
         <v/>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="12">
         <f>H19*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J19" s="36" t="n">
+      <c r="J19" s="13" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>20х4 мм</t>
         </is>
       </c>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7738,35 +7766,35 @@
       <c r="F20" s="102" t="n">
         <v>397.04</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="12">
         <f>H20*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="12">
         <f>IF(OR(D20="",F20=""),0,D20*F20)</f>
         <v/>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="12">
         <f>H20*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J20" s="36" t="n">
+      <c r="J20" s="13" t="n">
         <v>4.1</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="106">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>25х4 мм</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7774,35 +7802,35 @@
       <c r="F21" s="102" t="n">
         <v>493.88</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="12">
         <f>H21*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="12">
         <f>IF(OR(D21="",F21=""),0,D21*F21)</f>
         <v/>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="12">
         <f>H21*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J21" s="36" t="n">
+      <c r="J21" s="13" t="n">
         <v>5.1</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="106">
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>30х4 мм</t>
         </is>
       </c>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7810,35 +7838,35 @@
       <c r="F22" s="102" t="n">
         <v>557.85</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="12">
         <f>H22*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="12">
         <f>IF(OR(D22="",F22=""),0,D22*F22)</f>
         <v/>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="12">
         <f>H22*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J22" s="36" t="n">
+      <c r="J22" s="13" t="n">
         <v>6.1</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="106">
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>40х4 мм</t>
         </is>
       </c>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7846,35 +7874,37 @@
       <c r="F23" s="102" t="n">
         <v>731.6</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="12">
         <f>H23*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="12">
         <f>IF(OR(D23="",F23=""),0,D23*F23)</f>
         <v/>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="12">
         <f>H23*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J23" s="36" t="n">
+      <c r="J23" s="13" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="106">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>50х4 мм</t>
         </is>
       </c>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="D24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7882,35 +7912,35 @@
       <c r="F24" s="102" t="n">
         <v>914.5</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="12">
         <f>H24*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="12">
         <f>IF(OR(D24="",F24=""),0,D24*F24)</f>
         <v/>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="12">
         <f>H24*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J24" s="36" t="n">
+      <c r="J24" s="13" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="106">
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>100х10 мм</t>
         </is>
       </c>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7918,35 +7948,35 @@
       <c r="F25" s="102" t="n">
         <v>4687.83</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="12">
         <f>H25*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="12">
         <f>IF(OR(D25="",F25=""),0,D25*F25)</f>
         <v/>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="12">
         <f>H25*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J25" s="36" t="n">
+      <c r="J25" s="13" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="106">
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Труба в/г</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>15х2.8</t>
         </is>
       </c>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7954,35 +7984,35 @@
       <c r="F26" s="102" t="n">
         <v>641.52</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="12">
         <f>H26*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="12">
         <f>IF(OR(D26="",F26=""),0,D26*F26)</f>
         <v/>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="12">
         <f>H26*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J26" s="36" t="n">
+      <c r="J26" s="13" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="106">
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Труба в/г</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>20х2.8</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -7990,35 +8020,35 @@
       <c r="F27" s="102" t="n">
         <v>882.09</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="12">
         <f>H27*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="12">
         <f>IF(OR(D27="",F27=""),0,D27*F27)</f>
         <v/>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="12">
         <f>H27*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J27" s="36" t="n">
+      <c r="J27" s="13" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Труба в/г</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>25х3.2</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8026,35 +8056,35 @@
       <c r="F28" s="102" t="n">
         <v>1268.8</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="12">
         <f>H28*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="12">
         <f>IF(OR(D28="",F28=""),0,D28*F28)</f>
         <v/>
       </c>
-      <c r="I28" s="34">
+      <c r="I28" s="12">
         <f>H28*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J28" s="36" t="n">
+      <c r="J28" s="13" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="106">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Труба в/г</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>32х3.2</t>
         </is>
       </c>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8062,35 +8092,35 @@
       <c r="F29" s="102" t="n">
         <v>1586</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="12">
         <f>H29*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="12">
         <f>IF(OR(D29="",F29=""),0,D29*F29)</f>
         <v/>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="12">
         <f>H29*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J29" s="36" t="n">
+      <c r="J29" s="13" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="106">
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Труба в/г</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>40х3.5</t>
         </is>
       </c>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="23" t="inlineStr">
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8098,35 +8128,35 @@
       <c r="F30" s="102" t="n">
         <v>1982.5</v>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="12">
         <f>H30*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="12">
         <f>IF(OR(D30="",F30=""),0,D30*F30)</f>
         <v/>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="12">
         <f>H30*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J30" s="36" t="n">
+      <c r="J30" s="13" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="106">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Ø6</t>
         </is>
       </c>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8134,35 +8164,35 @@
       <c r="F31" s="102" t="n">
         <v>156.24</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="12">
         <f>H31*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="12">
         <f>IF(OR(D31="",F31=""),0,D31*F31)</f>
         <v/>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="12">
         <f>H31*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J31" s="36" t="n">
+      <c r="J31" s="13" t="n">
         <v>1.6</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="106">
-      <c r="B32" s="23" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Ø8</t>
         </is>
       </c>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="23" t="inlineStr">
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8170,35 +8200,35 @@
       <c r="F32" s="102" t="n">
         <v>270.87</v>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="12">
         <f>H32*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H32" s="34">
+      <c r="H32" s="12">
         <f>IF(OR(D32="",F32=""),0,D32*F32)</f>
         <v/>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="12">
         <f>H32*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J32" s="36" t="n">
+      <c r="J32" s="13" t="n">
         <v>2.8</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="106">
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Ø10</t>
         </is>
       </c>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="23" t="inlineStr">
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8206,35 +8236,35 @@
       <c r="F33" s="102" t="n">
         <v>387.8</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="12">
         <f>H33*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="12">
         <f>IF(OR(D33="",F33=""),0,D33*F33)</f>
         <v/>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="12">
         <f>H33*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J33" s="36" t="n">
+      <c r="J33" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="106">
-      <c r="B34" s="23" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C34" s="23" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Ø12</t>
         </is>
       </c>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="23" t="inlineStr">
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8242,35 +8272,35 @@
       <c r="F34" s="102" t="n">
         <v>581.7</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="12">
         <f>H34*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="12">
         <f>IF(OR(D34="",F34=""),0,D34*F34)</f>
         <v/>
       </c>
-      <c r="I34" s="34">
+      <c r="I34" s="12">
         <f>H34*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J34" s="36" t="n">
+      <c r="J34" s="13" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="106">
-      <c r="B35" s="23" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C35" s="23" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Ø14</t>
         </is>
       </c>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="23" t="inlineStr">
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8278,35 +8308,35 @@
       <c r="F35" s="102" t="n">
         <v>1352.55</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="12">
         <f>H35*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="12">
         <f>IF(OR(D35="",F35=""),0,D35*F35)</f>
         <v/>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="12">
         <f>H35*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J35" s="36" t="n">
+      <c r="J35" s="13" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="106">
-      <c r="B36" s="23" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Прокат круглый</t>
         </is>
       </c>
-      <c r="C36" s="23" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Ø16</t>
         </is>
       </c>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="23" t="inlineStr">
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8314,19 +8344,19 @@
       <c r="F36" s="102" t="n">
         <v>901.7</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="12">
         <f>H36*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="12">
         <f>IF(OR(D36="",F36=""),0,D36*F36)</f>
         <v/>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="12">
         <f>H36*'Параметры'!$C$6</f>
         <v/>
       </c>
-      <c r="J36" s="36" t="n">
+      <c r="J36" s="13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8341,15 +8371,15 @@
           <t>Прокат — себестоимость:</t>
         </is>
       </c>
-      <c r="G37" s="18">
+      <c r="G37" s="23">
         <f>SUM(G6:G36)</f>
         <v/>
       </c>
-      <c r="H37" s="18">
+      <c r="H37" s="23">
         <f>SUM(H6:H36)</f>
         <v/>
       </c>
-      <c r="I37" s="18">
+      <c r="I37" s="23">
         <f>SUM(I6:I36)</f>
         <v/>
       </c>
@@ -8371,81 +8401,85 @@
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106"/>
     <row r="41" ht="15.75" customHeight="1" s="106">
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Сечение / описание</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>Цена поставщика</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>С наценкой менеджера</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="106">
-      <c r="B42" s="23" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n">
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Краснознаменск </t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="F42" s="102" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G42" s="12">
+        <f>H42*(1+'Параметры'!$C$6)</f>
+        <v/>
+      </c>
+      <c r="H42" s="12">
+        <f>IF(OR(D42="",F42=""),0,D42*F42)</f>
+        <v/>
+      </c>
+      <c r="I42" s="12">
+        <f>H42*'Параметры'!$C$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="106">
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="F42" s="102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="34">
-        <f>H42*(1+'Параметры'!$C$6)</f>
-        <v/>
-      </c>
-      <c r="H42" s="34">
-        <f>IF(OR(D42="",F42=""),0,D42*F42)</f>
-        <v/>
-      </c>
-      <c r="I42" s="34">
-        <f>H42*'Параметры'!$C$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="106">
-      <c r="B43" s="23" t="n"/>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8453,26 +8487,26 @@
       <c r="F43" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="12">
         <f>H43*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H43" s="34">
+      <c r="H43" s="12">
         <f>IF(OR(D43="",F43=""),0,D43*F43)</f>
         <v/>
       </c>
-      <c r="I43" s="34">
+      <c r="I43" s="12">
         <f>H43*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="106">
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n">
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="23" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8480,26 +8514,26 @@
       <c r="F44" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="12">
         <f>H44*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="12">
         <f>IF(OR(D44="",F44=""),0,D44*F44)</f>
         <v/>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="12">
         <f>H44*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="106">
-      <c r="B45" s="23" t="n"/>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="23" t="n">
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="23" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8507,26 +8541,26 @@
       <c r="F45" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="12">
         <f>H45*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="12">
         <f>IF(OR(D45="",F45=""),0,D45*F45)</f>
         <v/>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="12">
         <f>H45*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="106">
-      <c r="B46" s="23" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="23" t="n">
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="23" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8534,26 +8568,26 @@
       <c r="F46" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="12">
         <f>H46*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H46" s="34">
+      <c r="H46" s="12">
         <f>IF(OR(D46="",F46=""),0,D46*F46)</f>
         <v/>
       </c>
-      <c r="I46" s="34">
+      <c r="I46" s="12">
         <f>H46*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="106">
-      <c r="B47" s="23" t="n"/>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="23" t="n">
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="23" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8561,26 +8595,26 @@
       <c r="F47" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="12">
         <f>H47*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="12">
         <f>IF(OR(D47="",F47=""),0,D47*F47)</f>
         <v/>
       </c>
-      <c r="I47" s="34">
+      <c r="I47" s="12">
         <f>H47*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="106">
-      <c r="B48" s="23" t="n"/>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="23" t="n">
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="23" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8588,26 +8622,26 @@
       <c r="F48" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="12">
         <f>H48*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="12">
         <f>IF(OR(D48="",F48=""),0,D48*F48)</f>
         <v/>
       </c>
-      <c r="I48" s="34">
+      <c r="I48" s="12">
         <f>H48*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="106">
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n">
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="23" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8615,26 +8649,26 @@
       <c r="F49" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="12">
         <f>H49*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H49" s="34">
+      <c r="H49" s="12">
         <f>IF(OR(D49="",F49=""),0,D49*F49)</f>
         <v/>
       </c>
-      <c r="I49" s="34">
+      <c r="I49" s="12">
         <f>H49*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="106">
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n">
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="23" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8642,26 +8676,26 @@
       <c r="F50" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="12">
         <f>H50*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="12">
         <f>IF(OR(D50="",F50=""),0,D50*F50)</f>
         <v/>
       </c>
-      <c r="I50" s="34">
+      <c r="I50" s="12">
         <f>H50*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="106">
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n">
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="23" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8669,34 +8703,34 @@
       <c r="F51" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="12">
         <f>H51*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="12">
         <f>IF(OR(D51="",F51=""),0,D51*F51)</f>
         <v/>
       </c>
-      <c r="I51" s="34">
+      <c r="I51" s="12">
         <f>H51*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="106">
-      <c r="F52" s="99" t="inlineStr">
+      <c r="F52" s="98" t="inlineStr">
         <is>
           <t>ПЛАЗМА / ЛАЗЕР — себестоимость:</t>
         </is>
       </c>
-      <c r="G52" s="18">
+      <c r="G52" s="23">
         <f>SUM(G42:G51)</f>
         <v/>
       </c>
-      <c r="H52" s="18">
+      <c r="H52" s="23">
         <f>SUM(H42:H51)</f>
         <v/>
       </c>
-      <c r="I52" s="18">
+      <c r="I52" s="23">
         <f>SUM(I42:I51)</f>
         <v/>
       </c>
@@ -8718,85 +8752,87 @@
     </row>
     <row r="55" ht="15.75" customHeight="1" s="106"/>
     <row r="56" ht="15.75" customHeight="1" s="106">
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Элемент / артикул</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Сечение</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Цена поставщика</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>С наценкой менеджера</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="106">
-      <c r="B57" s="23" t="inlineStr">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>Пики</t>
         </is>
       </c>
-      <c r="C57" s="23" t="n"/>
-      <c r="D57" s="23" t="n"/>
-      <c r="E57" s="23" t="inlineStr">
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
       <c r="F57" s="102" t="n">
-        <v>3200</v>
-      </c>
-      <c r="G57" s="34">
+        <v>1000000</v>
+      </c>
+      <c r="G57" s="12">
         <f>H57*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="12">
         <f>IF(OR(D57="",F57=""),0,D57*F57)</f>
         <v/>
       </c>
-      <c r="I57" s="34">
+      <c r="I57" s="12">
         <f>H57*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="106">
-      <c r="B58" s="23" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>Полоса</t>
         </is>
       </c>
-      <c r="C58" s="23" t="n"/>
-      <c r="D58" s="23" t="n"/>
-      <c r="E58" s="23" t="inlineStr">
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8804,28 +8840,28 @@
       <c r="F58" s="102" t="n">
         <v>10340</v>
       </c>
-      <c r="G58" s="34">
+      <c r="G58" s="12">
         <f>H58*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H58" s="34">
+      <c r="H58" s="12">
         <f>IF(OR(D58="",F58=""),0,D58*F58)</f>
         <v/>
       </c>
-      <c r="I58" s="34">
+      <c r="I58" s="12">
         <f>H58*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="106">
-      <c r="B59" s="23" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>шар</t>
         </is>
       </c>
-      <c r="C59" s="23" t="n"/>
-      <c r="D59" s="23" t="n"/>
-      <c r="E59" s="23" t="inlineStr">
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8833,24 +8869,24 @@
       <c r="F59" s="102" t="n">
         <v>1050</v>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="12">
         <f>H59*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="12">
         <f>IF(OR(D59="",F59=""),0,D59*F59)</f>
         <v/>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="12">
         <f>H59*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="106">
-      <c r="B60" s="23" t="n"/>
-      <c r="C60" s="23" t="n"/>
-      <c r="D60" s="23" t="n"/>
-      <c r="E60" s="23" t="inlineStr">
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8858,24 +8894,24 @@
       <c r="F60" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="12">
         <f>H60*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="12">
         <f>IF(OR(D60="",F60=""),0,D60*F60)</f>
         <v/>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="12">
         <f>H60*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="106">
-      <c r="B61" s="23" t="n"/>
-      <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
-      <c r="E61" s="23" t="inlineStr">
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8883,26 +8919,26 @@
       <c r="F61" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="34">
+      <c r="G61" s="12">
         <f>H61*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H61" s="34">
+      <c r="H61" s="12">
         <f>IF(OR(D61="",F61=""),0,D61*F61)</f>
         <v/>
       </c>
-      <c r="I61" s="34">
+      <c r="I61" s="12">
         <f>H61*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="106">
-      <c r="B62" s="23" t="n"/>
-      <c r="C62" s="23" t="n"/>
-      <c r="D62" s="23" t="n">
+      <c r="B62" s="9" t="n"/>
+      <c r="C62" s="9" t="n"/>
+      <c r="D62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="23" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8910,26 +8946,26 @@
       <c r="F62" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="12">
         <f>H62*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="12">
         <f>IF(OR(D62="",F62=""),0,D62*F62)</f>
         <v/>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="12">
         <f>H62*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="106">
-      <c r="B63" s="23" t="n"/>
-      <c r="C63" s="23" t="n"/>
-      <c r="D63" s="23" t="n">
+      <c r="B63" s="9" t="n"/>
+      <c r="C63" s="9" t="n"/>
+      <c r="D63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="23" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8937,26 +8973,26 @@
       <c r="F63" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="12">
         <f>H63*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H63" s="34">
+      <c r="H63" s="12">
         <f>IF(OR(D63="",F63=""),0,D63*F63)</f>
         <v/>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="12">
         <f>H63*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="106">
-      <c r="B64" s="23" t="n"/>
-      <c r="C64" s="23" t="n"/>
-      <c r="D64" s="23" t="n">
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="23" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8964,26 +9000,26 @@
       <c r="F64" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="34">
+      <c r="G64" s="12">
         <f>H64*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H64" s="34">
+      <c r="H64" s="12">
         <f>IF(OR(D64="",F64=""),0,D64*F64)</f>
         <v/>
       </c>
-      <c r="I64" s="34">
+      <c r="I64" s="12">
         <f>H64*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="106">
-      <c r="B65" s="23" t="n"/>
-      <c r="C65" s="23" t="n"/>
-      <c r="D65" s="23" t="n">
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="23" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -8991,26 +9027,26 @@
       <c r="F65" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="12">
         <f>H65*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H65" s="34">
+      <c r="H65" s="12">
         <f>IF(OR(D65="",F65=""),0,D65*F65)</f>
         <v/>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="12">
         <f>H65*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="106">
-      <c r="B66" s="23" t="n"/>
-      <c r="C66" s="23" t="n"/>
-      <c r="D66" s="23" t="n">
+      <c r="B66" s="9" t="n"/>
+      <c r="C66" s="9" t="n"/>
+      <c r="D66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="23" t="inlineStr">
+      <c r="E66" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9018,34 +9054,34 @@
       <c r="F66" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="12">
         <f>H66*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H66" s="34">
+      <c r="H66" s="12">
         <f>IF(OR(D66="",F66=""),0,D66*F66)</f>
         <v/>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="12">
         <f>H66*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="106">
-      <c r="F67" s="99" t="inlineStr">
+      <c r="F67" s="98" t="inlineStr">
         <is>
           <t>КОВАНЫЕ ЭЛЕМЕНТЫ / СПЕЦ. ПРОКАТ — себестоимость:</t>
         </is>
       </c>
-      <c r="G67" s="18">
+      <c r="G67" s="23">
         <f>SUM(G57:G66)</f>
         <v/>
       </c>
-      <c r="H67" s="18">
+      <c r="H67" s="23">
         <f>SUM(H57:H66)</f>
         <v/>
       </c>
-      <c r="I67" s="18">
+      <c r="I67" s="23">
         <f>SUM(I57:I66)</f>
         <v/>
       </c>
@@ -9067,54 +9103,54 @@
     </row>
     <row r="70" ht="15.75" customHeight="1" s="106"/>
     <row r="71" ht="15.75" customHeight="1" s="106">
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Позиция</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>Сечение / описание</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E71" s="5" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="F71" s="5" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>Цена поставщика</t>
         </is>
       </c>
-      <c r="G71" s="5" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>С наценкой менеджера</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="106">
-      <c r="B72" s="23" t="n"/>
-      <c r="C72" s="23" t="n"/>
-      <c r="D72" s="23" t="n">
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="23" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9122,26 +9158,26 @@
       <c r="F72" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="34">
+      <c r="G72" s="12">
         <f>H72*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H72" s="34">
+      <c r="H72" s="12">
         <f>IF(OR(D72="",F72=""),0,D72*F72)</f>
         <v/>
       </c>
-      <c r="I72" s="34">
+      <c r="I72" s="12">
         <f>H72*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="106">
-      <c r="B73" s="23" t="n"/>
-      <c r="C73" s="23" t="n"/>
-      <c r="D73" s="23" t="n">
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="23" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9149,26 +9185,26 @@
       <c r="F73" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="34">
+      <c r="G73" s="12">
         <f>H73*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H73" s="34">
+      <c r="H73" s="12">
         <f>IF(OR(D73="",F73=""),0,D73*F73)</f>
         <v/>
       </c>
-      <c r="I73" s="34">
+      <c r="I73" s="12">
         <f>H73*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="106">
-      <c r="B74" s="23" t="n"/>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n">
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="23" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9176,26 +9212,26 @@
       <c r="F74" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="34">
+      <c r="G74" s="12">
         <f>H74*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H74" s="34">
+      <c r="H74" s="12">
         <f>IF(OR(D74="",F74=""),0,D74*F74)</f>
         <v/>
       </c>
-      <c r="I74" s="34">
+      <c r="I74" s="12">
         <f>H74*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="106">
-      <c r="B75" s="23" t="n"/>
-      <c r="C75" s="23" t="n"/>
-      <c r="D75" s="23" t="n">
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="23" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9203,26 +9239,26 @@
       <c r="F75" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="34">
+      <c r="G75" s="12">
         <f>H75*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H75" s="34">
+      <c r="H75" s="12">
         <f>IF(OR(D75="",F75=""),0,D75*F75)</f>
         <v/>
       </c>
-      <c r="I75" s="34">
+      <c r="I75" s="12">
         <f>H75*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="106">
-      <c r="B76" s="23" t="n"/>
-      <c r="C76" s="23" t="n"/>
-      <c r="D76" s="23" t="n">
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="23" t="inlineStr">
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9230,26 +9266,26 @@
       <c r="F76" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="34">
+      <c r="G76" s="12">
         <f>H76*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H76" s="34">
+      <c r="H76" s="12">
         <f>IF(OR(D76="",F76=""),0,D76*F76)</f>
         <v/>
       </c>
-      <c r="I76" s="34">
+      <c r="I76" s="12">
         <f>H76*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="106">
-      <c r="B77" s="23" t="n"/>
-      <c r="C77" s="23" t="n"/>
-      <c r="D77" s="23" t="n">
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="23" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9257,26 +9293,26 @@
       <c r="F77" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="34">
+      <c r="G77" s="12">
         <f>H77*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H77" s="34">
+      <c r="H77" s="12">
         <f>IF(OR(D77="",F77=""),0,D77*F77)</f>
         <v/>
       </c>
-      <c r="I77" s="34">
+      <c r="I77" s="12">
         <f>H77*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="106">
-      <c r="B78" s="23" t="n"/>
-      <c r="C78" s="23" t="n"/>
-      <c r="D78" s="23" t="n">
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="23" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9284,26 +9320,26 @@
       <c r="F78" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="34">
+      <c r="G78" s="12">
         <f>H78*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H78" s="34">
+      <c r="H78" s="12">
         <f>IF(OR(D78="",F78=""),0,D78*F78)</f>
         <v/>
       </c>
-      <c r="I78" s="34">
+      <c r="I78" s="12">
         <f>H78*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="106">
-      <c r="B79" s="23" t="n"/>
-      <c r="C79" s="23" t="n"/>
-      <c r="D79" s="23" t="n">
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="23" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9311,26 +9347,26 @@
       <c r="F79" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="34">
+      <c r="G79" s="12">
         <f>H79*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H79" s="34">
+      <c r="H79" s="12">
         <f>IF(OR(D79="",F79=""),0,D79*F79)</f>
         <v/>
       </c>
-      <c r="I79" s="34">
+      <c r="I79" s="12">
         <f>H79*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="106">
-      <c r="B80" s="23" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n">
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="23" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9338,26 +9374,26 @@
       <c r="F80" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="34">
+      <c r="G80" s="12">
         <f>H80*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H80" s="34">
+      <c r="H80" s="12">
         <f>IF(OR(D80="",F80=""),0,D80*F80)</f>
         <v/>
       </c>
-      <c r="I80" s="34">
+      <c r="I80" s="12">
         <f>H80*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="106">
-      <c r="B81" s="23" t="n"/>
-      <c r="C81" s="23" t="n"/>
-      <c r="D81" s="23" t="n">
+      <c r="B81" s="9" t="n"/>
+      <c r="C81" s="9" t="n"/>
+      <c r="D81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="23" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9365,34 +9401,34 @@
       <c r="F81" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="34">
+      <c r="G81" s="12">
         <f>H81*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H81" s="34">
+      <c r="H81" s="12">
         <f>IF(OR(D81="",F81=""),0,D81*F81)</f>
         <v/>
       </c>
-      <c r="I81" s="34">
+      <c r="I81" s="12">
         <f>H81*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="106">
-      <c r="F82" s="99" t="inlineStr">
+      <c r="F82" s="98" t="inlineStr">
         <is>
           <t>ТОКАРНЫЕ РАБОТЫ — себестоимость:</t>
         </is>
       </c>
-      <c r="G82" s="18">
+      <c r="G82" s="23">
         <f>SUM(G72:G81)</f>
         <v/>
       </c>
-      <c r="H82" s="18">
+      <c r="H82" s="23">
         <f>SUM(H72:H81)</f>
         <v/>
       </c>
-      <c r="I82" s="18">
+      <c r="I82" s="23">
         <f>SUM(I72:I81)</f>
         <v/>
       </c>
@@ -9414,56 +9450,56 @@
     </row>
     <row r="85" ht="15.75" customHeight="1" s="106"/>
     <row r="86" ht="15.75" customHeight="1" s="106">
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Комплектующая</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Описание / артикул</t>
         </is>
       </c>
-      <c r="D86" s="5" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Ед.</t>
         </is>
       </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>Цена поставщика</t>
         </is>
       </c>
-      <c r="G86" s="5" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>С наценкой менеджера</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Себестоимость</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
         <is>
           <t>Наценка менеджера</t>
         </is>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="106">
-      <c r="B87" s="23" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>Петли</t>
         </is>
       </c>
-      <c r="C87" s="23" t="n"/>
-      <c r="D87" s="23" t="n"/>
-      <c r="E87" s="23" t="inlineStr">
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9471,28 +9507,28 @@
       <c r="F87" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="34">
+      <c r="G87" s="12">
         <f>H87*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H87" s="34">
+      <c r="H87" s="12">
         <f>IF(OR(D87="",F87=""),0,D87*F87)</f>
         <v/>
       </c>
-      <c r="I87" s="34">
+      <c r="I87" s="12">
         <f>H87*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="106">
-      <c r="B88" s="23" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
         <is>
           <t>ЗАмок</t>
         </is>
       </c>
-      <c r="C88" s="23" t="n"/>
-      <c r="D88" s="23" t="n"/>
-      <c r="E88" s="23" t="inlineStr">
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9500,24 +9536,24 @@
       <c r="F88" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="34">
+      <c r="G88" s="12">
         <f>H88*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H88" s="34">
+      <c r="H88" s="12">
         <f>IF(OR(D88="",F88=""),0,D88*F88)</f>
         <v/>
       </c>
-      <c r="I88" s="34">
+      <c r="I88" s="12">
         <f>H88*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="106">
-      <c r="B89" s="23" t="n"/>
-      <c r="C89" s="23" t="n"/>
-      <c r="D89" s="23" t="n"/>
-      <c r="E89" s="23" t="inlineStr">
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9525,26 +9561,26 @@
       <c r="F89" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="34">
+      <c r="G89" s="12">
         <f>H89*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H89" s="34">
+      <c r="H89" s="12">
         <f>IF(OR(D89="",F89=""),0,D89*F89)</f>
         <v/>
       </c>
-      <c r="I89" s="34">
+      <c r="I89" s="12">
         <f>H89*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="106">
-      <c r="B90" s="23" t="n"/>
-      <c r="C90" s="23" t="n"/>
-      <c r="D90" s="23" t="n">
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E90" s="23" t="inlineStr">
+      <c r="E90" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9552,26 +9588,26 @@
       <c r="F90" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G90" s="34">
+      <c r="G90" s="12">
         <f>H90*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H90" s="34">
+      <c r="H90" s="12">
         <f>IF(OR(D90="",F90=""),0,D90*F90)</f>
         <v/>
       </c>
-      <c r="I90" s="34">
+      <c r="I90" s="12">
         <f>H90*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="106">
-      <c r="B91" s="23" t="n"/>
-      <c r="C91" s="23" t="n"/>
-      <c r="D91" s="23" t="n">
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E91" s="23" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9579,26 +9615,26 @@
       <c r="F91" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G91" s="34">
+      <c r="G91" s="12">
         <f>H91*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H91" s="34">
+      <c r="H91" s="12">
         <f>IF(OR(D91="",F91=""),0,D91*F91)</f>
         <v/>
       </c>
-      <c r="I91" s="34">
+      <c r="I91" s="12">
         <f>H91*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="106">
-      <c r="B92" s="23" t="n"/>
-      <c r="C92" s="23" t="n"/>
-      <c r="D92" s="23" t="n">
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="9" t="n"/>
+      <c r="D92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="23" t="inlineStr">
+      <c r="E92" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9606,26 +9642,26 @@
       <c r="F92" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G92" s="34">
+      <c r="G92" s="12">
         <f>H92*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H92" s="34">
+      <c r="H92" s="12">
         <f>IF(OR(D92="",F92=""),0,D92*F92)</f>
         <v/>
       </c>
-      <c r="I92" s="34">
+      <c r="I92" s="12">
         <f>H92*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="106">
-      <c r="B93" s="23" t="n"/>
-      <c r="C93" s="23" t="n"/>
-      <c r="D93" s="23" t="n">
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="9" t="n"/>
+      <c r="D93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="23" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9633,26 +9669,26 @@
       <c r="F93" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G93" s="34">
+      <c r="G93" s="12">
         <f>H93*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H93" s="34">
+      <c r="H93" s="12">
         <f>IF(OR(D93="",F93=""),0,D93*F93)</f>
         <v/>
       </c>
-      <c r="I93" s="34">
+      <c r="I93" s="12">
         <f>H93*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="106">
-      <c r="B94" s="23" t="n"/>
-      <c r="C94" s="23" t="n"/>
-      <c r="D94" s="23" t="n">
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="23" t="inlineStr">
+      <c r="E94" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9660,26 +9696,26 @@
       <c r="F94" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G94" s="34">
+      <c r="G94" s="12">
         <f>H94*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H94" s="34">
+      <c r="H94" s="12">
         <f>IF(OR(D94="",F94=""),0,D94*F94)</f>
         <v/>
       </c>
-      <c r="I94" s="34">
+      <c r="I94" s="12">
         <f>H94*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="106">
-      <c r="B95" s="23" t="n"/>
-      <c r="C95" s="23" t="n"/>
-      <c r="D95" s="23" t="n">
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="23" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9687,26 +9723,26 @@
       <c r="F95" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G95" s="34">
+      <c r="G95" s="12">
         <f>H95*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H95" s="34">
+      <c r="H95" s="12">
         <f>IF(OR(D95="",F95=""),0,D95*F95)</f>
         <v/>
       </c>
-      <c r="I95" s="34">
+      <c r="I95" s="12">
         <f>H95*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="106">
-      <c r="B96" s="23" t="n"/>
-      <c r="C96" s="23" t="n"/>
-      <c r="D96" s="23" t="n">
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E96" s="23" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -9714,34 +9750,34 @@
       <c r="F96" s="102" t="n">
         <v>0</v>
       </c>
-      <c r="G96" s="34">
+      <c r="G96" s="12">
         <f>H96*(1+'Параметры'!$C$6)</f>
         <v/>
       </c>
-      <c r="H96" s="34">
+      <c r="H96" s="12">
         <f>IF(OR(D96="",F96=""),0,D96*F96)</f>
         <v/>
       </c>
-      <c r="I96" s="34">
+      <c r="I96" s="12">
         <f>H96*'Параметры'!$C$6</f>
         <v/>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="106">
-      <c r="F97" s="99" t="inlineStr">
+      <c r="F97" s="98" t="inlineStr">
         <is>
           <t>ДОПОЛНИТЕЛЬНЫЕ КОМПЛЕКТУЮЩИЕ — себестоимость:</t>
         </is>
       </c>
-      <c r="G97" s="18">
+      <c r="G97" s="23">
         <f>SUM(G87:G96)</f>
         <v/>
       </c>
-      <c r="H97" s="18">
+      <c r="H97" s="23">
         <f>SUM(H87:H96)</f>
         <v/>
       </c>
-      <c r="I97" s="18">
+      <c r="I97" s="23">
         <f>SUM(I87:I96)</f>
         <v/>
       </c>
@@ -9753,7 +9789,7 @@
           <t>ВСЕГО металл — себестоимость:</t>
         </is>
       </c>
-      <c r="H99" s="57">
+      <c r="H99" s="49">
         <f>H37+H52+H67+H82+H97</f>
         <v/>
       </c>
@@ -9771,7 +9807,7 @@
     </row>
     <row r="101" ht="15.75" customHeight="1" s="106"/>
     <row r="102" ht="15.75" customHeight="1" s="106">
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Обновление прайса: меняйте жёлтые цены в колонке F. Кол-во D — под заказ. Прокат, плазма, ковка, токарка и комплектующие — с наценкой менеджера. Итоги уходят в Калькуляцию автоматически.</t>
         </is>
@@ -10713,27 +10749,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>ЛЕНДИНГ-КП ДЛЯ PDF (стиль Cenzyk). Цена — со Сводки. Жёлтые доли раскладывают Итого. Экспорт: Файл → PDF.</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Цена КП:</t>
         </is>
       </c>
-      <c r="G1" s="8">
+      <c r="G1" s="21">
         <f>'Сводка'!D24</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="17">
+      <c r="B3" s="26">
         <f>UPPER('Параметры'!C23)&amp;"  ·  КП"</f>
         <v/>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>№</t>
         </is>
@@ -10765,35 +10801,35 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="37" t="n"/>
-      <c r="C8" s="37" t="n"/>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
+      <c r="B8" s="39" t="n"/>
+      <c r="C8" s="39" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>КЛИЕНТ</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="42">
         <f>'Сводка'!C10</f>
         <v/>
       </c>
       <c r="D9" s="116" t="n"/>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>ОБЪЕКТ</t>
         </is>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="42">
         <f>'Сводка'!C6</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>ДАТА</t>
         </is>
@@ -10803,25 +10839,25 @@
         <v/>
       </c>
       <c r="D10" s="116" t="n"/>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>АКТУАЛЬНО ДО</t>
         </is>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="47">
         <f>C10+'Параметры'!C31</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37" t="n"/>
-      <c r="C11" s="37" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="37" t="n"/>
-      <c r="F11" s="37" t="n"/>
+      <c r="B11" s="39" t="n"/>
+      <c r="C11" s="39" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>01  /  ВИЗУАЛИЗАЦИЯ</t>
         </is>
@@ -10833,18 +10869,18 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="106">
-      <c r="B13" s="49" t="inlineStr">
+      <c r="B13" s="52" t="inlineStr">
         <is>
           <t>РАКУРС 1  ·  ФРОНТ</t>
         </is>
       </c>
       <c r="C13" s="116" t="n"/>
-      <c r="D13" s="49" t="inlineStr">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>РАКУРС 2  ·  3/4</t>
         </is>
       </c>
-      <c r="E13" s="49" t="inlineStr">
+      <c r="E13" s="52" t="inlineStr">
         <is>
           <t>РАКУРС 3  ·  СБОКУ</t>
         </is>
@@ -10930,14 +10966,14 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="106">
-      <c r="B23" s="37" t="n"/>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
+      <c r="B23" s="39" t="n"/>
+      <c r="C23" s="39" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="106">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>02  /  ИЗДЕЛИЕ</t>
         </is>
@@ -10957,21 +10993,21 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
-      <c r="B28" s="37" t="n"/>
-      <c r="C28" s="37" t="n"/>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
+      <c r="B28" s="39" t="n"/>
+      <c r="C28" s="39" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="106">
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>03  /  СОСТАВ РАБОТ</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="106">
-      <c r="B30" s="67" t="inlineStr">
+      <c r="B30" s="71" t="inlineStr">
         <is>
           <t>01</t>
         </is>
@@ -10982,16 +11018,16 @@
         </is>
       </c>
       <c r="D30" s="116" t="n"/>
-      <c r="E30" s="69" t="n">
+      <c r="E30" s="73" t="n">
         <v>0.05</v>
       </c>
-      <c r="F30" s="71">
+      <c r="F30" s="74">
         <f>IF('Сводка'!$D$24=0,0,ROUND('Сводка'!$D$24*E30,2))</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="106">
-      <c r="B31" s="37" t="n"/>
+      <c r="B31" s="39" t="n"/>
       <c r="C31" s="132" t="inlineStr">
         <is>
           <t>замер, эскизы, лекала</t>
@@ -10999,7 +11035,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="106">
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="71" t="inlineStr">
         <is>
           <t>02</t>
         </is>
@@ -11010,16 +11046,16 @@
         </is>
       </c>
       <c r="D32" s="116" t="n"/>
-      <c r="E32" s="69" t="n">
+      <c r="E32" s="73" t="n">
         <v>0.35</v>
       </c>
-      <c r="F32" s="71">
+      <c r="F32" s="74">
         <f>IF('Сводка'!$D$24=0,0,ROUND('Сводка'!$D$24*E32,2))</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="106">
-      <c r="B33" s="37" t="n"/>
+      <c r="B33" s="39" t="n"/>
       <c r="C33" s="132" t="inlineStr">
         <is>
           <t>металл, комплектующие, резка / токарка</t>
@@ -11027,7 +11063,7 @@
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" s="106">
-      <c r="B34" s="67" t="inlineStr">
+      <c r="B34" s="71" t="inlineStr">
         <is>
           <t>03</t>
         </is>
@@ -11038,16 +11074,16 @@
         </is>
       </c>
       <c r="D34" s="116" t="n"/>
-      <c r="E34" s="69" t="n">
+      <c r="E34" s="73" t="n">
         <v>0.35</v>
       </c>
-      <c r="F34" s="71">
+      <c r="F34" s="74">
         <f>IF('Сводка'!$D$24=0,0,ROUND('Сводка'!$D$24*E34,2))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="106">
-      <c r="B35" s="37" t="n"/>
+      <c r="B35" s="39" t="n"/>
       <c r="C35" s="132" t="inlineStr">
         <is>
           <t>цех, сварка, расходники</t>
@@ -11055,7 +11091,7 @@
       </c>
     </row>
     <row r="36" ht="24" customHeight="1" s="106">
-      <c r="B36" s="67" t="inlineStr">
+      <c r="B36" s="71" t="inlineStr">
         <is>
           <t>04</t>
         </is>
@@ -11066,16 +11102,16 @@
         </is>
       </c>
       <c r="D36" s="116" t="n"/>
-      <c r="E36" s="69" t="n">
+      <c r="E36" s="73" t="n">
         <v>0.1</v>
       </c>
-      <c r="F36" s="71">
+      <c r="F36" s="74">
         <f>IF('Сводка'!$D$24=0,0,ROUND('Сводка'!$D$24*E36,2))</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="106">
-      <c r="B37" s="37" t="n"/>
+      <c r="B37" s="39" t="n"/>
       <c r="C37" s="132" t="inlineStr">
         <is>
           <t>эмаль / порошок / пескоструй</t>
@@ -11083,7 +11119,7 @@
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" s="106">
-      <c r="B38" s="67" t="inlineStr">
+      <c r="B38" s="71" t="inlineStr">
         <is>
           <t>05</t>
         </is>
@@ -11094,16 +11130,16 @@
         </is>
       </c>
       <c r="D38" s="116" t="n"/>
-      <c r="E38" s="69" t="n">
+      <c r="E38" s="73" t="n">
         <v>0.15</v>
       </c>
-      <c r="F38" s="71">
+      <c r="F38" s="74">
         <f>IF('Сводка'!$D$24=0,0,ROUND('Сводка'!$D$24*E38,2))</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="106">
-      <c r="B39" s="37" t="n"/>
+      <c r="B39" s="39" t="n"/>
       <c r="C39" s="132" t="inlineStr">
         <is>
           <t>доставка на объект, установка</t>
@@ -11111,21 +11147,21 @@
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106">
-      <c r="B40" s="37" t="n"/>
-      <c r="C40" s="37" t="n"/>
-      <c r="D40" s="37" t="n"/>
-      <c r="E40" s="37" t="n"/>
-      <c r="F40" s="37" t="n"/>
+      <c r="B40" s="39" t="n"/>
+      <c r="C40" s="39" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="106">
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>ДОЛИ</t>
         </is>
       </c>
-      <c r="C41" s="37" t="n"/>
-      <c r="D41" s="37" t="n"/>
-      <c r="E41" s="64">
+      <c r="C41" s="39" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="55">
         <f>SUM(E30,E32,E34,E36,E38)</f>
         <v/>
       </c>
@@ -11135,11 +11171,11 @@
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="106">
-      <c r="B42" s="37" t="n"/>
-      <c r="C42" s="37" t="n"/>
-      <c r="D42" s="37" t="n"/>
-      <c r="E42" s="37" t="n"/>
-      <c r="F42" s="37" t="n"/>
+      <c r="B42" s="39" t="n"/>
+      <c r="C42" s="39" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
     </row>
     <row r="43" ht="27.75" customHeight="1" s="106">
       <c r="B43" s="134" t="inlineStr">
@@ -11163,14 +11199,14 @@
       <c r="F44" s="128" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="106">
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>СВОДКА</t>
         </is>
       </c>
-      <c r="C45" s="37" t="n"/>
-      <c r="D45" s="37" t="n"/>
-      <c r="E45" s="80">
+      <c r="C45" s="39" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="81">
         <f>'Сводка'!D24</f>
         <v/>
       </c>
@@ -11180,11 +11216,11 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="106">
-      <c r="B46" s="37" t="n"/>
-      <c r="C46" s="37" t="n"/>
-      <c r="D46" s="37" t="n"/>
-      <c r="E46" s="37" t="n"/>
-      <c r="F46" s="37" t="n"/>
+      <c r="B46" s="39" t="n"/>
+      <c r="C46" s="39" t="n"/>
+      <c r="D46" s="39" t="n"/>
+      <c r="E46" s="39" t="n"/>
+      <c r="F46" s="39" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="106">
       <c r="B47" s="138" t="inlineStr">
@@ -11192,8 +11228,8 @@
           <t>ПРОВЕДЕНИЕ ЧЕРЕЗ СЗ 4%  ·  ФИЗ. ЛИЦО</t>
         </is>
       </c>
-      <c r="E47" s="37" t="n"/>
-      <c r="F47" s="82">
+      <c r="E47" s="39" t="n"/>
+      <c r="F47" s="83">
         <f>E43*1.04</f>
         <v/>
       </c>
@@ -11204,21 +11240,21 @@
           <t>ПРОВЕДЕНИЕ ЧЕРЕЗ СЗ 6%  ·  ЮР. ЛИЦО</t>
         </is>
       </c>
-      <c r="E48" s="37" t="n"/>
-      <c r="F48" s="82">
+      <c r="E48" s="39" t="n"/>
+      <c r="F48" s="83">
         <f>E43*1.06</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="106">
-      <c r="B49" s="37" t="n"/>
-      <c r="C49" s="37" t="n"/>
-      <c r="D49" s="37" t="n"/>
-      <c r="E49" s="37" t="n"/>
-      <c r="F49" s="37" t="n"/>
+      <c r="B49" s="39" t="n"/>
+      <c r="C49" s="39" t="n"/>
+      <c r="D49" s="39" t="n"/>
+      <c r="E49" s="39" t="n"/>
+      <c r="F49" s="39" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="106">
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>04  /  УСЛОВИЯ</t>
         </is>
@@ -11231,11 +11267,11 @@
         </is>
       </c>
       <c r="C51" s="116" t="n"/>
-      <c r="D51" s="69" t="n">
+      <c r="D51" s="73" t="n">
         <v>0.5</v>
       </c>
-      <c r="E51" s="83" t="n"/>
-      <c r="F51" s="71">
+      <c r="E51" s="84" t="n"/>
+      <c r="F51" s="74">
         <f>E43*D51</f>
         <v/>
       </c>
@@ -11248,8 +11284,8 @@
       </c>
       <c r="C52" s="139" t="n"/>
       <c r="D52" s="116" t="n"/>
-      <c r="E52" s="83" t="n"/>
-      <c r="F52" s="71">
+      <c r="E52" s="84" t="n"/>
+      <c r="F52" s="74">
         <f>E43-F51</f>
         <v/>
       </c>
@@ -11270,11 +11306,11 @@
       <c r="F53" s="116" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="106">
-      <c r="B54" s="37" t="n"/>
-      <c r="C54" s="37" t="n"/>
-      <c r="D54" s="37" t="n"/>
-      <c r="E54" s="37" t="n"/>
-      <c r="F54" s="37" t="n"/>
+      <c r="B54" s="39" t="n"/>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="39" t="n"/>
+      <c r="F54" s="39" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="106">
       <c r="B55" s="141" t="inlineStr">
@@ -11328,9 +11364,9 @@
         <f>"A  "&amp;'Параметры'!C25</f>
         <v/>
       </c>
-      <c r="D60" s="37" t="n"/>
-      <c r="E60" s="37" t="n"/>
-      <c r="F60" s="37" t="n"/>
+      <c r="D60" s="39" t="n"/>
+      <c r="E60" s="39" t="n"/>
+      <c r="F60" s="39" t="n"/>
     </row>
     <row r="61" ht="24" customHeight="1" s="106">
       <c r="B61" s="143">
@@ -11339,74 +11375,74 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="106">
-      <c r="B62" s="37" t="n"/>
-      <c r="C62" s="37" t="n"/>
-      <c r="D62" s="37" t="n"/>
-      <c r="E62" s="37" t="n"/>
-      <c r="F62" s="37" t="n"/>
+      <c r="B62" s="39" t="n"/>
+      <c r="C62" s="39" t="n"/>
+      <c r="D62" s="39" t="n"/>
+      <c r="E62" s="39" t="n"/>
+      <c r="F62" s="39" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="106">
-      <c r="B63" s="37" t="n"/>
-      <c r="C63" s="37" t="n"/>
-      <c r="D63" s="37" t="n"/>
-      <c r="E63" s="37" t="n"/>
-      <c r="F63" s="37" t="n"/>
+      <c r="B63" s="39" t="n"/>
+      <c r="C63" s="39" t="n"/>
+      <c r="D63" s="39" t="n"/>
+      <c r="E63" s="39" t="n"/>
+      <c r="F63" s="39" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="106">
-      <c r="B64" s="37" t="n"/>
-      <c r="C64" s="37" t="n"/>
-      <c r="D64" s="37" t="n"/>
-      <c r="E64" s="37" t="n"/>
-      <c r="F64" s="37" t="n"/>
+      <c r="B64" s="39" t="n"/>
+      <c r="C64" s="39" t="n"/>
+      <c r="D64" s="39" t="n"/>
+      <c r="E64" s="39" t="n"/>
+      <c r="F64" s="39" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="106">
-      <c r="B65" s="37" t="n"/>
-      <c r="C65" s="37" t="n"/>
-      <c r="D65" s="37" t="n"/>
-      <c r="E65" s="37" t="n"/>
-      <c r="F65" s="37" t="n"/>
+      <c r="B65" s="39" t="n"/>
+      <c r="C65" s="39" t="n"/>
+      <c r="D65" s="39" t="n"/>
+      <c r="E65" s="39" t="n"/>
+      <c r="F65" s="39" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="106">
-      <c r="B66" s="37" t="n"/>
-      <c r="C66" s="37" t="n"/>
-      <c r="D66" s="37" t="n"/>
-      <c r="E66" s="37" t="n"/>
-      <c r="F66" s="37" t="n"/>
+      <c r="B66" s="39" t="n"/>
+      <c r="C66" s="39" t="n"/>
+      <c r="D66" s="39" t="n"/>
+      <c r="E66" s="39" t="n"/>
+      <c r="F66" s="39" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="106">
-      <c r="B67" s="37" t="n"/>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="37" t="n"/>
-      <c r="E67" s="37" t="n"/>
-      <c r="F67" s="37" t="n"/>
+      <c r="B67" s="39" t="n"/>
+      <c r="C67" s="39" t="n"/>
+      <c r="D67" s="39" t="n"/>
+      <c r="E67" s="39" t="n"/>
+      <c r="F67" s="39" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="106">
-      <c r="B68" s="37" t="n"/>
-      <c r="C68" s="37" t="n"/>
-      <c r="D68" s="37" t="n"/>
-      <c r="E68" s="37" t="n"/>
-      <c r="F68" s="37" t="n"/>
+      <c r="B68" s="39" t="n"/>
+      <c r="C68" s="39" t="n"/>
+      <c r="D68" s="39" t="n"/>
+      <c r="E68" s="39" t="n"/>
+      <c r="F68" s="39" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="106">
-      <c r="B69" s="37" t="n"/>
-      <c r="C69" s="37" t="n"/>
-      <c r="D69" s="37" t="n"/>
-      <c r="E69" s="37" t="n"/>
-      <c r="F69" s="37" t="n"/>
+      <c r="B69" s="39" t="n"/>
+      <c r="C69" s="39" t="n"/>
+      <c r="D69" s="39" t="n"/>
+      <c r="E69" s="39" t="n"/>
+      <c r="F69" s="39" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="106">
-      <c r="B70" s="37" t="n"/>
-      <c r="C70" s="37" t="n"/>
-      <c r="D70" s="37" t="n"/>
-      <c r="E70" s="37" t="n"/>
-      <c r="F70" s="37" t="n"/>
+      <c r="B70" s="39" t="n"/>
+      <c r="C70" s="39" t="n"/>
+      <c r="D70" s="39" t="n"/>
+      <c r="E70" s="39" t="n"/>
+      <c r="F70" s="39" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="106">
-      <c r="B71" s="37" t="n"/>
-      <c r="C71" s="37" t="n"/>
-      <c r="D71" s="37" t="n"/>
-      <c r="E71" s="37" t="n"/>
-      <c r="F71" s="37" t="n"/>
+      <c r="B71" s="39" t="n"/>
+      <c r="C71" s="39" t="n"/>
+      <c r="D71" s="39" t="n"/>
+      <c r="E71" s="39" t="n"/>
+      <c r="F71" s="39" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="106"/>
     <row r="73" ht="15.75" customHeight="1" s="106"/>
@@ -12436,31 +12472,31 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Меняйте только жёлтые ячейки. Все калькуляции подтягивают значения отсюда.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Наценка менеджера на закупки</t>
         </is>
@@ -12475,7 +12511,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Целевая маржа проекта (от выручки)</t>
         </is>
@@ -12490,7 +12526,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Минимальная допустимая маржа</t>
         </is>
@@ -12505,7 +12541,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Налог НПД (самозанятость)</t>
         </is>
@@ -12520,7 +12556,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Аренда, ₽ / рабочий день</t>
         </is>
@@ -12535,7 +12571,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Рабочих дней в месяце</t>
         </is>
@@ -12550,7 +12586,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Агентские, % от цены КП</t>
         </is>
@@ -12572,7 +12608,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Множитель цены при целевой марже</t>
         </is>
@@ -12588,7 +12624,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Множитель цены при минимальной марже</t>
         </is>
@@ -12607,7 +12643,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Имя в шапке КП</t>
         </is>
@@ -12620,7 +12656,7 @@
       <c r="D19" s="108" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Подзаголовок</t>
         </is>
@@ -12633,7 +12669,7 @@
       <c r="D20" s="108" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="106">
-      <c r="B21" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>ФИО полностью</t>
         </is>
@@ -12646,7 +12682,7 @@
       <c r="D21" s="108" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="106">
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
@@ -12659,7 +12695,7 @@
       <c r="D22" s="108" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="106">
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
@@ -12672,7 +12708,7 @@
       <c r="D23" s="108" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="106">
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
@@ -12685,7 +12721,7 @@
       <c r="D24" s="108" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="106">
-      <c r="B25" s="9" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Адрес</t>
         </is>
@@ -12698,7 +12734,7 @@
       <c r="D25" s="108" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="106">
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>График Пн–Пт</t>
         </is>
@@ -12711,7 +12747,7 @@
       <c r="D26" s="108" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="106">
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>График Сб</t>
         </is>
@@ -12724,7 +12760,7 @@
       <c r="D27" s="108" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>График Вс</t>
         </is>
@@ -12737,7 +12773,7 @@
       <c r="D28" s="108" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="106">
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Стаж</t>
         </is>
@@ -12750,7 +12786,7 @@
       <c r="D29" s="108" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="106">
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Профиль (текст)</t>
         </is>
@@ -12763,7 +12799,7 @@
       <c r="D30" s="108" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="106">
-      <c r="B31" s="9" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Срок действия КП, дней</t>
         </is>
@@ -12782,56 +12818,56 @@
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="106">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Ворота</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="106">
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>Забор</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="106">
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Лестница</t>
         </is>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="106">
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Мебель</t>
         </is>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="106">
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>Интерьер</t>
         </is>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="106">
-      <c r="B39" s="9" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Экстерьер</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106">
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>Сувенир</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="106">
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>Прочее</t>
         </is>
@@ -13887,76 +13923,76 @@
       <c r="D9" s="108" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Что за платёж</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="102" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
       <c r="D12" s="102" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
       <c r="D13" s="102" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
       <c r="D14" s="102" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="102" t="n"/>
     </row>
     <row r="16">
-      <c r="C16" s="99" t="inlineStr">
+      <c r="C16" s="98" t="inlineStr">
         <is>
           <t>Всего получено:</t>
         </is>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="23">
         <f>SUM(D11:D15)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="99" t="inlineStr">
+      <c r="C17" s="98" t="inlineStr">
         <is>
           <t>Цена КП (из Сводки, только для справки):</t>
         </is>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="12">
         <f>'Сводка'!D24</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="99" t="inlineStr">
+      <c r="C18" s="98" t="inlineStr">
         <is>
           <t>Ещё должен клиент:</t>
         </is>
       </c>
-      <c r="D18" s="100">
+      <c r="D18" s="99">
         <f>D17-D16</f>
         <v/>
       </c>
@@ -13971,148 +14007,148 @@
       <c r="D20" s="108" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="106">
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Кому / за что</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Сумма</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="106">
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="23" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
       <c r="D22" s="102" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="106">
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="23" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="102" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="106">
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
       <c r="D24" s="102" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="106">
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
       <c r="D25" s="102" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="106">
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="23" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
       <c r="D26" s="102" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="106">
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="23" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
       <c r="D27" s="102" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="106">
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="23" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
       <c r="D28" s="102" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="106">
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="23" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
       <c r="D29" s="102" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="106">
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="23" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
       <c r="D30" s="102" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="106">
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="23" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
       <c r="D31" s="102" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="106">
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="23" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
       <c r="D32" s="102" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="106">
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="23" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
       <c r="D33" s="102" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="106">
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
       <c r="D34" s="102" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="106">
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="23" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
       <c r="D35" s="102" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="106">
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
       <c r="D36" s="102" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="106">
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
       <c r="D37" s="102" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="106">
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
       <c r="D38" s="102" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="106">
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
       <c r="D39" s="102" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="106">
-      <c r="B40" s="23" t="n"/>
-      <c r="C40" s="23" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
       <c r="D40" s="102" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="106">
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="23" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
       <c r="D41" s="102" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="106"/>
     <row r="43" ht="15.75" customHeight="1" s="106">
-      <c r="C43" s="99" t="inlineStr">
+      <c r="C43" s="98" t="inlineStr">
         <is>
           <t>Всего выплат:</t>
         </is>
       </c>
-      <c r="D43" s="18">
+      <c r="D43" s="23">
         <f>SUM(D22:D41)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="106">
-      <c r="C44" s="99" t="inlineStr">
+      <c r="C44" s="98" t="inlineStr">
         <is>
           <t>Живые деньги по заказу сейчас (получено − выплаты):</t>
         </is>
       </c>
-      <c r="D44" s="57">
+      <c r="D44" s="49">
         <f>D16-D43</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="106"/>
     <row r="46" ht="15.75" customHeight="1" s="106">
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Пример: КП 100 000, аванс 50 000, купили металл 20 000 → получено 50 000, выплат 20 000, в кассе заказа 30 000. Прибыль при этом смотрите на Сводке, не здесь.</t>
         </is>
